--- a/database/event/7440/event_7440_evp_summary.xlsx
+++ b/database/event/7440/event_7440_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>11.2022</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>7.0838</v>
       </c>
       <c r="D2" t="n">
         <v>4.1041</v>
@@ -545,7 +545,7 @@
         <v>8.5114</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>5.3823</v>
       </c>
       <c r="D3" t="n">
         <v>3.0171</v>
@@ -591,7 +591,7 @@
         <v>7.8542</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>4.9667</v>
       </c>
       <c r="D4" t="n">
         <v>2.7516</v>
@@ -637,7 +637,7 @@
         <v>7.7711</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>4.9141</v>
       </c>
       <c r="D5" t="n">
         <v>2.718</v>
@@ -683,7 +683,7 @@
         <v>6.3869</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>4.0388</v>
       </c>
       <c r="D6" t="n">
         <v>2.1588</v>
@@ -729,7 +729,7 @@
         <v>6.2998</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>3.9838</v>
       </c>
       <c r="D7" t="n">
         <v>2.1236</v>
@@ -775,7 +775,7 @@
         <v>6.2358</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>3.9433</v>
       </c>
       <c r="D8" t="n">
         <v>2.0978</v>
@@ -821,7 +821,7 @@
         <v>6.1456</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>3.8862</v>
       </c>
       <c r="D9" t="n">
         <v>2.0613</v>
@@ -867,7 +867,7 @@
         <v>6.018</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>3.8056</v>
       </c>
       <c r="D10" t="n">
         <v>2.0098</v>
@@ -913,7 +913,7 @@
         <v>6.0002</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>3.7943</v>
       </c>
       <c r="D11" t="n">
         <v>2.0026</v>
@@ -959,7 +959,7 @@
         <v>5.5185</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>3.4897</v>
       </c>
       <c r="D12" t="n">
         <v>1.808</v>
@@ -1005,7 +1005,7 @@
         <v>5.4428</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>3.4418</v>
       </c>
       <c r="D13" t="n">
         <v>1.7774</v>
@@ -1051,7 +1051,7 @@
         <v>5.3753</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>3.3991</v>
       </c>
       <c r="D14" t="n">
         <v>1.7501</v>
@@ -1097,7 +1097,7 @@
         <v>5.3027</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3.3532</v>
       </c>
       <c r="D15" t="n">
         <v>1.7208</v>
@@ -1143,7 +1143,7 @@
         <v>5.281</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.3395</v>
       </c>
       <c r="D16" t="n">
         <v>1.712</v>
@@ -1189,7 +1189,7 @@
         <v>4.9833</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>3.1512</v>
       </c>
       <c r="D17" t="n">
         <v>1.5918</v>
@@ -1235,7 +1235,7 @@
         <v>4.9285</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>3.1166</v>
       </c>
       <c r="D18" t="n">
         <v>1.5696</v>
@@ -1281,7 +1281,7 @@
         <v>4.927</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3.1156</v>
       </c>
       <c r="D19" t="n">
         <v>1.569</v>
@@ -1327,7 +1327,7 @@
         <v>4.8747</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>3.0826</v>
       </c>
       <c r="D20" t="n">
         <v>1.5479</v>
@@ -1373,7 +1373,7 @@
         <v>4.8473</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>3.0652</v>
       </c>
       <c r="D21" t="n">
         <v>1.5368</v>
@@ -1419,7 +1419,7 @@
         <v>4.8196</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>3.0477</v>
       </c>
       <c r="D22" t="n">
         <v>1.5256</v>
@@ -1465,7 +1465,7 @@
         <v>4.8182</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>3.0468</v>
       </c>
       <c r="D23" t="n">
         <v>1.5251</v>
@@ -1511,7 +1511,7 @@
         <v>4.6388</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2.9334</v>
       </c>
       <c r="D24" t="n">
         <v>1.4526</v>
@@ -1557,7 +1557,7 @@
         <v>4.5466</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>2.8751</v>
       </c>
       <c r="D25" t="n">
         <v>1.4154</v>
@@ -1603,7 +1603,7 @@
         <v>4.5291</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>2.864</v>
       </c>
       <c r="D26" t="n">
         <v>1.4083</v>
@@ -1649,7 +1649,7 @@
         <v>4.4431</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>2.8096</v>
       </c>
       <c r="D27" t="n">
         <v>1.3736</v>
@@ -1695,7 +1695,7 @@
         <v>4.4324</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>2.8029</v>
       </c>
       <c r="D28" t="n">
         <v>1.3692</v>
@@ -1741,7 +1741,7 @@
         <v>4.4279</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="D29" t="n">
         <v>1.3674</v>
@@ -1787,7 +1787,7 @@
         <v>4.367</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>2.7615</v>
       </c>
       <c r="D30" t="n">
         <v>1.3428</v>
@@ -1833,7 +1833,7 @@
         <v>4.1769</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>2.6413</v>
       </c>
       <c r="D31" t="n">
         <v>1.266</v>
@@ -1879,7 +1879,7 @@
         <v>3.7105</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>2.3464</v>
       </c>
       <c r="D32" t="n">
         <v>1.0776</v>
@@ -1925,7 +1925,7 @@
         <v>3.6863</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>2.3311</v>
       </c>
       <c r="D33" t="n">
         <v>1.0678</v>
@@ -1971,7 +1971,7 @@
         <v>3.602</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>2.2778</v>
       </c>
       <c r="D34" t="n">
         <v>1.0338</v>
@@ -2017,7 +2017,7 @@
         <v>3.5733</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>2.2596</v>
       </c>
       <c r="D35" t="n">
         <v>1.0222</v>
@@ -2063,7 +2063,7 @@
         <v>3.564</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>2.2537</v>
       </c>
       <c r="D36" t="n">
         <v>1.0184</v>
@@ -2109,7 +2109,7 @@
         <v>3.416</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>2.1601</v>
       </c>
       <c r="D37" t="n">
         <v>0.9586</v>
@@ -2155,7 +2155,7 @@
         <v>3.3579</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>2.1234</v>
       </c>
       <c r="D38" t="n">
         <v>0.9352</v>
@@ -2201,7 +2201,7 @@
         <v>3.3207</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>2.0999</v>
       </c>
       <c r="D39" t="n">
         <v>0.9201</v>
@@ -2247,7 +2247,7 @@
         <v>3.2063</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>2.0275</v>
       </c>
       <c r="D40" t="n">
         <v>0.8739</v>
@@ -2293,7 +2293,7 @@
         <v>3.128</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>1.978</v>
       </c>
       <c r="D41" t="n">
         <v>0.8423</v>
@@ -2339,7 +2339,7 @@
         <v>3.0688</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1.9406</v>
       </c>
       <c r="D42" t="n">
         <v>0.8184</v>
@@ -2385,7 +2385,7 @@
         <v>3.0037</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>1.8994</v>
       </c>
       <c r="D43" t="n">
         <v>0.7921</v>
@@ -2431,7 +2431,7 @@
         <v>2.9921</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>1.8921</v>
       </c>
       <c r="D44" t="n">
         <v>0.7874</v>
@@ -2477,7 +2477,7 @@
         <v>2.9626</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1.8734</v>
       </c>
       <c r="D45" t="n">
         <v>0.7755</v>
@@ -2523,7 +2523,7 @@
         <v>2.9363</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>1.8568</v>
       </c>
       <c r="D46" t="n">
         <v>0.7648</v>
@@ -2569,7 +2569,7 @@
         <v>2.8768</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>1.8192</v>
       </c>
       <c r="D47" t="n">
         <v>0.7408</v>
@@ -2615,7 +2615,7 @@
         <v>2.8521</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>1.8036</v>
       </c>
       <c r="D48" t="n">
         <v>0.7308</v>
@@ -2661,7 +2661,7 @@
         <v>2.6461</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>1.6733</v>
       </c>
       <c r="D49" t="n">
         <v>0.6476</v>
@@ -2707,7 +2707,7 @@
         <v>2.6378</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>1.668</v>
       </c>
       <c r="D50" t="n">
         <v>0.6443</v>
@@ -2753,7 +2753,7 @@
         <v>2.6221</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>1.6581</v>
       </c>
       <c r="D51" t="n">
         <v>0.6379</v>
@@ -2799,7 +2799,7 @@
         <v>2.6073</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>1.6488</v>
       </c>
       <c r="D52" t="n">
         <v>0.6319</v>
@@ -2845,7 +2845,7 @@
         <v>2.5867</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1.6357</v>
       </c>
       <c r="D53" t="n">
         <v>0.6236</v>
@@ -2891,7 +2891,7 @@
         <v>2.4898</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>1.5745</v>
       </c>
       <c r="D54" t="n">
         <v>0.5845</v>
@@ -2937,7 +2937,7 @@
         <v>2.3755</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>1.5022</v>
       </c>
       <c r="D55" t="n">
         <v>0.5383</v>
@@ -2983,7 +2983,7 @@
         <v>2.2905</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>1.4484</v>
       </c>
       <c r="D56" t="n">
         <v>0.5039</v>
@@ -3029,7 +3029,7 @@
         <v>2.2659</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>1.4329</v>
       </c>
       <c r="D57" t="n">
         <v>0.494</v>
@@ -3075,7 +3075,7 @@
         <v>2.2233</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>1.4059</v>
       </c>
       <c r="D58" t="n">
         <v>0.4768</v>
@@ -3121,7 +3121,7 @@
         <v>2.0755</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>1.3125</v>
       </c>
       <c r="D59" t="n">
         <v>0.4171</v>
@@ -3167,7 +3167,7 @@
         <v>2.0664</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>1.3067</v>
       </c>
       <c r="D60" t="n">
         <v>0.4134</v>
@@ -3213,7 +3213,7 @@
         <v>2.0478</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>1.295</v>
       </c>
       <c r="D61" t="n">
         <v>0.4059</v>
@@ -3259,7 +3259,7 @@
         <v>2.0259</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>1.2811</v>
       </c>
       <c r="D62" t="n">
         <v>0.3971</v>
@@ -3305,7 +3305,7 @@
         <v>1.9955</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>1.2619</v>
       </c>
       <c r="D63" t="n">
         <v>0.3848</v>
@@ -3351,7 +3351,7 @@
         <v>1.9438</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>1.2292</v>
       </c>
       <c r="D64" t="n">
         <v>0.3639</v>
@@ -3397,7 +3397,7 @@
         <v>1.9271</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="D65" t="n">
         <v>0.3571</v>
@@ -3443,7 +3443,7 @@
         <v>1.926</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>1.2179</v>
       </c>
       <c r="D66" t="n">
         <v>0.3567</v>
@@ -3489,7 +3489,7 @@
         <v>1.9009</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>1.2021</v>
       </c>
       <c r="D67" t="n">
         <v>0.3466</v>
@@ -3535,7 +3535,7 @@
         <v>1.8992</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>1.201</v>
       </c>
       <c r="D68" t="n">
         <v>0.3459</v>
@@ -3581,7 +3581,7 @@
         <v>1.8826</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>1.1905</v>
       </c>
       <c r="D69" t="n">
         <v>0.3392</v>
@@ -3627,7 +3627,7 @@
         <v>1.8595</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>1.1759</v>
       </c>
       <c r="D70" t="n">
         <v>0.3298</v>
@@ -3673,7 +3673,7 @@
         <v>1.8585</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>1.1752</v>
       </c>
       <c r="D71" t="n">
         <v>0.3294</v>
@@ -3719,7 +3719,7 @@
         <v>1.7804</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>1.1259</v>
       </c>
       <c r="D72" t="n">
         <v>0.2979</v>
@@ -3765,7 +3765,7 @@
         <v>1.7451</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>1.1035</v>
       </c>
       <c r="D73" t="n">
         <v>0.2836</v>
@@ -3811,7 +3811,7 @@
         <v>1.7039</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>1.0775</v>
       </c>
       <c r="D74" t="n">
         <v>0.267</v>
@@ -3857,7 +3857,7 @@
         <v>1.6611</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>1.0504</v>
       </c>
       <c r="D75" t="n">
         <v>0.2497</v>
@@ -3903,7 +3903,7 @@
         <v>1.6107</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>1.0185</v>
       </c>
       <c r="D76" t="n">
         <v>0.2293</v>
@@ -3949,7 +3949,7 @@
         <v>1.5586</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>0.9856</v>
       </c>
       <c r="D77" t="n">
         <v>0.2083</v>
@@ -3995,7 +3995,7 @@
         <v>1.4762</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>0.9335</v>
       </c>
       <c r="D78" t="n">
         <v>0.175</v>
@@ -4041,7 +4041,7 @@
         <v>1.3244</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>0.8375</v>
       </c>
       <c r="D79" t="n">
         <v>0.1137</v>
@@ -4087,7 +4087,7 @@
         <v>1.3168</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>0.8327</v>
       </c>
       <c r="D80" t="n">
         <v>0.1106</v>
@@ -4133,7 +4133,7 @@
         <v>1.2487</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>0.7896</v>
       </c>
       <c r="D81" t="n">
         <v>0.08309999999999999</v>
@@ -4179,7 +4179,7 @@
         <v>1.2249</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>0.7746</v>
       </c>
       <c r="D82" t="n">
         <v>0.0735</v>
@@ -4225,7 +4225,7 @@
         <v>1.218</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>0.7702</v>
       </c>
       <c r="D83" t="n">
         <v>0.0707</v>
@@ -4271,7 +4271,7 @@
         <v>1.1549</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="D84" t="n">
         <v>0.0452</v>
@@ -4317,7 +4317,7 @@
         <v>1.051</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>0.6646</v>
       </c>
       <c r="D85" t="n">
         <v>0.0032</v>
@@ -4363,7 +4363,7 @@
         <v>1.0226</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="D86" t="n">
         <v>-0.0083</v>
@@ -4409,7 +4409,7 @@
         <v>1.0086</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>0.6378</v>
       </c>
       <c r="D87" t="n">
         <v>-0.0139</v>
@@ -4455,7 +4455,7 @@
         <v>1.0031</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>0.6343</v>
       </c>
       <c r="D88" t="n">
         <v>-0.0161</v>
@@ -4501,7 +4501,7 @@
         <v>0.9667</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>0.6113</v>
       </c>
       <c r="D89" t="n">
         <v>-0.0308</v>
@@ -4547,7 +4547,7 @@
         <v>0.9446</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="D90" t="n">
         <v>-0.0398</v>
@@ -4593,7 +4593,7 @@
         <v>0.88</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>0.5565</v>
       </c>
       <c r="D91" t="n">
         <v>-0.0659</v>
@@ -4639,7 +4639,7 @@
         <v>0.8295</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>0.5245</v>
       </c>
       <c r="D92" t="n">
         <v>-0.0863</v>
@@ -4685,7 +4685,7 @@
         <v>0.7867</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>0.4975</v>
       </c>
       <c r="D93" t="n">
         <v>-0.1036</v>
@@ -4731,7 +4731,7 @@
         <v>0.7131</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>0.4509</v>
       </c>
       <c r="D94" t="n">
         <v>-0.1333</v>
@@ -4777,7 +4777,7 @@
         <v>0.6562</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>0.415</v>
       </c>
       <c r="D95" t="n">
         <v>-0.1563</v>
@@ -4823,7 +4823,7 @@
         <v>0.6088</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>0.385</v>
       </c>
       <c r="D96" t="n">
         <v>-0.1754</v>
@@ -4869,7 +4869,7 @@
         <v>0.5867</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>0.371</v>
       </c>
       <c r="D97" t="n">
         <v>-0.1843</v>
@@ -4915,7 +4915,7 @@
         <v>0.5695</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>0.3601</v>
       </c>
       <c r="D98" t="n">
         <v>-0.1913</v>
@@ -4961,7 +4961,7 @@
         <v>0.435</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>0.2751</v>
       </c>
       <c r="D99" t="n">
         <v>-0.2456</v>
@@ -5007,7 +5007,7 @@
         <v>0.3989</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>0.2522</v>
       </c>
       <c r="D100" t="n">
         <v>-0.2602</v>
@@ -5053,7 +5053,7 @@
         <v>0.3972</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>0.2512</v>
       </c>
       <c r="D101" t="n">
         <v>-0.2609</v>
@@ -5099,7 +5099,7 @@
         <v>0.3967</v>
       </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>0.2509</v>
       </c>
       <c r="D102" t="n">
         <v>-0.2611</v>
@@ -5145,7 +5145,7 @@
         <v>0.3838</v>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>0.2427</v>
       </c>
       <c r="D103" t="n">
         <v>-0.2663</v>
@@ -5191,7 +5191,7 @@
         <v>0.2808</v>
       </c>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>0.1776</v>
       </c>
       <c r="D104" t="n">
         <v>-0.3079</v>
@@ -5237,7 +5237,7 @@
         <v>0.252</v>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>0.1594</v>
       </c>
       <c r="D105" t="n">
         <v>-0.3196</v>
@@ -5283,7 +5283,7 @@
         <v>0.2188</v>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>0.1384</v>
       </c>
       <c r="D106" t="n">
         <v>-0.333</v>
@@ -5329,7 +5329,7 @@
         <v>0.1234</v>
       </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>0.078</v>
       </c>
       <c r="D107" t="n">
         <v>-0.3715</v>
@@ -5375,7 +5375,7 @@
         <v>-0.0711</v>
       </c>
       <c r="C108" t="n">
-        <v>-0</v>
+        <v>-0.045</v>
       </c>
       <c r="D108" t="n">
         <v>-0.4501</v>
@@ -5421,7 +5421,7 @@
         <v>-0.1592</v>
       </c>
       <c r="C109" t="n">
-        <v>-0</v>
+        <v>-0.1007</v>
       </c>
       <c r="D109" t="n">
         <v>-0.4857</v>
@@ -5467,7 +5467,7 @@
         <v>-0.1861</v>
       </c>
       <c r="C110" t="n">
-        <v>-0</v>
+        <v>-0.1177</v>
       </c>
       <c r="D110" t="n">
         <v>-0.4965</v>
@@ -5513,7 +5513,7 @@
         <v>-0.2445</v>
       </c>
       <c r="C111" t="n">
-        <v>-0</v>
+        <v>-0.1546</v>
       </c>
       <c r="D111" t="n">
         <v>-0.5201</v>
@@ -5559,7 +5559,7 @@
         <v>-0.2757</v>
       </c>
       <c r="C112" t="n">
-        <v>-0</v>
+        <v>-0.1743</v>
       </c>
       <c r="D112" t="n">
         <v>-0.5327</v>
@@ -5605,7 +5605,7 @@
         <v>-0.2997</v>
       </c>
       <c r="C113" t="n">
-        <v>-0</v>
+        <v>-0.1895</v>
       </c>
       <c r="D113" t="n">
         <v>-0.5424</v>
@@ -5651,7 +5651,7 @@
         <v>-0.3526</v>
       </c>
       <c r="C114" t="n">
-        <v>-0</v>
+        <v>-0.223</v>
       </c>
       <c r="D114" t="n">
         <v>-0.5638</v>
@@ -5697,7 +5697,7 @@
         <v>-0.4415</v>
       </c>
       <c r="C115" t="n">
-        <v>-0</v>
+        <v>-0.2792</v>
       </c>
       <c r="D115" t="n">
         <v>-0.5997</v>
@@ -5743,7 +5743,7 @@
         <v>-0.4947</v>
       </c>
       <c r="C116" t="n">
-        <v>-0</v>
+        <v>-0.3128</v>
       </c>
       <c r="D116" t="n">
         <v>-0.6212</v>
@@ -5789,7 +5789,7 @@
         <v>-0.5008</v>
       </c>
       <c r="C117" t="n">
-        <v>-0</v>
+        <v>-0.3167</v>
       </c>
       <c r="D117" t="n">
         <v>-0.6237</v>
@@ -5835,7 +5835,7 @@
         <v>-0.5425</v>
       </c>
       <c r="C118" t="n">
-        <v>-0</v>
+        <v>-0.3431</v>
       </c>
       <c r="D118" t="n">
         <v>-0.6405</v>
@@ -5881,7 +5881,7 @@
         <v>-0.575</v>
       </c>
       <c r="C119" t="n">
-        <v>-0</v>
+        <v>-0.3636</v>
       </c>
       <c r="D119" t="n">
         <v>-0.6536</v>
@@ -5927,7 +5927,7 @@
         <v>-0.5879</v>
       </c>
       <c r="C120" t="n">
-        <v>-0</v>
+        <v>-0.3718</v>
       </c>
       <c r="D120" t="n">
         <v>-0.6589</v>
@@ -5973,7 +5973,7 @@
         <v>-0.5989</v>
       </c>
       <c r="C121" t="n">
-        <v>-0</v>
+        <v>-0.3787</v>
       </c>
       <c r="D121" t="n">
         <v>-0.6633</v>
@@ -6019,7 +6019,7 @@
         <v>-0.6107</v>
       </c>
       <c r="C122" t="n">
-        <v>-0</v>
+        <v>-0.3862</v>
       </c>
       <c r="D122" t="n">
         <v>-0.6681</v>
@@ -6065,7 +6065,7 @@
         <v>-0.6414</v>
       </c>
       <c r="C123" t="n">
-        <v>-0</v>
+        <v>-0.4056</v>
       </c>
       <c r="D123" t="n">
         <v>-0.6805</v>
@@ -6111,7 +6111,7 @@
         <v>-0.7158</v>
       </c>
       <c r="C124" t="n">
-        <v>-0</v>
+        <v>-0.4526</v>
       </c>
       <c r="D124" t="n">
         <v>-0.7105</v>
@@ -6157,7 +6157,7 @@
         <v>-0.7298</v>
       </c>
       <c r="C125" t="n">
-        <v>-0</v>
+        <v>-0.4615</v>
       </c>
       <c r="D125" t="n">
         <v>-0.7161999999999999</v>
@@ -6203,7 +6203,7 @@
         <v>-0.7359</v>
       </c>
       <c r="C126" t="n">
-        <v>-0</v>
+        <v>-0.4654</v>
       </c>
       <c r="D126" t="n">
         <v>-0.7186</v>
@@ -6249,7 +6249,7 @@
         <v>-0.8148</v>
       </c>
       <c r="C127" t="n">
-        <v>-0</v>
+        <v>-0.5152</v>
       </c>
       <c r="D127" t="n">
         <v>-0.7504999999999999</v>
@@ -6295,7 +6295,7 @@
         <v>-0.8165</v>
       </c>
       <c r="C128" t="n">
-        <v>-0</v>
+        <v>-0.5163</v>
       </c>
       <c r="D128" t="n">
         <v>-0.7512</v>
@@ -6341,7 +6341,7 @@
         <v>-0.8442</v>
       </c>
       <c r="C129" t="n">
-        <v>-0</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="D129" t="n">
         <v>-0.7624</v>
@@ -6387,7 +6387,7 @@
         <v>-0.8501</v>
       </c>
       <c r="C130" t="n">
-        <v>-0</v>
+        <v>-0.5376</v>
       </c>
       <c r="D130" t="n">
         <v>-0.7648</v>
@@ -6433,7 +6433,7 @@
         <v>-0.8666</v>
       </c>
       <c r="C131" t="n">
-        <v>-0</v>
+        <v>-0.548</v>
       </c>
       <c r="D131" t="n">
         <v>-0.7714</v>
@@ -6479,7 +6479,7 @@
         <v>-0.9058</v>
       </c>
       <c r="C132" t="n">
-        <v>-0</v>
+        <v>-0.5728</v>
       </c>
       <c r="D132" t="n">
         <v>-0.7873</v>
@@ -6525,7 +6525,7 @@
         <v>-1.0327</v>
       </c>
       <c r="C133" t="n">
-        <v>-0</v>
+        <v>-0.653</v>
       </c>
       <c r="D133" t="n">
         <v>-0.8386</v>
@@ -6571,7 +6571,7 @@
         <v>-1.0425</v>
       </c>
       <c r="C134" t="n">
-        <v>-0</v>
+        <v>-0.6592</v>
       </c>
       <c r="D134" t="n">
         <v>-0.8425</v>
@@ -6617,7 +6617,7 @@
         <v>-1.271</v>
       </c>
       <c r="C135" t="n">
-        <v>-0</v>
+        <v>-0.8037</v>
       </c>
       <c r="D135" t="n">
         <v>-0.9348</v>
@@ -6663,7 +6663,7 @@
         <v>-1.5286</v>
       </c>
       <c r="C136" t="n">
-        <v>-0</v>
+        <v>-0.9666</v>
       </c>
       <c r="D136" t="n">
         <v>-1.0389</v>
@@ -6709,7 +6709,7 @@
         <v>-1.5854</v>
       </c>
       <c r="C137" t="n">
-        <v>-0</v>
+        <v>-1.0025</v>
       </c>
       <c r="D137" t="n">
         <v>-1.0618</v>
@@ -6755,7 +6755,7 @@
         <v>-1.7034</v>
       </c>
       <c r="C138" t="n">
-        <v>-0</v>
+        <v>-1.0772</v>
       </c>
       <c r="D138" t="n">
         <v>-1.1095</v>
@@ -6801,7 +6801,7 @@
         <v>-1.7135</v>
       </c>
       <c r="C139" t="n">
-        <v>-0</v>
+        <v>-1.0836</v>
       </c>
       <c r="D139" t="n">
         <v>-1.1136</v>
@@ -6847,7 +6847,7 @@
         <v>-1.7187</v>
       </c>
       <c r="C140" t="n">
-        <v>-0</v>
+        <v>-1.0868</v>
       </c>
       <c r="D140" t="n">
         <v>-1.1157</v>
@@ -6893,7 +6893,7 @@
         <v>-1.8985</v>
       </c>
       <c r="C141" t="n">
-        <v>-0</v>
+        <v>-1.2005</v>
       </c>
       <c r="D141" t="n">
         <v>-1.1883</v>
@@ -6939,7 +6939,7 @@
         <v>-1.979</v>
       </c>
       <c r="C142" t="n">
-        <v>-0</v>
+        <v>-1.2514</v>
       </c>
       <c r="D142" t="n">
         <v>-1.2208</v>
@@ -6985,7 +6985,7 @@
         <v>-1.9793</v>
       </c>
       <c r="C143" t="n">
-        <v>-0</v>
+        <v>-1.2516</v>
       </c>
       <c r="D143" t="n">
         <v>-1.221</v>
@@ -7031,7 +7031,7 @@
         <v>-2.0933</v>
       </c>
       <c r="C144" t="n">
-        <v>-0</v>
+        <v>-1.3237</v>
       </c>
       <c r="D144" t="n">
         <v>-1.267</v>
@@ -7077,7 +7077,7 @@
         <v>-2.1292</v>
       </c>
       <c r="C145" t="n">
-        <v>-0</v>
+        <v>-1.3464</v>
       </c>
       <c r="D145" t="n">
         <v>-1.2815</v>
@@ -7123,7 +7123,7 @@
         <v>-2.2754</v>
       </c>
       <c r="C146" t="n">
-        <v>-0</v>
+        <v>-1.4389</v>
       </c>
       <c r="D146" t="n">
         <v>-1.3406</v>
@@ -7169,7 +7169,7 @@
         <v>-2.3715</v>
       </c>
       <c r="C147" t="n">
-        <v>-0</v>
+        <v>-1.4996</v>
       </c>
       <c r="D147" t="n">
         <v>-1.3794</v>
@@ -7215,7 +7215,7 @@
         <v>-2.5575</v>
       </c>
       <c r="C148" t="n">
-        <v>-0</v>
+        <v>-1.6173</v>
       </c>
       <c r="D148" t="n">
         <v>-1.4545</v>
@@ -7261,7 +7261,7 @@
         <v>-2.6382</v>
       </c>
       <c r="C149" t="n">
-        <v>-0</v>
+        <v>-1.6683</v>
       </c>
       <c r="D149" t="n">
         <v>-1.4871</v>
@@ -7307,7 +7307,7 @@
         <v>-2.6454</v>
       </c>
       <c r="C150" t="n">
-        <v>-0</v>
+        <v>-1.6729</v>
       </c>
       <c r="D150" t="n">
         <v>-1.49</v>
@@ -7353,7 +7353,7 @@
         <v>-2.6823</v>
       </c>
       <c r="C151" t="n">
-        <v>-0</v>
+        <v>-1.6962</v>
       </c>
       <c r="D151" t="n">
         <v>-1.505</v>
@@ -7399,7 +7399,7 @@
         <v>-2.8384</v>
       </c>
       <c r="C152" t="n">
-        <v>-0</v>
+        <v>-1.7949</v>
       </c>
       <c r="D152" t="n">
         <v>-1.568</v>
@@ -7445,7 +7445,7 @@
         <v>-2.8407</v>
       </c>
       <c r="C153" t="n">
-        <v>-0</v>
+        <v>-1.7964</v>
       </c>
       <c r="D153" t="n">
         <v>-1.5689</v>
@@ -7491,7 +7491,7 @@
         <v>-2.8914</v>
       </c>
       <c r="C154" t="n">
-        <v>-0</v>
+        <v>-1.8284</v>
       </c>
       <c r="D154" t="n">
         <v>-1.5894</v>
@@ -7537,7 +7537,7 @@
         <v>-2.8985</v>
       </c>
       <c r="C155" t="n">
-        <v>-0</v>
+        <v>-1.8329</v>
       </c>
       <c r="D155" t="n">
         <v>-1.5923</v>
@@ -7583,7 +7583,7 @@
         <v>-2.9724</v>
       </c>
       <c r="C156" t="n">
-        <v>-0</v>
+        <v>-1.8796</v>
       </c>
       <c r="D156" t="n">
         <v>-1.6221</v>
@@ -7629,7 +7629,7 @@
         <v>-2.9842</v>
       </c>
       <c r="C157" t="n">
-        <v>-0</v>
+        <v>-1.8871</v>
       </c>
       <c r="D157" t="n">
         <v>-1.6269</v>
@@ -7675,7 +7675,7 @@
         <v>-3.5891</v>
       </c>
       <c r="C158" t="n">
-        <v>-0</v>
+        <v>-2.2696</v>
       </c>
       <c r="D158" t="n">
         <v>-1.8713</v>
@@ -7721,7 +7721,7 @@
         <v>-3.6832</v>
       </c>
       <c r="C159" t="n">
-        <v>-0</v>
+        <v>-2.3291</v>
       </c>
       <c r="D159" t="n">
         <v>-1.9093</v>
@@ -7767,7 +7767,7 @@
         <v>-4.6659</v>
       </c>
       <c r="C160" t="n">
-        <v>-0</v>
+        <v>-2.9505</v>
       </c>
       <c r="D160" t="n">
         <v>-2.3063</v>
@@ -7813,7 +7813,7 @@
         <v>-6.0037</v>
       </c>
       <c r="C161" t="n">
-        <v>-0</v>
+        <v>-3.7965</v>
       </c>
       <c r="D161" t="n">
         <v>-2.8467</v>

--- a/database/event/7440/event_7440_evp_summary.xlsx
+++ b/database/event/7440/event_7440_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>7.0838</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1041</v>
+        <v>4.019</v>
       </c>
       <c r="E2" t="n">
         <v>11.2022</v>
@@ -548,7 +548,7 @@
         <v>5.3823</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0171</v>
+        <v>2.947</v>
       </c>
       <c r="E3" t="n">
         <v>8.5114</v>
@@ -594,7 +594,7 @@
         <v>4.9667</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7516</v>
+        <v>2.6852</v>
       </c>
       <c r="E4" t="n">
         <v>7.8542</v>
@@ -640,7 +640,7 @@
         <v>4.9141</v>
       </c>
       <c r="D5" t="n">
-        <v>2.718</v>
+        <v>2.6521</v>
       </c>
       <c r="E5" t="n">
         <v>7.7711</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.3869</v>
+        <v>6.3064</v>
       </c>
       <c r="C6" t="n">
-        <v>4.0388</v>
+        <v>3.9879</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1588</v>
+        <v>2.0686</v>
       </c>
       <c r="E6" t="n">
-        <v>6.3869</v>
+        <v>6.3064</v>
       </c>
       <c r="F6" t="n">
-        <v>5.8168</v>
+        <v>5.7363</v>
       </c>
       <c r="G6" t="n">
         <v>0.5701000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>6.8177</v>
+        <v>6.6915</v>
       </c>
       <c r="I6" t="n">
         <v>6.9778</v>
@@ -732,7 +732,7 @@
         <v>3.9838</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1236</v>
+        <v>2.0659</v>
       </c>
       <c r="E7" t="n">
         <v>6.2998</v>
@@ -778,7 +778,7 @@
         <v>3.9433</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0978</v>
+        <v>2.0404</v>
       </c>
       <c r="E8" t="n">
         <v>6.2358</v>
@@ -824,7 +824,7 @@
         <v>3.8862</v>
       </c>
       <c r="D9" t="n">
-        <v>2.0613</v>
+        <v>2.0045</v>
       </c>
       <c r="E9" t="n">
         <v>6.1456</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.018</v>
+        <v>5.9841</v>
       </c>
       <c r="C10" t="n">
-        <v>3.8056</v>
+        <v>3.7841</v>
       </c>
       <c r="D10" t="n">
-        <v>2.0098</v>
+        <v>1.9402</v>
       </c>
       <c r="E10" t="n">
-        <v>6.018</v>
+        <v>5.9841</v>
       </c>
       <c r="F10" t="n">
-        <v>6.018</v>
+        <v>5.9841</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>7.1331</v>
+        <v>7.08</v>
       </c>
       <c r="I10" t="n">
         <v>7.1997</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.0002</v>
+        <v>5.935</v>
       </c>
       <c r="C11" t="n">
-        <v>3.7943</v>
+        <v>3.7531</v>
       </c>
       <c r="D11" t="n">
-        <v>2.0026</v>
+        <v>1.9206</v>
       </c>
       <c r="E11" t="n">
-        <v>6.0002</v>
+        <v>5.935</v>
       </c>
       <c r="F11" t="n">
-        <v>4.9914</v>
+        <v>4.9262</v>
       </c>
       <c r="G11" t="n">
         <v>1.0088</v>
       </c>
       <c r="H11" t="n">
-        <v>5.5234</v>
+        <v>5.4212</v>
       </c>
       <c r="I11" t="n">
         <v>5.6532</v>
@@ -962,7 +962,7 @@
         <v>3.4897</v>
       </c>
       <c r="D12" t="n">
-        <v>1.808</v>
+        <v>1.7547</v>
       </c>
       <c r="E12" t="n">
         <v>5.5185</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.4428</v>
+        <v>5.3878</v>
       </c>
       <c r="C13" t="n">
-        <v>3.4418</v>
+        <v>3.407</v>
       </c>
       <c r="D13" t="n">
-        <v>1.7774</v>
+        <v>1.7026</v>
       </c>
       <c r="E13" t="n">
-        <v>5.4428</v>
+        <v>5.3878</v>
       </c>
       <c r="F13" t="n">
-        <v>5.1789</v>
+        <v>5.1239</v>
       </c>
       <c r="G13" t="n">
         <v>0.2639</v>
       </c>
       <c r="H13" t="n">
-        <v>5.8175</v>
+        <v>5.7312</v>
       </c>
       <c r="I13" t="n">
         <v>5.9266</v>
@@ -1054,7 +1054,7 @@
         <v>3.3991</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7501</v>
+        <v>1.6976</v>
       </c>
       <c r="E14" t="n">
         <v>5.3753</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>DemQQ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.3027</v>
+        <v>5.2667</v>
       </c>
       <c r="C15" t="n">
-        <v>3.3532</v>
+        <v>3.3305</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7208</v>
+        <v>1.6543</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3027</v>
+        <v>5.2667</v>
       </c>
       <c r="F15" t="n">
-        <v>5.3027</v>
+        <v>5.2667</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>6.0115</v>
+        <v>5.9552</v>
       </c>
       <c r="I15" t="n">
-        <v>6.0958</v>
+        <v>6.0053</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>6.0958</v>
+        <v>6.0053</v>
       </c>
       <c r="N15" t="n">
-        <v>372</v>
+        <v>385</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DemQQ</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.281</v>
+        <v>5.2599</v>
       </c>
       <c r="C16" t="n">
-        <v>3.3395</v>
+        <v>3.3262</v>
       </c>
       <c r="D16" t="n">
-        <v>1.712</v>
+        <v>1.6516</v>
       </c>
       <c r="E16" t="n">
-        <v>5.281</v>
+        <v>5.2599</v>
       </c>
       <c r="F16" t="n">
-        <v>5.281</v>
+        <v>5.2599</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>5.9775</v>
+        <v>5.9445</v>
       </c>
       <c r="I16" t="n">
-        <v>6.0053</v>
+        <v>6.0958</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>6.0053</v>
+        <v>6.0958</v>
       </c>
       <c r="N16" t="n">
-        <v>385</v>
+        <v>372</v>
       </c>
     </row>
     <row r="17">
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.9833</v>
+        <v>4.9702</v>
       </c>
       <c r="C17" t="n">
-        <v>3.1512</v>
+        <v>3.143</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5918</v>
+        <v>1.5362</v>
       </c>
       <c r="E17" t="n">
-        <v>4.9833</v>
+        <v>4.9702</v>
       </c>
       <c r="F17" t="n">
-        <v>4.9833</v>
+        <v>4.9702</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>5.5107</v>
+        <v>5.4902</v>
       </c>
       <c r="I17" t="n">
         <v>5.5364</v>
@@ -1238,7 +1238,7 @@
         <v>3.1166</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5696</v>
+        <v>1.5196</v>
       </c>
       <c r="E18" t="n">
         <v>4.9285</v>
@@ -1284,7 +1284,7 @@
         <v>3.1156</v>
       </c>
       <c r="D19" t="n">
-        <v>1.569</v>
+        <v>1.519</v>
       </c>
       <c r="E19" t="n">
         <v>4.927</v>
@@ -1330,7 +1330,7 @@
         <v>3.0826</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5479</v>
+        <v>1.4982</v>
       </c>
       <c r="E20" t="n">
         <v>4.8747</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.8473</v>
+        <v>4.8347</v>
       </c>
       <c r="C21" t="n">
-        <v>3.0652</v>
+        <v>3.0573</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5368</v>
+        <v>1.4822</v>
       </c>
       <c r="E21" t="n">
-        <v>4.8473</v>
+        <v>4.8347</v>
       </c>
       <c r="F21" t="n">
-        <v>4.8473</v>
+        <v>4.8347</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>5.2975</v>
+        <v>5.2777</v>
       </c>
       <c r="I21" t="n">
         <v>5.3221</v>
@@ -1412,93 +1412,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.8196</v>
+        <v>4.8182</v>
       </c>
       <c r="C22" t="n">
-        <v>3.0477</v>
+        <v>3.0468</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5256</v>
+        <v>1.4757</v>
       </c>
       <c r="E22" t="n">
-        <v>4.8196</v>
+        <v>4.8182</v>
       </c>
       <c r="F22" t="n">
-        <v>4.8196</v>
+        <v>4.8182</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>5.254</v>
+        <v>5.2519</v>
       </c>
       <c r="I22" t="n">
-        <v>5.2785</v>
+        <v>5.2519</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>299</v>
+        <v>207</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>5.2785</v>
+        <v>5.2519</v>
       </c>
       <c r="N22" t="n">
-        <v>299</v>
+        <v>207</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.8182</v>
+        <v>4.8071</v>
       </c>
       <c r="C23" t="n">
-        <v>3.0468</v>
+        <v>3.0398</v>
       </c>
       <c r="D23" t="n">
-        <v>1.5251</v>
+        <v>1.4712</v>
       </c>
       <c r="E23" t="n">
-        <v>4.8182</v>
+        <v>4.8071</v>
       </c>
       <c r="F23" t="n">
-        <v>4.8182</v>
+        <v>4.8071</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>5.2519</v>
+        <v>5.2344</v>
       </c>
       <c r="I23" t="n">
-        <v>5.2519</v>
+        <v>5.2785</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>207</v>
+        <v>299</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>5.2519</v>
+        <v>5.2785</v>
       </c>
       <c r="N23" t="n">
-        <v>207</v>
+        <v>299</v>
       </c>
     </row>
     <row r="24">
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.6388</v>
+        <v>4.627</v>
       </c>
       <c r="C24" t="n">
-        <v>2.9334</v>
+        <v>2.9259</v>
       </c>
       <c r="D24" t="n">
-        <v>1.4526</v>
+        <v>1.3995</v>
       </c>
       <c r="E24" t="n">
-        <v>4.6388</v>
+        <v>4.627</v>
       </c>
       <c r="F24" t="n">
-        <v>4.6388</v>
+        <v>4.627</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>4.9706</v>
+        <v>4.952</v>
       </c>
       <c r="I24" t="n">
         <v>4.9937</v>
@@ -1560,7 +1560,7 @@
         <v>2.8751</v>
       </c>
       <c r="D25" t="n">
-        <v>1.4154</v>
+        <v>1.3675</v>
       </c>
       <c r="E25" t="n">
         <v>4.5466</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.5291</v>
+        <v>4.465</v>
       </c>
       <c r="C26" t="n">
-        <v>2.864</v>
+        <v>2.8235</v>
       </c>
       <c r="D26" t="n">
-        <v>1.4083</v>
+        <v>1.3349</v>
       </c>
       <c r="E26" t="n">
-        <v>4.5291</v>
+        <v>4.465</v>
       </c>
       <c r="F26" t="n">
-        <v>4.9344</v>
+        <v>4.8703</v>
       </c>
       <c r="G26" t="n">
         <v>-0.4053</v>
       </c>
       <c r="H26" t="n">
-        <v>5.4341</v>
+        <v>5.3335</v>
       </c>
       <c r="I26" t="n">
         <v>5.5617</v>
@@ -1642,139 +1642,139 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>sl3nd</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.4431</v>
+        <v>4.4324</v>
       </c>
       <c r="C27" t="n">
-        <v>2.8096</v>
+        <v>2.8029</v>
       </c>
       <c r="D27" t="n">
-        <v>1.3736</v>
+        <v>1.322</v>
       </c>
       <c r="E27" t="n">
-        <v>4.4431</v>
+        <v>4.4324</v>
       </c>
       <c r="F27" t="n">
-        <v>5.0062</v>
+        <v>4.4324</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.5631</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>5.5467</v>
+        <v>4.647</v>
       </c>
       <c r="I27" t="n">
-        <v>5.677</v>
+        <v>4.647</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.5631</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>408</v>
+        <v>226</v>
       </c>
       <c r="L27" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>5.113899999999999</v>
+        <v>4.647</v>
       </c>
       <c r="N27" t="n">
-        <v>462</v>
+        <v>226</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sl3nd</t>
+          <t>slaxz-</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4.4324</v>
+        <v>4.4058</v>
       </c>
       <c r="C28" t="n">
-        <v>2.8029</v>
+        <v>2.7861</v>
       </c>
       <c r="D28" t="n">
-        <v>1.3692</v>
+        <v>1.3114</v>
       </c>
       <c r="E28" t="n">
-        <v>4.4324</v>
+        <v>4.4058</v>
       </c>
       <c r="F28" t="n">
-        <v>4.4324</v>
+        <v>4.4058</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>4.647</v>
+        <v>4.6053</v>
       </c>
       <c r="I28" t="n">
-        <v>4.647</v>
+        <v>4.6831</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>226</v>
+        <v>394</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.647</v>
+        <v>4.6831</v>
       </c>
       <c r="N28" t="n">
-        <v>226</v>
+        <v>394</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>slaxz-</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.4279</v>
+        <v>4.3776</v>
       </c>
       <c r="C29" t="n">
-        <v>2.8</v>
+        <v>2.7682</v>
       </c>
       <c r="D29" t="n">
-        <v>1.3674</v>
+        <v>1.3001</v>
       </c>
       <c r="E29" t="n">
-        <v>4.4279</v>
+        <v>4.3776</v>
       </c>
       <c r="F29" t="n">
-        <v>4.4279</v>
+        <v>4.9407</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.5631</v>
       </c>
       <c r="H29" t="n">
-        <v>4.6399</v>
+        <v>5.444</v>
       </c>
       <c r="I29" t="n">
-        <v>4.6831</v>
+        <v>5.677</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.5631</v>
       </c>
       <c r="K29" t="n">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M29" t="n">
-        <v>4.6831</v>
+        <v>5.113899999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>394</v>
+        <v>462</v>
       </c>
     </row>
     <row r="30">
@@ -1790,7 +1790,7 @@
         <v>2.7615</v>
       </c>
       <c r="D30" t="n">
-        <v>1.3428</v>
+        <v>1.2959</v>
       </c>
       <c r="E30" t="n">
         <v>4.367</v>
@@ -1836,7 +1836,7 @@
         <v>2.6413</v>
       </c>
       <c r="D31" t="n">
-        <v>1.266</v>
+        <v>1.2202</v>
       </c>
       <c r="E31" t="n">
         <v>4.1769</v>
@@ -1882,7 +1882,7 @@
         <v>2.3464</v>
       </c>
       <c r="D32" t="n">
-        <v>1.0776</v>
+        <v>1.0344</v>
       </c>
       <c r="E32" t="n">
         <v>3.7105</v>
@@ -1928,7 +1928,7 @@
         <v>2.3311</v>
       </c>
       <c r="D33" t="n">
-        <v>1.0678</v>
+        <v>1.0247</v>
       </c>
       <c r="E33" t="n">
         <v>3.6863</v>
@@ -1964,139 +1964,139 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.602</v>
+        <v>3.5733</v>
       </c>
       <c r="C34" t="n">
-        <v>2.2778</v>
+        <v>2.2596</v>
       </c>
       <c r="D34" t="n">
-        <v>1.0338</v>
+        <v>0.9797</v>
       </c>
       <c r="E34" t="n">
-        <v>3.602</v>
+        <v>3.5733</v>
       </c>
       <c r="F34" t="n">
-        <v>4.3049</v>
+        <v>3.5733</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.7029</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>4.447</v>
+        <v>3.5733</v>
       </c>
       <c r="I34" t="n">
-        <v>4.5515</v>
+        <v>3.5733</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.7029</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>408</v>
+        <v>237</v>
       </c>
       <c r="L34" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.8486</v>
+        <v>3.5733</v>
       </c>
       <c r="N34" t="n">
-        <v>462</v>
+        <v>237</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>hades</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.5733</v>
+        <v>3.564</v>
       </c>
       <c r="C35" t="n">
-        <v>2.2596</v>
+        <v>2.2537</v>
       </c>
       <c r="D35" t="n">
-        <v>1.0222</v>
+        <v>0.976</v>
       </c>
       <c r="E35" t="n">
-        <v>3.5733</v>
+        <v>3.564</v>
       </c>
       <c r="F35" t="n">
-        <v>3.5733</v>
+        <v>3.564</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>3.5733</v>
+        <v>3.564</v>
       </c>
       <c r="I35" t="n">
-        <v>3.5733</v>
+        <v>3.564</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5733</v>
+        <v>3.564</v>
       </c>
       <c r="N35" t="n">
-        <v>237</v>
+        <v>216</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>hades</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3.564</v>
+        <v>3.5495</v>
       </c>
       <c r="C36" t="n">
-        <v>2.2537</v>
+        <v>2.2446</v>
       </c>
       <c r="D36" t="n">
-        <v>1.0184</v>
+        <v>0.9702</v>
       </c>
       <c r="E36" t="n">
-        <v>3.564</v>
+        <v>3.5495</v>
       </c>
       <c r="F36" t="n">
-        <v>3.564</v>
+        <v>4.2524</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.7029</v>
       </c>
       <c r="H36" t="n">
-        <v>3.564</v>
+        <v>4.3647</v>
       </c>
       <c r="I36" t="n">
-        <v>3.564</v>
+        <v>4.5515</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.7029</v>
       </c>
       <c r="K36" t="n">
-        <v>216</v>
+        <v>408</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M36" t="n">
-        <v>3.564</v>
+        <v>3.8486</v>
       </c>
       <c r="N36" t="n">
-        <v>216</v>
+        <v>462</v>
       </c>
     </row>
     <row r="37">
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.416</v>
+        <v>3.3771</v>
       </c>
       <c r="C37" t="n">
-        <v>2.1601</v>
+        <v>2.1355</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9586</v>
+        <v>0.9015</v>
       </c>
       <c r="E37" t="n">
-        <v>3.416</v>
+        <v>3.3771</v>
       </c>
       <c r="F37" t="n">
-        <v>4.0961</v>
+        <v>4.0572</v>
       </c>
       <c r="G37" t="n">
         <v>-0.6801</v>
       </c>
       <c r="H37" t="n">
-        <v>4.1197</v>
+        <v>4.0586</v>
       </c>
       <c r="I37" t="n">
         <v>4.1969</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3.3579</v>
+        <v>3.3329</v>
       </c>
       <c r="C38" t="n">
-        <v>2.1234</v>
+        <v>2.1076</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9352</v>
+        <v>0.8839</v>
       </c>
       <c r="E38" t="n">
-        <v>3.3579</v>
+        <v>3.3329</v>
       </c>
       <c r="F38" t="n">
-        <v>3.3579</v>
+        <v>3.3329</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>3.3579</v>
+        <v>3.3329</v>
       </c>
       <c r="I38" t="n">
         <v>3.3892</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.3207</v>
+        <v>3.277</v>
       </c>
       <c r="C39" t="n">
-        <v>2.0999</v>
+        <v>2.0723</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9201</v>
+        <v>0.8616</v>
       </c>
       <c r="E39" t="n">
-        <v>3.3207</v>
+        <v>3.277</v>
       </c>
       <c r="F39" t="n">
-        <v>2.9435</v>
+        <v>2.8998</v>
       </c>
       <c r="G39" t="n">
         <v>0.3772</v>
       </c>
       <c r="H39" t="n">
-        <v>2.9435</v>
+        <v>2.8998</v>
       </c>
       <c r="I39" t="n">
         <v>2.9987</v>
@@ -2250,7 +2250,7 @@
         <v>2.0275</v>
       </c>
       <c r="D40" t="n">
-        <v>0.8739</v>
+        <v>0.8335</v>
       </c>
       <c r="E40" t="n">
         <v>3.2063</v>
@@ -2296,7 +2296,7 @@
         <v>1.978</v>
       </c>
       <c r="D41" t="n">
-        <v>0.8423</v>
+        <v>0.8023</v>
       </c>
       <c r="E41" t="n">
         <v>3.128</v>
@@ -2332,93 +2332,93 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>smooya</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.0688</v>
+        <v>3.0037</v>
       </c>
       <c r="C42" t="n">
-        <v>1.9406</v>
+        <v>1.8994</v>
       </c>
       <c r="D42" t="n">
-        <v>0.8184</v>
+        <v>0.7528</v>
       </c>
       <c r="E42" t="n">
-        <v>3.0688</v>
+        <v>3.0037</v>
       </c>
       <c r="F42" t="n">
-        <v>3.8158</v>
+        <v>3.0037</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.747</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>3.8158</v>
+        <v>3.0037</v>
       </c>
       <c r="I42" t="n">
-        <v>3.9054</v>
+        <v>3.0037</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.747</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>353</v>
+        <v>225</v>
       </c>
       <c r="L42" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.1584</v>
+        <v>3.0037</v>
       </c>
       <c r="N42" t="n">
-        <v>391</v>
+        <v>225</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>smooya</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.0037</v>
+        <v>2.9981</v>
       </c>
       <c r="C43" t="n">
-        <v>1.8994</v>
+        <v>1.8959</v>
       </c>
       <c r="D43" t="n">
-        <v>0.7921</v>
+        <v>0.7504999999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>3.0037</v>
+        <v>2.9981</v>
       </c>
       <c r="F43" t="n">
-        <v>3.0037</v>
+        <v>3.7451</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>-0.747</v>
       </c>
       <c r="H43" t="n">
-        <v>3.0037</v>
+        <v>3.7451</v>
       </c>
       <c r="I43" t="n">
-        <v>3.0037</v>
+        <v>3.9054</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>-0.747</v>
       </c>
       <c r="K43" t="n">
-        <v>225</v>
+        <v>353</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M43" t="n">
-        <v>3.0037</v>
+        <v>3.1584</v>
       </c>
       <c r="N43" t="n">
-        <v>225</v>
+        <v>391</v>
       </c>
     </row>
     <row r="44">
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.9921</v>
+        <v>2.9699</v>
       </c>
       <c r="C44" t="n">
-        <v>1.8921</v>
+        <v>1.8781</v>
       </c>
       <c r="D44" t="n">
-        <v>0.7874</v>
+        <v>0.7393</v>
       </c>
       <c r="E44" t="n">
-        <v>2.9921</v>
+        <v>2.9699</v>
       </c>
       <c r="F44" t="n">
-        <v>2.9921</v>
+        <v>2.9699</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>2.9921</v>
+        <v>2.9699</v>
       </c>
       <c r="I44" t="n">
         <v>3.0201</v>
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.9626</v>
+        <v>2.917</v>
       </c>
       <c r="C45" t="n">
-        <v>1.8734</v>
+        <v>1.8446</v>
       </c>
       <c r="D45" t="n">
-        <v>0.7755</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>2.9626</v>
+        <v>2.917</v>
       </c>
       <c r="F45" t="n">
-        <v>3.0755</v>
+        <v>3.0299</v>
       </c>
       <c r="G45" t="n">
         <v>-0.1129</v>
       </c>
       <c r="H45" t="n">
-        <v>3.0755</v>
+        <v>3.0299</v>
       </c>
       <c r="I45" t="n">
         <v>3.1332</v>
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.9363</v>
+        <v>2.8786</v>
       </c>
       <c r="C46" t="n">
-        <v>1.8568</v>
+        <v>1.8203</v>
       </c>
       <c r="D46" t="n">
-        <v>0.7648</v>
+        <v>0.7029</v>
       </c>
       <c r="E46" t="n">
-        <v>2.9363</v>
+        <v>2.8786</v>
       </c>
       <c r="F46" t="n">
-        <v>3.1127</v>
+        <v>3.055</v>
       </c>
       <c r="G46" t="n">
         <v>-0.1764</v>
       </c>
       <c r="H46" t="n">
-        <v>3.1127</v>
+        <v>3.055</v>
       </c>
       <c r="I46" t="n">
         <v>3.1858</v>
@@ -2572,7 +2572,7 @@
         <v>1.8192</v>
       </c>
       <c r="D47" t="n">
-        <v>0.7408</v>
+        <v>0.7022</v>
       </c>
       <c r="E47" t="n">
         <v>2.8768</v>
@@ -2618,7 +2618,7 @@
         <v>1.8036</v>
       </c>
       <c r="D48" t="n">
-        <v>0.7308</v>
+        <v>0.6924</v>
       </c>
       <c r="E48" t="n">
         <v>2.8521</v>
@@ -2664,7 +2664,7 @@
         <v>1.6733</v>
       </c>
       <c r="D49" t="n">
-        <v>0.6476</v>
+        <v>0.6103</v>
       </c>
       <c r="E49" t="n">
         <v>2.6461</v>
@@ -2710,7 +2710,7 @@
         <v>1.668</v>
       </c>
       <c r="D50" t="n">
-        <v>0.6443</v>
+        <v>0.607</v>
       </c>
       <c r="E50" t="n">
         <v>2.6378</v>
@@ -2756,7 +2756,7 @@
         <v>1.6581</v>
       </c>
       <c r="D51" t="n">
-        <v>0.6379</v>
+        <v>0.6007</v>
       </c>
       <c r="E51" t="n">
         <v>2.6221</v>
@@ -2802,7 +2802,7 @@
         <v>1.6488</v>
       </c>
       <c r="D52" t="n">
-        <v>0.6319</v>
+        <v>0.5948</v>
       </c>
       <c r="E52" t="n">
         <v>2.6073</v>
@@ -2848,7 +2848,7 @@
         <v>1.6357</v>
       </c>
       <c r="D53" t="n">
-        <v>0.6236</v>
+        <v>0.5866</v>
       </c>
       <c r="E53" t="n">
         <v>2.5867</v>
@@ -2894,7 +2894,7 @@
         <v>1.5745</v>
       </c>
       <c r="D54" t="n">
-        <v>0.5845</v>
+        <v>0.548</v>
       </c>
       <c r="E54" t="n">
         <v>2.4898</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.3755</v>
+        <v>2.313</v>
       </c>
       <c r="C55" t="n">
-        <v>1.5022</v>
+        <v>1.4627</v>
       </c>
       <c r="D55" t="n">
-        <v>0.5383</v>
+        <v>0.4776</v>
       </c>
       <c r="E55" t="n">
-        <v>2.3755</v>
+        <v>2.313</v>
       </c>
       <c r="F55" t="n">
-        <v>3.3755</v>
+        <v>3.313</v>
       </c>
       <c r="G55" t="n">
         <v>-1</v>
       </c>
       <c r="H55" t="n">
-        <v>3.3755</v>
+        <v>3.313</v>
       </c>
       <c r="I55" t="n">
         <v>3.4548</v>
@@ -2980,25 +2980,25 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2.2905</v>
+        <v>2.282</v>
       </c>
       <c r="C56" t="n">
-        <v>1.4484</v>
+        <v>1.443</v>
       </c>
       <c r="D56" t="n">
-        <v>0.5039</v>
+        <v>0.4652</v>
       </c>
       <c r="E56" t="n">
-        <v>2.2905</v>
+        <v>2.282</v>
       </c>
       <c r="F56" t="n">
-        <v>2.2905</v>
+        <v>2.282</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>2.2905</v>
+        <v>2.282</v>
       </c>
       <c r="I56" t="n">
         <v>2.3012</v>
@@ -3032,7 +3032,7 @@
         <v>1.4329</v>
       </c>
       <c r="D57" t="n">
-        <v>0.494</v>
+        <v>0.4588</v>
       </c>
       <c r="E57" t="n">
         <v>2.2659</v>
@@ -3072,25 +3072,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2.2233</v>
+        <v>2.215</v>
       </c>
       <c r="C58" t="n">
-        <v>1.4059</v>
+        <v>1.4007</v>
       </c>
       <c r="D58" t="n">
-        <v>0.4768</v>
+        <v>0.4385</v>
       </c>
       <c r="E58" t="n">
-        <v>2.2233</v>
+        <v>2.215</v>
       </c>
       <c r="F58" t="n">
-        <v>2.2233</v>
+        <v>2.215</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>2.2233</v>
+        <v>2.215</v>
       </c>
       <c r="I58" t="n">
         <v>2.2336</v>
@@ -3124,7 +3124,7 @@
         <v>1.3125</v>
       </c>
       <c r="D59" t="n">
-        <v>0.4171</v>
+        <v>0.383</v>
       </c>
       <c r="E59" t="n">
         <v>2.0755</v>
@@ -3170,7 +3170,7 @@
         <v>1.3067</v>
       </c>
       <c r="D60" t="n">
-        <v>0.4134</v>
+        <v>0.3793</v>
       </c>
       <c r="E60" t="n">
         <v>2.0664</v>
@@ -3216,7 +3216,7 @@
         <v>1.295</v>
       </c>
       <c r="D61" t="n">
-        <v>0.4059</v>
+        <v>0.3719</v>
       </c>
       <c r="E61" t="n">
         <v>2.0478</v>
@@ -3256,25 +3256,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2.0259</v>
+        <v>2.0183</v>
       </c>
       <c r="C62" t="n">
-        <v>1.2811</v>
+        <v>1.2763</v>
       </c>
       <c r="D62" t="n">
-        <v>0.3971</v>
+        <v>0.3602</v>
       </c>
       <c r="E62" t="n">
-        <v>2.0259</v>
+        <v>2.0183</v>
       </c>
       <c r="F62" t="n">
-        <v>2.0259</v>
+        <v>2.0183</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>2.0259</v>
+        <v>2.0183</v>
       </c>
       <c r="I62" t="n">
         <v>2.0353</v>
@@ -3308,7 +3308,7 @@
         <v>1.2619</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3848</v>
+        <v>0.3511</v>
       </c>
       <c r="E63" t="n">
         <v>1.9955</v>
@@ -3354,7 +3354,7 @@
         <v>1.2292</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3639</v>
+        <v>0.3305</v>
       </c>
       <c r="E64" t="n">
         <v>1.9438</v>
@@ -3400,7 +3400,7 @@
         <v>1.2186</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3571</v>
+        <v>0.3238</v>
       </c>
       <c r="E65" t="n">
         <v>1.9271</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1.926</v>
+        <v>1.9045</v>
       </c>
       <c r="C66" t="n">
-        <v>1.2179</v>
+        <v>1.2043</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3567</v>
+        <v>0.3148</v>
       </c>
       <c r="E66" t="n">
-        <v>1.926</v>
+        <v>1.9045</v>
       </c>
       <c r="F66" t="n">
-        <v>1.926</v>
+        <v>1.9045</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>1.926</v>
+        <v>1.9045</v>
       </c>
       <c r="I66" t="n">
         <v>1.953</v>
@@ -3492,7 +3492,7 @@
         <v>1.2021</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3466</v>
+        <v>0.3134</v>
       </c>
       <c r="E67" t="n">
         <v>1.9009</v>
@@ -3538,7 +3538,7 @@
         <v>1.201</v>
       </c>
       <c r="D68" t="n">
-        <v>0.3459</v>
+        <v>0.3127</v>
       </c>
       <c r="E68" t="n">
         <v>1.8992</v>
@@ -3584,7 +3584,7 @@
         <v>1.1905</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3392</v>
+        <v>0.3061</v>
       </c>
       <c r="E69" t="n">
         <v>1.8826</v>
@@ -3620,93 +3620,93 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>aliStair</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1.8595</v>
+        <v>1.8585</v>
       </c>
       <c r="C70" t="n">
-        <v>1.1759</v>
+        <v>1.1752</v>
       </c>
       <c r="D70" t="n">
-        <v>0.3298</v>
+        <v>0.2965</v>
       </c>
       <c r="E70" t="n">
-        <v>1.8595</v>
+        <v>1.8585</v>
       </c>
       <c r="F70" t="n">
-        <v>1.8595</v>
+        <v>1.8585</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>1.8595</v>
+        <v>1.8585</v>
       </c>
       <c r="I70" t="n">
-        <v>1.8856</v>
+        <v>1.8585</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>372</v>
+        <v>251</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>1.8856</v>
+        <v>1.8585</v>
       </c>
       <c r="N70" t="n">
-        <v>372</v>
+        <v>251</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>aliStair</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1.8585</v>
+        <v>1.8388</v>
       </c>
       <c r="C71" t="n">
-        <v>1.1752</v>
+        <v>1.1628</v>
       </c>
       <c r="D71" t="n">
-        <v>0.3294</v>
+        <v>0.2887</v>
       </c>
       <c r="E71" t="n">
-        <v>1.8585</v>
+        <v>1.8388</v>
       </c>
       <c r="F71" t="n">
-        <v>1.8585</v>
+        <v>1.8388</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>1.8585</v>
+        <v>1.8388</v>
       </c>
       <c r="I71" t="n">
-        <v>1.8585</v>
+        <v>1.8856</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>251</v>
+        <v>372</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>1.8585</v>
+        <v>1.8856</v>
       </c>
       <c r="N71" t="n">
-        <v>251</v>
+        <v>372</v>
       </c>
     </row>
     <row r="72">
@@ -3722,7 +3722,7 @@
         <v>1.1259</v>
       </c>
       <c r="D72" t="n">
-        <v>0.2979</v>
+        <v>0.2654</v>
       </c>
       <c r="E72" t="n">
         <v>1.7804</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1.7451</v>
+        <v>1.7386</v>
       </c>
       <c r="C73" t="n">
-        <v>1.1035</v>
+        <v>1.0994</v>
       </c>
       <c r="D73" t="n">
-        <v>0.2836</v>
+        <v>0.2487</v>
       </c>
       <c r="E73" t="n">
-        <v>1.7451</v>
+        <v>1.7386</v>
       </c>
       <c r="F73" t="n">
-        <v>1.7451</v>
+        <v>1.7386</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>1.7451</v>
+        <v>1.7386</v>
       </c>
       <c r="I73" t="n">
         <v>1.7532</v>
@@ -3814,7 +3814,7 @@
         <v>1.0775</v>
       </c>
       <c r="D74" t="n">
-        <v>0.267</v>
+        <v>0.2349</v>
       </c>
       <c r="E74" t="n">
         <v>1.7039</v>
@@ -3860,7 +3860,7 @@
         <v>1.0504</v>
       </c>
       <c r="D75" t="n">
-        <v>0.2497</v>
+        <v>0.2179</v>
       </c>
       <c r="E75" t="n">
         <v>1.6611</v>
@@ -3906,7 +3906,7 @@
         <v>1.0185</v>
       </c>
       <c r="D76" t="n">
-        <v>0.2293</v>
+        <v>0.1978</v>
       </c>
       <c r="E76" t="n">
         <v>1.6107</v>
@@ -3946,25 +3946,25 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1.5586</v>
+        <v>1.5527</v>
       </c>
       <c r="C77" t="n">
-        <v>0.9856</v>
+        <v>0.9819</v>
       </c>
       <c r="D77" t="n">
-        <v>0.2083</v>
+        <v>0.1747</v>
       </c>
       <c r="E77" t="n">
-        <v>1.5586</v>
+        <v>1.5527</v>
       </c>
       <c r="F77" t="n">
-        <v>1.5586</v>
+        <v>1.5527</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>1.5586</v>
+        <v>1.5527</v>
       </c>
       <c r="I77" t="n">
         <v>1.5658</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1.4762</v>
+        <v>1.4707</v>
       </c>
       <c r="C78" t="n">
-        <v>0.9335</v>
+        <v>0.93</v>
       </c>
       <c r="D78" t="n">
-        <v>0.175</v>
+        <v>0.142</v>
       </c>
       <c r="E78" t="n">
-        <v>1.4762</v>
+        <v>1.4707</v>
       </c>
       <c r="F78" t="n">
-        <v>1.4762</v>
+        <v>1.4707</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>1.4762</v>
+        <v>1.4707</v>
       </c>
       <c r="I78" t="n">
         <v>1.4831</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1.3244</v>
+        <v>1.3195</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8375</v>
+        <v>0.8344</v>
       </c>
       <c r="D79" t="n">
-        <v>0.1137</v>
+        <v>0.0818</v>
       </c>
       <c r="E79" t="n">
-        <v>1.3244</v>
+        <v>1.3195</v>
       </c>
       <c r="F79" t="n">
-        <v>1.3244</v>
+        <v>1.3195</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>1.3244</v>
+        <v>1.3195</v>
       </c>
       <c r="I79" t="n">
         <v>1.3306</v>
@@ -4090,7 +4090,7 @@
         <v>0.8327</v>
       </c>
       <c r="D80" t="n">
-        <v>0.1106</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="E80" t="n">
         <v>1.3168</v>
@@ -4136,7 +4136,7 @@
         <v>0.7896</v>
       </c>
       <c r="D81" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0536</v>
       </c>
       <c r="E81" t="n">
         <v>1.2487</v>
@@ -4182,7 +4182,7 @@
         <v>0.7746</v>
       </c>
       <c r="D82" t="n">
-        <v>0.0735</v>
+        <v>0.0441</v>
       </c>
       <c r="E82" t="n">
         <v>1.2249</v>
@@ -4228,7 +4228,7 @@
         <v>0.7702</v>
       </c>
       <c r="D83" t="n">
-        <v>0.0707</v>
+        <v>0.0413</v>
       </c>
       <c r="E83" t="n">
         <v>1.218</v>
@@ -4274,7 +4274,7 @@
         <v>0.7302999999999999</v>
       </c>
       <c r="D84" t="n">
-        <v>0.0452</v>
+        <v>0.0162</v>
       </c>
       <c r="E84" t="n">
         <v>1.1549</v>
@@ -4320,7 +4320,7 @@
         <v>0.6646</v>
       </c>
       <c r="D85" t="n">
-        <v>0.0032</v>
+        <v>-0.0252</v>
       </c>
       <c r="E85" t="n">
         <v>1.051</v>
@@ -4366,7 +4366,7 @@
         <v>0.6467000000000001</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.0083</v>
+        <v>-0.0365</v>
       </c>
       <c r="E86" t="n">
         <v>1.0226</v>
@@ -4412,7 +4412,7 @@
         <v>0.6378</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.0139</v>
+        <v>-0.0421</v>
       </c>
       <c r="E87" t="n">
         <v>1.0086</v>
@@ -4458,7 +4458,7 @@
         <v>0.6343</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.0161</v>
+        <v>-0.0443</v>
       </c>
       <c r="E88" t="n">
         <v>1.0031</v>
@@ -4504,7 +4504,7 @@
         <v>0.6113</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.0308</v>
+        <v>-0.0588</v>
       </c>
       <c r="E89" t="n">
         <v>0.9667</v>
@@ -4550,7 +4550,7 @@
         <v>0.5973000000000001</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.0398</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="E90" t="n">
         <v>0.9446</v>
@@ -4590,25 +4590,25 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.88</v>
+        <v>0.8701</v>
       </c>
       <c r="C91" t="n">
-        <v>0.5565</v>
+        <v>0.5502</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.0659</v>
+        <v>-0.0973</v>
       </c>
       <c r="E91" t="n">
-        <v>0.88</v>
+        <v>0.8701</v>
       </c>
       <c r="F91" t="n">
-        <v>0.88</v>
+        <v>0.8701</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>0.88</v>
+        <v>0.8701</v>
       </c>
       <c r="I91" t="n">
         <v>0.8923</v>
@@ -4642,7 +4642,7 @@
         <v>0.5245</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.0863</v>
+        <v>-0.1134</v>
       </c>
       <c r="E92" t="n">
         <v>0.8295</v>
@@ -4688,7 +4688,7 @@
         <v>0.4975</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.1036</v>
+        <v>-0.1305</v>
       </c>
       <c r="E93" t="n">
         <v>0.7867</v>
@@ -4734,7 +4734,7 @@
         <v>0.4509</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.1333</v>
+        <v>-0.1598</v>
       </c>
       <c r="E94" t="n">
         <v>0.7131</v>
@@ -4780,7 +4780,7 @@
         <v>0.415</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.1563</v>
+        <v>-0.1825</v>
       </c>
       <c r="E95" t="n">
         <v>0.6562</v>
@@ -4826,7 +4826,7 @@
         <v>0.385</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.1754</v>
+        <v>-0.2014</v>
       </c>
       <c r="E96" t="n">
         <v>0.6088</v>
@@ -4872,7 +4872,7 @@
         <v>0.371</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.1843</v>
+        <v>-0.2102</v>
       </c>
       <c r="E97" t="n">
         <v>0.5867</v>
@@ -4918,7 +4918,7 @@
         <v>0.3601</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.1913</v>
+        <v>-0.217</v>
       </c>
       <c r="E98" t="n">
         <v>0.5695</v>
@@ -4958,25 +4958,25 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.435</v>
+        <v>0.4137</v>
       </c>
       <c r="C99" t="n">
-        <v>0.2751</v>
+        <v>0.2616</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.2456</v>
+        <v>-0.2791</v>
       </c>
       <c r="E99" t="n">
-        <v>0.435</v>
+        <v>0.4137</v>
       </c>
       <c r="F99" t="n">
-        <v>1.435</v>
+        <v>1.4137</v>
       </c>
       <c r="G99" t="n">
         <v>-1</v>
       </c>
       <c r="H99" t="n">
-        <v>1.435</v>
+        <v>1.4137</v>
       </c>
       <c r="I99" t="n">
         <v>1.4619</v>
@@ -5010,7 +5010,7 @@
         <v>0.2522</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.2602</v>
+        <v>-0.285</v>
       </c>
       <c r="E100" t="n">
         <v>0.3989</v>
@@ -5046,93 +5046,93 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>reck</t>
+          <t>KaiR0N-</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.3972</v>
+        <v>0.3952</v>
       </c>
       <c r="C101" t="n">
-        <v>0.2512</v>
+        <v>0.2499</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.2609</v>
+        <v>-0.2865</v>
       </c>
       <c r="E101" t="n">
-        <v>0.3972</v>
+        <v>0.3952</v>
       </c>
       <c r="F101" t="n">
-        <v>0.3972</v>
+        <v>0.3952</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>0.3972</v>
+        <v>0.3952</v>
       </c>
       <c r="I101" t="n">
-        <v>0.4009</v>
+        <v>0.3985</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>394</v>
+        <v>275</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>0.4009</v>
+        <v>0.3985</v>
       </c>
       <c r="N101" t="n">
-        <v>394</v>
+        <v>275</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>KaiR0N-</t>
+          <t>reck</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.3967</v>
+        <v>0.3942</v>
       </c>
       <c r="C102" t="n">
-        <v>0.2509</v>
+        <v>0.2493</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.2611</v>
+        <v>-0.2869</v>
       </c>
       <c r="E102" t="n">
-        <v>0.3967</v>
+        <v>0.3942</v>
       </c>
       <c r="F102" t="n">
-        <v>0.3967</v>
+        <v>0.3942</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>0.3967</v>
+        <v>0.3942</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3985</v>
+        <v>0.4009</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>275</v>
+        <v>394</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>0.3985</v>
+        <v>0.4009</v>
       </c>
       <c r="N102" t="n">
-        <v>275</v>
+        <v>394</v>
       </c>
     </row>
     <row r="103">
@@ -5148,7 +5148,7 @@
         <v>0.2427</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.2663</v>
+        <v>-0.291</v>
       </c>
       <c r="E103" t="n">
         <v>0.3838</v>
@@ -5194,7 +5194,7 @@
         <v>0.1776</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.3079</v>
+        <v>-0.332</v>
       </c>
       <c r="E104" t="n">
         <v>0.2808</v>
@@ -5240,7 +5240,7 @@
         <v>0.1594</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.3196</v>
+        <v>-0.3435</v>
       </c>
       <c r="E105" t="n">
         <v>0.252</v>
@@ -5286,7 +5286,7 @@
         <v>0.1384</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.333</v>
+        <v>-0.3567</v>
       </c>
       <c r="E106" t="n">
         <v>0.2188</v>
@@ -5332,7 +5332,7 @@
         <v>0.078</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.3715</v>
+        <v>-0.3947</v>
       </c>
       <c r="E107" t="n">
         <v>0.1234</v>
@@ -5378,7 +5378,7 @@
         <v>-0.045</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.4501</v>
+        <v>-0.4722</v>
       </c>
       <c r="E108" t="n">
         <v>-0.0711</v>
@@ -5418,25 +5418,25 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-0.1592</v>
+        <v>-0.1574</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.1007</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.4857</v>
+        <v>-0.5066000000000001</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.1592</v>
+        <v>-0.1574</v>
       </c>
       <c r="F109" t="n">
-        <v>-0.1592</v>
+        <v>-0.1574</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>-0.1592</v>
+        <v>-0.1574</v>
       </c>
       <c r="I109" t="n">
         <v>-0.1615</v>
@@ -5470,7 +5470,7 @@
         <v>-0.1177</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.4965</v>
+        <v>-0.5181</v>
       </c>
       <c r="E110" t="n">
         <v>-0.1861</v>
@@ -5516,7 +5516,7 @@
         <v>-0.1546</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.5201</v>
+        <v>-0.5413</v>
       </c>
       <c r="E111" t="n">
         <v>-0.2445</v>
@@ -5562,7 +5562,7 @@
         <v>-0.1743</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.5327</v>
+        <v>-0.5537</v>
       </c>
       <c r="E112" t="n">
         <v>-0.2757</v>
@@ -5608,7 +5608,7 @@
         <v>-0.1895</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.5424</v>
+        <v>-0.5633</v>
       </c>
       <c r="E113" t="n">
         <v>-0.2997</v>
@@ -5654,7 +5654,7 @@
         <v>-0.223</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.5638</v>
+        <v>-0.5844</v>
       </c>
       <c r="E114" t="n">
         <v>-0.3526</v>
@@ -5700,7 +5700,7 @@
         <v>-0.2792</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.5997</v>
+        <v>-0.6198</v>
       </c>
       <c r="E115" t="n">
         <v>-0.4415</v>
@@ -5746,7 +5746,7 @@
         <v>-0.3128</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.6212</v>
+        <v>-0.641</v>
       </c>
       <c r="E116" t="n">
         <v>-0.4947</v>
@@ -5792,7 +5792,7 @@
         <v>-0.3167</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.6237</v>
+        <v>-0.6434</v>
       </c>
       <c r="E117" t="n">
         <v>-0.5008</v>
@@ -5838,7 +5838,7 @@
         <v>-0.3431</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.6405</v>
+        <v>-0.66</v>
       </c>
       <c r="E118" t="n">
         <v>-0.5425</v>
@@ -5884,7 +5884,7 @@
         <v>-0.3636</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.6536</v>
+        <v>-0.673</v>
       </c>
       <c r="E119" t="n">
         <v>-0.575</v>
@@ -5930,7 +5930,7 @@
         <v>-0.3718</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.6589</v>
+        <v>-0.6781</v>
       </c>
       <c r="E120" t="n">
         <v>-0.5879</v>
@@ -5976,7 +5976,7 @@
         <v>-0.3787</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.6633</v>
+        <v>-0.6825</v>
       </c>
       <c r="E121" t="n">
         <v>-0.5989</v>
@@ -6022,7 +6022,7 @@
         <v>-0.3862</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.6681</v>
+        <v>-0.6872</v>
       </c>
       <c r="E122" t="n">
         <v>-0.6107</v>
@@ -6068,7 +6068,7 @@
         <v>-0.4056</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.6805</v>
+        <v>-0.6994</v>
       </c>
       <c r="E123" t="n">
         <v>-0.6414</v>
@@ -6114,7 +6114,7 @@
         <v>-0.4526</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.7105</v>
+        <v>-0.7291</v>
       </c>
       <c r="E124" t="n">
         <v>-0.7158</v>
@@ -6154,25 +6154,25 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-0.7298</v>
+        <v>-0.7271</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.4615</v>
+        <v>-0.4598</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.7336</v>
       </c>
       <c r="E125" t="n">
-        <v>-0.7298</v>
+        <v>-0.7271</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.7298</v>
+        <v>-0.7271</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>-0.7298</v>
+        <v>-0.7271</v>
       </c>
       <c r="I125" t="n">
         <v>-0.7332</v>
@@ -6206,7 +6206,7 @@
         <v>-0.4654</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.7186</v>
+        <v>-0.7371</v>
       </c>
       <c r="E126" t="n">
         <v>-0.7359</v>
@@ -6252,7 +6252,7 @@
         <v>-0.5152</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.7504999999999999</v>
+        <v>-0.7685</v>
       </c>
       <c r="E127" t="n">
         <v>-0.8148</v>
@@ -6298,7 +6298,7 @@
         <v>-0.5163</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.7512</v>
+        <v>-0.7692</v>
       </c>
       <c r="E128" t="n">
         <v>-0.8165</v>
@@ -6344,7 +6344,7 @@
         <v>-0.5338000000000001</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.7624</v>
+        <v>-0.7802</v>
       </c>
       <c r="E129" t="n">
         <v>-0.8442</v>
@@ -6390,7 +6390,7 @@
         <v>-0.5376</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.7648</v>
+        <v>-0.7826</v>
       </c>
       <c r="E130" t="n">
         <v>-0.8501</v>
@@ -6436,7 +6436,7 @@
         <v>-0.548</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.7714</v>
+        <v>-0.7892</v>
       </c>
       <c r="E131" t="n">
         <v>-0.8666</v>
@@ -6476,25 +6476,25 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-0.9058</v>
+        <v>-0.9024</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.5728</v>
+        <v>-0.5706</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.7873</v>
+        <v>-0.8034</v>
       </c>
       <c r="E132" t="n">
-        <v>-0.9058</v>
+        <v>-0.9024</v>
       </c>
       <c r="F132" t="n">
-        <v>-0.9058</v>
+        <v>-0.9024</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>-0.9058</v>
+        <v>-0.9024</v>
       </c>
       <c r="I132" t="n">
         <v>-0.91</v>
@@ -6528,7 +6528,7 @@
         <v>-0.653</v>
       </c>
       <c r="D133" t="n">
-        <v>-0.8386</v>
+        <v>-0.8552999999999999</v>
       </c>
       <c r="E133" t="n">
         <v>-1.0327</v>
@@ -6574,7 +6574,7 @@
         <v>-0.6592</v>
       </c>
       <c r="D134" t="n">
-        <v>-0.8425</v>
+        <v>-0.8592</v>
       </c>
       <c r="E134" t="n">
         <v>-1.0425</v>
@@ -6614,25 +6614,25 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>-1.271</v>
+        <v>-1.2662</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.8037</v>
+        <v>-0.8007</v>
       </c>
       <c r="D135" t="n">
-        <v>-0.9348</v>
+        <v>-0.9484</v>
       </c>
       <c r="E135" t="n">
-        <v>-1.271</v>
+        <v>-1.2662</v>
       </c>
       <c r="F135" t="n">
-        <v>-1.271</v>
+        <v>-1.2662</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>-1.271</v>
+        <v>-1.2662</v>
       </c>
       <c r="I135" t="n">
         <v>-1.2769</v>
@@ -6666,7 +6666,7 @@
         <v>-0.9666</v>
       </c>
       <c r="D136" t="n">
-        <v>-1.0389</v>
+        <v>-1.0529</v>
       </c>
       <c r="E136" t="n">
         <v>-1.5286</v>
@@ -6712,7 +6712,7 @@
         <v>-1.0025</v>
       </c>
       <c r="D137" t="n">
-        <v>-1.0618</v>
+        <v>-1.0755</v>
       </c>
       <c r="E137" t="n">
         <v>-1.5854</v>
@@ -6758,7 +6758,7 @@
         <v>-1.0772</v>
       </c>
       <c r="D138" t="n">
-        <v>-1.1095</v>
+        <v>-1.1225</v>
       </c>
       <c r="E138" t="n">
         <v>-1.7034</v>
@@ -6804,7 +6804,7 @@
         <v>-1.0836</v>
       </c>
       <c r="D139" t="n">
-        <v>-1.1136</v>
+        <v>-1.1266</v>
       </c>
       <c r="E139" t="n">
         <v>-1.7135</v>
@@ -6850,7 +6850,7 @@
         <v>-1.0868</v>
       </c>
       <c r="D140" t="n">
-        <v>-1.1157</v>
+        <v>-1.1286</v>
       </c>
       <c r="E140" t="n">
         <v>-1.7187</v>
@@ -6896,7 +6896,7 @@
         <v>-1.2005</v>
       </c>
       <c r="D141" t="n">
-        <v>-1.1883</v>
+        <v>-1.2003</v>
       </c>
       <c r="E141" t="n">
         <v>-1.8985</v>
@@ -6942,7 +6942,7 @@
         <v>-1.2514</v>
       </c>
       <c r="D142" t="n">
-        <v>-1.2208</v>
+        <v>-1.2323</v>
       </c>
       <c r="E142" t="n">
         <v>-1.979</v>
@@ -6988,7 +6988,7 @@
         <v>-1.2516</v>
       </c>
       <c r="D143" t="n">
-        <v>-1.221</v>
+        <v>-1.2325</v>
       </c>
       <c r="E143" t="n">
         <v>-1.9793</v>
@@ -7034,7 +7034,7 @@
         <v>-1.3237</v>
       </c>
       <c r="D144" t="n">
-        <v>-1.267</v>
+        <v>-1.2779</v>
       </c>
       <c r="E144" t="n">
         <v>-2.0933</v>
@@ -7080,7 +7080,7 @@
         <v>-1.3464</v>
       </c>
       <c r="D145" t="n">
-        <v>-1.2815</v>
+        <v>-1.2922</v>
       </c>
       <c r="E145" t="n">
         <v>-2.1292</v>
@@ -7120,25 +7120,25 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-2.2754</v>
+        <v>-2.2669</v>
       </c>
       <c r="C146" t="n">
-        <v>-1.4389</v>
+        <v>-1.4335</v>
       </c>
       <c r="D146" t="n">
-        <v>-1.3406</v>
+        <v>-1.347</v>
       </c>
       <c r="E146" t="n">
-        <v>-2.2754</v>
+        <v>-2.2669</v>
       </c>
       <c r="F146" t="n">
-        <v>-2.2754</v>
+        <v>-2.2669</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>-2.2754</v>
+        <v>-2.2669</v>
       </c>
       <c r="I146" t="n">
         <v>-2.286</v>
@@ -7172,7 +7172,7 @@
         <v>-1.4996</v>
       </c>
       <c r="D147" t="n">
-        <v>-1.3794</v>
+        <v>-1.3887</v>
       </c>
       <c r="E147" t="n">
         <v>-2.3715</v>
@@ -7218,7 +7218,7 @@
         <v>-1.6173</v>
       </c>
       <c r="D148" t="n">
-        <v>-1.4545</v>
+        <v>-1.4628</v>
       </c>
       <c r="E148" t="n">
         <v>-2.5575</v>
@@ -7264,7 +7264,7 @@
         <v>-1.6683</v>
       </c>
       <c r="D149" t="n">
-        <v>-1.4871</v>
+        <v>-1.495</v>
       </c>
       <c r="E149" t="n">
         <v>-2.6382</v>
@@ -7310,7 +7310,7 @@
         <v>-1.6729</v>
       </c>
       <c r="D150" t="n">
-        <v>-1.49</v>
+        <v>-1.4978</v>
       </c>
       <c r="E150" t="n">
         <v>-2.6454</v>
@@ -7350,25 +7350,25 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-2.6823</v>
+        <v>-2.6723</v>
       </c>
       <c r="C151" t="n">
-        <v>-1.6962</v>
+        <v>-1.6899</v>
       </c>
       <c r="D151" t="n">
-        <v>-1.505</v>
+        <v>-1.5086</v>
       </c>
       <c r="E151" t="n">
-        <v>-2.6823</v>
+        <v>-2.6723</v>
       </c>
       <c r="F151" t="n">
-        <v>-2.6823</v>
+        <v>-2.6723</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
       </c>
       <c r="H151" t="n">
-        <v>-2.6823</v>
+        <v>-2.6723</v>
       </c>
       <c r="I151" t="n">
         <v>-2.6948</v>
@@ -7396,25 +7396,25 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-2.8384</v>
+        <v>-2.8034</v>
       </c>
       <c r="C152" t="n">
-        <v>-1.7949</v>
+        <v>-1.7728</v>
       </c>
       <c r="D152" t="n">
-        <v>-1.568</v>
+        <v>-1.5608</v>
       </c>
       <c r="E152" t="n">
-        <v>-2.8384</v>
+        <v>-2.8034</v>
       </c>
       <c r="F152" t="n">
-        <v>-1.8926</v>
+        <v>-1.8576</v>
       </c>
       <c r="G152" t="n">
         <v>-0.9458</v>
       </c>
       <c r="H152" t="n">
-        <v>-1.8926</v>
+        <v>-1.8576</v>
       </c>
       <c r="I152" t="n">
         <v>-1.9371</v>
@@ -7448,7 +7448,7 @@
         <v>-1.7964</v>
       </c>
       <c r="D153" t="n">
-        <v>-1.5689</v>
+        <v>-1.5756</v>
       </c>
       <c r="E153" t="n">
         <v>-2.8407</v>
@@ -7494,7 +7494,7 @@
         <v>-1.8284</v>
       </c>
       <c r="D154" t="n">
-        <v>-1.5894</v>
+        <v>-1.5958</v>
       </c>
       <c r="E154" t="n">
         <v>-2.8914</v>
@@ -7540,7 +7540,7 @@
         <v>-1.8329</v>
       </c>
       <c r="D155" t="n">
-        <v>-1.5923</v>
+        <v>-1.5987</v>
       </c>
       <c r="E155" t="n">
         <v>-2.8985</v>
@@ -7586,7 +7586,7 @@
         <v>-1.8796</v>
       </c>
       <c r="D156" t="n">
-        <v>-1.6221</v>
+        <v>-1.6281</v>
       </c>
       <c r="E156" t="n">
         <v>-2.9724</v>
@@ -7626,25 +7626,25 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-2.9842</v>
+        <v>-2.9731</v>
       </c>
       <c r="C157" t="n">
-        <v>-1.8871</v>
+        <v>-1.8801</v>
       </c>
       <c r="D157" t="n">
-        <v>-1.6269</v>
+        <v>-1.6284</v>
       </c>
       <c r="E157" t="n">
-        <v>-2.9842</v>
+        <v>-2.9731</v>
       </c>
       <c r="F157" t="n">
-        <v>-2.9842</v>
+        <v>-2.9731</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>-2.9842</v>
+        <v>-2.9731</v>
       </c>
       <c r="I157" t="n">
         <v>-2.9981</v>
@@ -7672,25 +7672,25 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-3.5891</v>
+        <v>-3.5757</v>
       </c>
       <c r="C158" t="n">
-        <v>-2.2696</v>
+        <v>-2.2611</v>
       </c>
       <c r="D158" t="n">
-        <v>-1.8713</v>
+        <v>-1.8685</v>
       </c>
       <c r="E158" t="n">
-        <v>-3.5891</v>
+        <v>-3.5757</v>
       </c>
       <c r="F158" t="n">
-        <v>-3.5891</v>
+        <v>-3.5757</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>-3.5891</v>
+        <v>-3.5757</v>
       </c>
       <c r="I158" t="n">
         <v>-3.6058</v>
@@ -7724,7 +7724,7 @@
         <v>-2.3291</v>
       </c>
       <c r="D159" t="n">
-        <v>-1.9093</v>
+        <v>-1.9113</v>
       </c>
       <c r="E159" t="n">
         <v>-3.6832</v>
@@ -7770,7 +7770,7 @@
         <v>-2.9505</v>
       </c>
       <c r="D160" t="n">
-        <v>-2.3063</v>
+        <v>-2.3028</v>
       </c>
       <c r="E160" t="n">
         <v>-4.6659</v>
@@ -7810,25 +7810,25 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-6.0037</v>
+        <v>-5.9057</v>
       </c>
       <c r="C161" t="n">
-        <v>-3.7965</v>
+        <v>-3.7345</v>
       </c>
       <c r="D161" t="n">
-        <v>-2.8467</v>
+        <v>-2.7967</v>
       </c>
       <c r="E161" t="n">
-        <v>-6.0037</v>
+        <v>-5.9057</v>
       </c>
       <c r="F161" t="n">
-        <v>-5.2943</v>
+        <v>-5.1963</v>
       </c>
       <c r="G161" t="n">
         <v>-0.7094</v>
       </c>
       <c r="H161" t="n">
-        <v>-5.2943</v>
+        <v>-5.1963</v>
       </c>
       <c r="I161" t="n">
         <v>-5.4187</v>

--- a/database/event/7440/event_7440_evp_summary.xlsx
+++ b/database/event/7440/event_7440_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.2387</v>
+        <v>11.9349</v>
       </c>
       <c r="C2" t="n">
-        <v>7.1069</v>
+        <v>7.5472</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4919</v>
+        <v>4.7172</v>
       </c>
       <c r="E2" t="n">
-        <v>11.2387</v>
+        <v>11.9349</v>
       </c>
       <c r="F2" t="n">
         <v>5.048</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.3696</v>
+        <v>8.648899999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>5.2926</v>
+        <v>5.4692</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1858</v>
+        <v>3.2495</v>
       </c>
       <c r="E3" t="n">
-        <v>8.3696</v>
+        <v>8.648899999999999</v>
       </c>
       <c r="F3" t="n">
         <v>2.1788</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.5241</v>
+        <v>7.5913</v>
       </c>
       <c r="C4" t="n">
-        <v>4.758</v>
+        <v>4.8004</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8009</v>
+        <v>2.777</v>
       </c>
       <c r="E4" t="n">
-        <v>7.5241</v>
+        <v>7.5913</v>
       </c>
       <c r="F4" t="n">
         <v>2.7476</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.312</v>
+        <v>7.2873</v>
       </c>
       <c r="C5" t="n">
-        <v>4.6238</v>
+        <v>4.6082</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7044</v>
+        <v>2.6413</v>
       </c>
       <c r="E5" t="n">
-        <v>7.312</v>
+        <v>7.2873</v>
       </c>
       <c r="F5" t="n">
         <v>3.3728</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.8479</v>
+        <v>6.104</v>
       </c>
       <c r="C6" t="n">
-        <v>3.698</v>
+        <v>3.8599</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0379</v>
+        <v>2.1127</v>
       </c>
       <c r="E6" t="n">
-        <v>5.8479</v>
+        <v>6.104</v>
       </c>
       <c r="F6" t="n">
         <v>3.16</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.5967</v>
+        <v>5.9128</v>
       </c>
       <c r="C7" t="n">
-        <v>3.5391</v>
+        <v>3.739</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9235</v>
+        <v>2.0273</v>
       </c>
       <c r="E7" t="n">
-        <v>5.5967</v>
+        <v>5.9128</v>
       </c>
       <c r="F7" t="n">
         <v>3.0284</v>
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.586</v>
+        <v>5.7726</v>
       </c>
       <c r="C8" t="n">
-        <v>3.5324</v>
+        <v>3.6504</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9187</v>
+        <v>1.9647</v>
       </c>
       <c r="E8" t="n">
-        <v>5.586</v>
+        <v>5.7726</v>
       </c>
       <c r="F8" t="n">
         <v>3.1794</v>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.5608</v>
+        <v>5.7564</v>
       </c>
       <c r="C9" t="n">
-        <v>3.5164</v>
+        <v>3.6401</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9072</v>
+        <v>1.9574</v>
       </c>
       <c r="E9" t="n">
-        <v>5.5608</v>
+        <v>5.7564</v>
       </c>
       <c r="F9" t="n">
         <v>4.4822</v>
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.5085</v>
+        <v>5.59</v>
       </c>
       <c r="C10" t="n">
-        <v>3.4834</v>
+        <v>3.5349</v>
       </c>
       <c r="D10" t="n">
-        <v>1.8834</v>
+        <v>1.8831</v>
       </c>
       <c r="E10" t="n">
-        <v>5.5085</v>
+        <v>5.59</v>
       </c>
       <c r="F10" t="n">
         <v>5.0803</v>
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.4274</v>
+        <v>5.5832</v>
       </c>
       <c r="C11" t="n">
-        <v>3.4321</v>
+        <v>3.5306</v>
       </c>
       <c r="D11" t="n">
-        <v>1.8465</v>
+        <v>1.8801</v>
       </c>
       <c r="E11" t="n">
-        <v>5.4274</v>
+        <v>5.5832</v>
       </c>
       <c r="F11" t="n">
         <v>4.2231</v>
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.1798</v>
+        <v>5.5065</v>
       </c>
       <c r="C12" t="n">
-        <v>3.2755</v>
+        <v>3.4821</v>
       </c>
       <c r="D12" t="n">
-        <v>1.7337</v>
+        <v>1.8458</v>
       </c>
       <c r="E12" t="n">
-        <v>5.1798</v>
+        <v>5.5065</v>
       </c>
       <c r="F12" t="n">
         <v>5.1798</v>
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.0702</v>
+        <v>5.3951</v>
       </c>
       <c r="C13" t="n">
-        <v>3.2062</v>
+        <v>3.4117</v>
       </c>
       <c r="D13" t="n">
-        <v>1.6839</v>
+        <v>1.7961</v>
       </c>
       <c r="E13" t="n">
-        <v>5.0702</v>
+        <v>5.3951</v>
       </c>
       <c r="F13" t="n">
         <v>5.0702</v>
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.7789</v>
+        <v>4.9514</v>
       </c>
       <c r="C14" t="n">
-        <v>3.022</v>
+        <v>3.1311</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5513</v>
+        <v>1.5979</v>
       </c>
       <c r="E14" t="n">
-        <v>4.7789</v>
+        <v>4.9514</v>
       </c>
       <c r="F14" t="n">
         <v>2.0174</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.7541</v>
+        <v>4.9296</v>
       </c>
       <c r="C15" t="n">
-        <v>3.0063</v>
+        <v>3.1173</v>
       </c>
       <c r="D15" t="n">
-        <v>1.54</v>
+        <v>1.5881</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7541</v>
+        <v>4.9296</v>
       </c>
       <c r="F15" t="n">
-        <v>4.7541</v>
+        <v>4.7624</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>7.6802</v>
+        <v>7.6984</v>
       </c>
       <c r="I15" t="n">
-        <v>8.289400000000001</v>
+        <v>8.308999999999999</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>8.289400000000001</v>
+        <v>8.308999999999999</v>
       </c>
       <c r="N15" t="n">
         <v>372</v>
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.6974</v>
+        <v>4.8264</v>
       </c>
       <c r="C16" t="n">
-        <v>2.9705</v>
+        <v>3.052</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5141</v>
+        <v>1.542</v>
       </c>
       <c r="E16" t="n">
-        <v>4.6974</v>
+        <v>4.8264</v>
       </c>
       <c r="F16" t="n">
         <v>1.6927</v>
@@ -1182,185 +1182,185 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Krimbo</t>
+          <t>DemQQ</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.6053</v>
+        <v>4.8021</v>
       </c>
       <c r="C17" t="n">
-        <v>2.9122</v>
+        <v>3.0367</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4722</v>
+        <v>1.5312</v>
       </c>
       <c r="E17" t="n">
-        <v>4.6053</v>
+        <v>4.8021</v>
       </c>
       <c r="F17" t="n">
-        <v>4.6053</v>
+        <v>4.5966</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>7.3546</v>
+        <v>7.3355</v>
       </c>
       <c r="I17" t="n">
-        <v>7.5441</v>
+        <v>7.5245</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>281</v>
+        <v>385</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>7.5441</v>
+        <v>7.5245</v>
       </c>
       <c r="N17" t="n">
-        <v>281</v>
+        <v>385</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DemQQ</t>
+          <t>Krimbo</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.5966</v>
+        <v>4.7725</v>
       </c>
       <c r="C18" t="n">
-        <v>2.9067</v>
+        <v>3.0179</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4683</v>
+        <v>1.518</v>
       </c>
       <c r="E18" t="n">
-        <v>4.5966</v>
+        <v>4.7725</v>
       </c>
       <c r="F18" t="n">
-        <v>4.5966</v>
+        <v>4.6053</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>7.3355</v>
+        <v>7.3546</v>
       </c>
       <c r="I18" t="n">
-        <v>7.5245</v>
+        <v>7.5441</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>385</v>
+        <v>281</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>7.5245</v>
+        <v>7.5441</v>
       </c>
       <c r="N18" t="n">
-        <v>385</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.457</v>
+        <v>4.6766</v>
       </c>
       <c r="C19" t="n">
-        <v>2.8184</v>
+        <v>2.9573</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4047</v>
+        <v>1.4751</v>
       </c>
       <c r="E19" t="n">
-        <v>4.457</v>
+        <v>4.6766</v>
       </c>
       <c r="F19" t="n">
-        <v>3.1534</v>
+        <v>4.079</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3036</v>
+        <v>0.346</v>
       </c>
       <c r="H19" t="n">
-        <v>4.1769</v>
+        <v>6.2027</v>
       </c>
       <c r="I19" t="n">
-        <v>4.1769</v>
+        <v>6.8672</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3036</v>
+        <v>0.346</v>
       </c>
       <c r="K19" t="n">
-        <v>172</v>
+        <v>316</v>
       </c>
       <c r="L19" t="n">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="M19" t="n">
-        <v>5.4805</v>
+        <v>7.213200000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>270</v>
+        <v>355</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.4205</v>
+        <v>4.6675</v>
       </c>
       <c r="C20" t="n">
-        <v>2.7954</v>
+        <v>2.9515</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3881</v>
+        <v>1.471</v>
       </c>
       <c r="E20" t="n">
-        <v>4.4205</v>
+        <v>4.6675</v>
       </c>
       <c r="F20" t="n">
-        <v>4.0745</v>
+        <v>3.1534</v>
       </c>
       <c r="G20" t="n">
-        <v>0.346</v>
+        <v>1.3036</v>
       </c>
       <c r="H20" t="n">
-        <v>6.193</v>
+        <v>4.1769</v>
       </c>
       <c r="I20" t="n">
-        <v>6.8564</v>
+        <v>4.1769</v>
       </c>
       <c r="J20" t="n">
-        <v>0.346</v>
+        <v>1.3036</v>
       </c>
       <c r="K20" t="n">
-        <v>316</v>
+        <v>172</v>
       </c>
       <c r="L20" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="M20" t="n">
-        <v>7.2024</v>
+        <v>5.4805</v>
       </c>
       <c r="N20" t="n">
-        <v>355</v>
+        <v>270</v>
       </c>
     </row>
     <row r="21">
@@ -1370,16 +1370,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.1534</v>
+        <v>4.4281</v>
       </c>
       <c r="C21" t="n">
-        <v>2.6265</v>
+        <v>2.8002</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2665</v>
+        <v>1.3641</v>
       </c>
       <c r="E21" t="n">
-        <v>4.1534</v>
+        <v>4.4281</v>
       </c>
       <c r="F21" t="n">
         <v>4.1534</v>
@@ -1412,32 +1412,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.0973</v>
+        <v>4.2804</v>
       </c>
       <c r="C22" t="n">
-        <v>2.591</v>
+        <v>2.7068</v>
       </c>
       <c r="D22" t="n">
-        <v>1.241</v>
+        <v>1.2981</v>
       </c>
       <c r="E22" t="n">
-        <v>4.0973</v>
+        <v>4.2804</v>
       </c>
       <c r="F22" t="n">
-        <v>4.0973</v>
+        <v>4.0888</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>6.2428</v>
+        <v>6.2242</v>
       </c>
       <c r="I22" t="n">
-        <v>6.4037</v>
+        <v>6.3846</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>6.4037</v>
+        <v>6.3846</v>
       </c>
       <c r="N22" t="n">
         <v>299</v>
@@ -1458,32 +1458,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.0888</v>
+        <v>4.2599</v>
       </c>
       <c r="C23" t="n">
-        <v>2.5856</v>
+        <v>2.6938</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2371</v>
+        <v>1.289</v>
       </c>
       <c r="E23" t="n">
-        <v>4.0888</v>
+        <v>4.2599</v>
       </c>
       <c r="F23" t="n">
-        <v>4.0888</v>
+        <v>4.0973</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>6.2242</v>
+        <v>6.2428</v>
       </c>
       <c r="I23" t="n">
-        <v>6.3846</v>
+        <v>6.4037</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>6.3846</v>
+        <v>6.4037</v>
       </c>
       <c r="N23" t="n">
         <v>299</v>
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.0322</v>
+        <v>4.2351</v>
       </c>
       <c r="C24" t="n">
-        <v>2.5498</v>
+        <v>2.6781</v>
       </c>
       <c r="D24" t="n">
-        <v>1.2113</v>
+        <v>1.2779</v>
       </c>
       <c r="E24" t="n">
-        <v>4.0322</v>
+        <v>4.2351</v>
       </c>
       <c r="F24" t="n">
         <v>4.0322</v>
@@ -1550,185 +1550,185 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>hades</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.9287</v>
+        <v>4.1278</v>
       </c>
       <c r="C25" t="n">
-        <v>2.4844</v>
+        <v>2.6103</v>
       </c>
       <c r="D25" t="n">
-        <v>1.1642</v>
+        <v>1.23</v>
       </c>
       <c r="E25" t="n">
-        <v>3.9287</v>
+        <v>4.1278</v>
       </c>
       <c r="F25" t="n">
-        <v>3.4405</v>
+        <v>3.6942</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4882</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>4.8053</v>
+        <v>5.3606</v>
       </c>
       <c r="I25" t="n">
-        <v>4.8053</v>
+        <v>5.3606</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4882</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>249</v>
+        <v>216</v>
       </c>
       <c r="L25" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>5.2935</v>
+        <v>5.3606</v>
       </c>
       <c r="N25" t="n">
-        <v>291</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sl3nd</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.8185</v>
+        <v>4.0693</v>
       </c>
       <c r="C26" t="n">
-        <v>2.4147</v>
+        <v>2.5733</v>
       </c>
       <c r="D26" t="n">
-        <v>1.1141</v>
+        <v>1.2038</v>
       </c>
       <c r="E26" t="n">
-        <v>3.8185</v>
+        <v>4.0693</v>
       </c>
       <c r="F26" t="n">
-        <v>3.8185</v>
+        <v>3.4405</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.4882</v>
       </c>
       <c r="H26" t="n">
-        <v>5.6326</v>
+        <v>4.8053</v>
       </c>
       <c r="I26" t="n">
-        <v>5.6326</v>
+        <v>4.8053</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.4882</v>
       </c>
       <c r="K26" t="n">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M26" t="n">
-        <v>5.6326</v>
+        <v>5.2935</v>
       </c>
       <c r="N26" t="n">
-        <v>226</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>sl3nd</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.8127</v>
+        <v>3.9918</v>
       </c>
       <c r="C27" t="n">
-        <v>2.411</v>
+        <v>2.5243</v>
       </c>
       <c r="D27" t="n">
-        <v>1.1114</v>
+        <v>1.1692</v>
       </c>
       <c r="E27" t="n">
-        <v>3.8127</v>
+        <v>3.9918</v>
       </c>
       <c r="F27" t="n">
-        <v>4.0909</v>
+        <v>3.824</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.2782</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>6.2288</v>
+        <v>5.6447</v>
       </c>
       <c r="I27" t="n">
-        <v>7.0738</v>
+        <v>5.6447</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.2782</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>408</v>
+        <v>226</v>
       </c>
       <c r="L27" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>6.7956</v>
+        <v>5.6447</v>
       </c>
       <c r="N27" t="n">
-        <v>462</v>
+        <v>226</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>hades</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.6942</v>
+        <v>3.9852</v>
       </c>
       <c r="C28" t="n">
-        <v>2.3361</v>
+        <v>2.5201</v>
       </c>
       <c r="D28" t="n">
-        <v>1.0575</v>
+        <v>1.1663</v>
       </c>
       <c r="E28" t="n">
-        <v>3.6942</v>
+        <v>3.9852</v>
       </c>
       <c r="F28" t="n">
-        <v>3.6942</v>
+        <v>4.0909</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.2782</v>
       </c>
       <c r="H28" t="n">
-        <v>5.3606</v>
+        <v>6.2288</v>
       </c>
       <c r="I28" t="n">
-        <v>5.3606</v>
+        <v>7.0738</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.2782</v>
       </c>
       <c r="K28" t="n">
-        <v>216</v>
+        <v>408</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M28" t="n">
-        <v>5.3606</v>
+        <v>6.7956</v>
       </c>
       <c r="N28" t="n">
-        <v>216</v>
+        <v>462</v>
       </c>
     </row>
     <row r="29">
@@ -1738,16 +1738,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.5965</v>
+        <v>3.7596</v>
       </c>
       <c r="C29" t="n">
-        <v>2.2743</v>
+        <v>2.3774</v>
       </c>
       <c r="D29" t="n">
-        <v>1.013</v>
+        <v>1.0655</v>
       </c>
       <c r="E29" t="n">
-        <v>3.5965</v>
+        <v>3.7596</v>
       </c>
       <c r="F29" t="n">
         <v>3.5965</v>
@@ -1780,262 +1780,262 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.5647</v>
+        <v>3.72</v>
       </c>
       <c r="C30" t="n">
-        <v>2.2542</v>
+        <v>2.3524</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9985000000000001</v>
+        <v>1.0478</v>
       </c>
       <c r="E30" t="n">
-        <v>3.5647</v>
+        <v>3.72</v>
       </c>
       <c r="F30" t="n">
-        <v>3.2787</v>
+        <v>3.5045</v>
       </c>
       <c r="G30" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>4.4511</v>
+        <v>4.9454</v>
       </c>
       <c r="I30" t="n">
-        <v>4.4511</v>
+        <v>4.9454</v>
       </c>
       <c r="J30" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>249</v>
+        <v>300</v>
       </c>
       <c r="L30" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.7371</v>
+        <v>4.9454</v>
       </c>
       <c r="N30" t="n">
-        <v>291</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.5045</v>
+        <v>3.6381</v>
       </c>
       <c r="C31" t="n">
-        <v>2.2161</v>
+        <v>2.3006</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9711</v>
+        <v>1.0112</v>
       </c>
       <c r="E31" t="n">
-        <v>3.5045</v>
+        <v>3.6381</v>
       </c>
       <c r="F31" t="n">
-        <v>3.5045</v>
+        <v>3.2787</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="H31" t="n">
-        <v>4.9454</v>
+        <v>4.4511</v>
       </c>
       <c r="I31" t="n">
-        <v>4.9454</v>
+        <v>4.4511</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="K31" t="n">
-        <v>300</v>
+        <v>249</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M31" t="n">
-        <v>4.9454</v>
+        <v>4.7371</v>
       </c>
       <c r="N31" t="n">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Swisher</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.3941</v>
+        <v>3.4237</v>
       </c>
       <c r="C32" t="n">
-        <v>2.1463</v>
+        <v>2.165</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.9155</v>
       </c>
       <c r="E32" t="n">
-        <v>3.3941</v>
+        <v>3.4237</v>
       </c>
       <c r="F32" t="n">
-        <v>3.3941</v>
+        <v>3.7008</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.3613</v>
       </c>
       <c r="H32" t="n">
-        <v>4.7038</v>
+        <v>5.3749</v>
       </c>
       <c r="I32" t="n">
-        <v>4.9493</v>
+        <v>6.104</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.3613</v>
       </c>
       <c r="K32" t="n">
-        <v>394</v>
+        <v>353</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M32" t="n">
-        <v>4.9493</v>
+        <v>5.7427</v>
       </c>
       <c r="N32" t="n">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>Swisher</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.372</v>
+        <v>3.4129</v>
       </c>
       <c r="C33" t="n">
-        <v>2.1323</v>
+        <v>2.1582</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9108000000000001</v>
+        <v>0.9106</v>
       </c>
       <c r="E33" t="n">
-        <v>3.372</v>
+        <v>3.4129</v>
       </c>
       <c r="F33" t="n">
-        <v>2.8739</v>
+        <v>3.3941</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4981</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>3.5651</v>
+        <v>4.7038</v>
       </c>
       <c r="I33" t="n">
-        <v>3.947</v>
+        <v>4.9493</v>
       </c>
       <c r="J33" t="n">
-        <v>0.4981</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>316</v>
+        <v>394</v>
       </c>
       <c r="L33" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.4451</v>
+        <v>4.9493</v>
       </c>
       <c r="N33" t="n">
-        <v>355</v>
+        <v>394</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.3399</v>
+        <v>3.4004</v>
       </c>
       <c r="C34" t="n">
-        <v>2.112</v>
+        <v>2.1503</v>
       </c>
       <c r="D34" t="n">
-        <v>0.8962</v>
+        <v>0.9051</v>
       </c>
       <c r="E34" t="n">
-        <v>3.3399</v>
+        <v>3.4004</v>
       </c>
       <c r="F34" t="n">
-        <v>3.7012</v>
+        <v>3.336</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.3613</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>5.3757</v>
+        <v>4.5766</v>
       </c>
       <c r="I34" t="n">
-        <v>6.105</v>
+        <v>4.5766</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.3613</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>353</v>
+        <v>207</v>
       </c>
       <c r="L34" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>5.7437</v>
+        <v>4.5766</v>
       </c>
       <c r="N34" t="n">
-        <v>391</v>
+        <v>207</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.336</v>
+        <v>3.3957</v>
       </c>
       <c r="C35" t="n">
-        <v>2.1096</v>
+        <v>2.1473</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8944</v>
+        <v>0.903</v>
       </c>
       <c r="E35" t="n">
-        <v>3.336</v>
+        <v>3.3957</v>
       </c>
       <c r="F35" t="n">
-        <v>3.336</v>
+        <v>3.1818</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>4.5766</v>
+        <v>4.239</v>
       </c>
       <c r="I35" t="n">
-        <v>4.5766</v>
+        <v>4.239</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4.5766</v>
+        <v>4.239</v>
       </c>
       <c r="N35" t="n">
         <v>207</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3.2744</v>
+        <v>3.3539</v>
       </c>
       <c r="C36" t="n">
-        <v>2.0706</v>
+        <v>2.1209</v>
       </c>
       <c r="D36" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8843</v>
       </c>
       <c r="E36" t="n">
-        <v>3.2744</v>
+        <v>3.3539</v>
       </c>
       <c r="F36" t="n">
-        <v>3.2744</v>
+        <v>3.2668</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>4.4417</v>
+        <v>4.4251</v>
       </c>
       <c r="I36" t="n">
-        <v>4.4417</v>
+        <v>4.4251</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>4.4417</v>
+        <v>4.4251</v>
       </c>
       <c r="N36" t="n">
         <v>228</v>
@@ -2106,16 +2106,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.2482</v>
+        <v>3.3037</v>
       </c>
       <c r="C37" t="n">
-        <v>2.054</v>
+        <v>2.0891</v>
       </c>
       <c r="D37" t="n">
-        <v>0.8544</v>
+        <v>0.8619</v>
       </c>
       <c r="E37" t="n">
-        <v>3.2482</v>
+        <v>3.3037</v>
       </c>
       <c r="F37" t="n">
         <v>3.2482</v>
@@ -2148,47 +2148,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3.2189</v>
+        <v>3.2907</v>
       </c>
       <c r="C38" t="n">
-        <v>2.0355</v>
+        <v>2.0809</v>
       </c>
       <c r="D38" t="n">
-        <v>0.8411</v>
+        <v>0.8561</v>
       </c>
       <c r="E38" t="n">
-        <v>3.2189</v>
+        <v>3.2907</v>
       </c>
       <c r="F38" t="n">
-        <v>3.534</v>
+        <v>2.8737</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.3151</v>
+        <v>0.4981</v>
       </c>
       <c r="H38" t="n">
-        <v>5.0099</v>
+        <v>3.5647</v>
       </c>
       <c r="I38" t="n">
-        <v>5.0099</v>
+        <v>3.9466</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.3151</v>
+        <v>0.4981</v>
       </c>
       <c r="K38" t="n">
-        <v>123</v>
+        <v>316</v>
       </c>
       <c r="L38" t="n">
-        <v>175</v>
+        <v>39</v>
       </c>
       <c r="M38" t="n">
-        <v>4.6948</v>
+        <v>4.4447</v>
       </c>
       <c r="N38" t="n">
-        <v>298</v>
+        <v>355</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.185</v>
+        <v>3.2805</v>
       </c>
       <c r="C39" t="n">
-        <v>2.0141</v>
+        <v>2.0745</v>
       </c>
       <c r="D39" t="n">
-        <v>0.8257</v>
+        <v>0.8515</v>
       </c>
       <c r="E39" t="n">
-        <v>3.185</v>
+        <v>3.2805</v>
       </c>
       <c r="F39" t="n">
-        <v>3.1664</v>
+        <v>3.1662</v>
       </c>
       <c r="G39" t="n">
         <v>0.0186</v>
       </c>
       <c r="H39" t="n">
-        <v>4.2054</v>
+        <v>4.2049</v>
       </c>
       <c r="I39" t="n">
-        <v>4.7759</v>
+        <v>4.7753</v>
       </c>
       <c r="J39" t="n">
         <v>0.0186</v>
@@ -2231,7 +2231,7 @@
         <v>38</v>
       </c>
       <c r="M39" t="n">
-        <v>4.7945</v>
+        <v>4.7939</v>
       </c>
       <c r="N39" t="n">
         <v>391</v>
@@ -2240,93 +2240,93 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3.1818</v>
+        <v>3.2772</v>
       </c>
       <c r="C40" t="n">
-        <v>2.012</v>
+        <v>2.0724</v>
       </c>
       <c r="D40" t="n">
-        <v>0.8242</v>
+        <v>0.85</v>
       </c>
       <c r="E40" t="n">
-        <v>3.1818</v>
+        <v>3.2772</v>
       </c>
       <c r="F40" t="n">
-        <v>3.1818</v>
+        <v>3.0043</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>4.239</v>
+        <v>3.8506</v>
       </c>
       <c r="I40" t="n">
-        <v>4.239</v>
+        <v>3.8506</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>207</v>
+        <v>286</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.239</v>
+        <v>3.8506</v>
       </c>
       <c r="N40" t="n">
-        <v>207</v>
+        <v>286</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3.1347</v>
+        <v>3.2453</v>
       </c>
       <c r="C41" t="n">
-        <v>1.9823</v>
+        <v>2.0522</v>
       </c>
       <c r="D41" t="n">
-        <v>0.8028</v>
+        <v>0.8358</v>
       </c>
       <c r="E41" t="n">
-        <v>3.1347</v>
+        <v>3.2453</v>
       </c>
       <c r="F41" t="n">
-        <v>3.4968</v>
+        <v>3.534</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.3621</v>
+        <v>-0.3151</v>
       </c>
       <c r="H41" t="n">
-        <v>4.9284</v>
+        <v>5.0099</v>
       </c>
       <c r="I41" t="n">
-        <v>5.597</v>
+        <v>5.0099</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.3621</v>
+        <v>-0.3151</v>
       </c>
       <c r="K41" t="n">
-        <v>408</v>
+        <v>123</v>
       </c>
       <c r="L41" t="n">
-        <v>54</v>
+        <v>175</v>
       </c>
       <c r="M41" t="n">
-        <v>5.234900000000001</v>
+        <v>4.6948</v>
       </c>
       <c r="N41" t="n">
-        <v>462</v>
+        <v>298</v>
       </c>
     </row>
     <row r="42">
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.1153</v>
+        <v>3.1895</v>
       </c>
       <c r="C42" t="n">
-        <v>1.97</v>
+        <v>2.0169</v>
       </c>
       <c r="D42" t="n">
-        <v>0.7939000000000001</v>
+        <v>0.8109</v>
       </c>
       <c r="E42" t="n">
-        <v>3.1153</v>
+        <v>3.1895</v>
       </c>
       <c r="F42" t="n">
-        <v>3.6816</v>
+        <v>3.6865</v>
       </c>
       <c r="G42" t="n">
         <v>-0.5663</v>
       </c>
       <c r="H42" t="n">
-        <v>5.3329</v>
+        <v>5.3437</v>
       </c>
       <c r="I42" t="n">
-        <v>6.0564</v>
+        <v>6.0686</v>
       </c>
       <c r="J42" t="n">
         <v>-0.5663</v>
@@ -2369,7 +2369,7 @@
         <v>38</v>
       </c>
       <c r="M42" t="n">
-        <v>5.4901</v>
+        <v>5.5023</v>
       </c>
       <c r="N42" t="n">
         <v>391</v>
@@ -2378,277 +2378,277 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>s1n</t>
+          <t>arrozdoce</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.104</v>
+        <v>3.1711</v>
       </c>
       <c r="C43" t="n">
-        <v>1.9629</v>
+        <v>2.0053</v>
       </c>
       <c r="D43" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.8026</v>
       </c>
       <c r="E43" t="n">
-        <v>3.104</v>
+        <v>3.1711</v>
       </c>
       <c r="F43" t="n">
-        <v>3.104</v>
+        <v>2.9573</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>4.0687</v>
+        <v>3.7476</v>
       </c>
       <c r="I43" t="n">
-        <v>4.2811</v>
+        <v>3.7476</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>394</v>
+        <v>228</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4.2811</v>
+        <v>3.7476</v>
       </c>
       <c r="N43" t="n">
-        <v>394</v>
+        <v>228</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Goofy</t>
+          <t>JamYoung</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3.0236</v>
+        <v>3.146</v>
       </c>
       <c r="C44" t="n">
-        <v>1.912</v>
+        <v>1.9894</v>
       </c>
       <c r="D44" t="n">
-        <v>0.7522</v>
+        <v>0.7914</v>
       </c>
       <c r="E44" t="n">
-        <v>3.0236</v>
+        <v>3.146</v>
       </c>
       <c r="F44" t="n">
-        <v>3.0236</v>
+        <v>2.7688</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>3.8927</v>
+        <v>3.335</v>
       </c>
       <c r="I44" t="n">
-        <v>3.8927</v>
+        <v>3.335</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.8927</v>
+        <v>3.335</v>
       </c>
       <c r="N44" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3.0041</v>
+        <v>3.1369</v>
       </c>
       <c r="C45" t="n">
-        <v>1.8997</v>
+        <v>1.9837</v>
       </c>
       <c r="D45" t="n">
-        <v>0.7433</v>
+        <v>0.7874</v>
       </c>
       <c r="E45" t="n">
-        <v>3.0041</v>
+        <v>3.1369</v>
       </c>
       <c r="F45" t="n">
-        <v>3.0041</v>
+        <v>2.9694</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>3.85</v>
+        <v>3.7741</v>
       </c>
       <c r="I45" t="n">
-        <v>3.85</v>
+        <v>3.7741</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.85</v>
+        <v>3.7741</v>
       </c>
       <c r="N45" t="n">
-        <v>286</v>
+        <v>237</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.9694</v>
+        <v>3.1188</v>
       </c>
       <c r="C46" t="n">
-        <v>1.8777</v>
+        <v>1.9722</v>
       </c>
       <c r="D46" t="n">
-        <v>0.7275</v>
+        <v>0.7793</v>
       </c>
       <c r="E46" t="n">
-        <v>2.9694</v>
+        <v>3.1188</v>
       </c>
       <c r="F46" t="n">
-        <v>2.9694</v>
+        <v>3.4968</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>-0.3621</v>
       </c>
       <c r="H46" t="n">
-        <v>3.7741</v>
+        <v>4.9284</v>
       </c>
       <c r="I46" t="n">
-        <v>3.7741</v>
+        <v>5.597</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>-0.3621</v>
       </c>
       <c r="K46" t="n">
-        <v>237</v>
+        <v>408</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M46" t="n">
-        <v>3.7741</v>
+        <v>5.234900000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>237</v>
+        <v>462</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>arrozdoce</t>
+          <t>Goofy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.9666</v>
+        <v>3.1129</v>
       </c>
       <c r="C47" t="n">
-        <v>1.876</v>
+        <v>1.9685</v>
       </c>
       <c r="D47" t="n">
-        <v>0.7262999999999999</v>
+        <v>0.7766</v>
       </c>
       <c r="E47" t="n">
-        <v>2.9666</v>
+        <v>3.1129</v>
       </c>
       <c r="F47" t="n">
-        <v>2.9666</v>
+        <v>3.0236</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>3.7681</v>
+        <v>3.8927</v>
       </c>
       <c r="I47" t="n">
-        <v>3.7681</v>
+        <v>3.8927</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.7681</v>
+        <v>3.8927</v>
       </c>
       <c r="N47" t="n">
-        <v>228</v>
+        <v>216</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>s1n</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.822</v>
+        <v>3.0687</v>
       </c>
       <c r="C48" t="n">
-        <v>1.7845</v>
+        <v>1.9405</v>
       </c>
       <c r="D48" t="n">
-        <v>0.6604</v>
+        <v>0.7569</v>
       </c>
       <c r="E48" t="n">
-        <v>2.822</v>
+        <v>3.0687</v>
       </c>
       <c r="F48" t="n">
-        <v>2.699</v>
+        <v>3.104</v>
       </c>
       <c r="G48" t="n">
-        <v>0.123</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>3.1823</v>
+        <v>4.0687</v>
       </c>
       <c r="I48" t="n">
-        <v>3.1823</v>
+        <v>4.2811</v>
       </c>
       <c r="J48" t="n">
-        <v>0.123</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>122</v>
+        <v>394</v>
       </c>
       <c r="L48" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.3053</v>
+        <v>4.2811</v>
       </c>
       <c r="N48" t="n">
-        <v>236</v>
+        <v>394</v>
       </c>
     </row>
     <row r="49">
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.8165</v>
+        <v>3.0463</v>
       </c>
       <c r="C49" t="n">
-        <v>1.781</v>
+        <v>1.9264</v>
       </c>
       <c r="D49" t="n">
-        <v>0.6579</v>
+        <v>0.7469</v>
       </c>
       <c r="E49" t="n">
-        <v>2.8165</v>
+        <v>3.0463</v>
       </c>
       <c r="F49" t="n">
-        <v>2.8165</v>
+        <v>2.8078</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>3.4394</v>
+        <v>3.4204</v>
       </c>
       <c r="I49" t="n">
-        <v>3.4394</v>
+        <v>3.4204</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.4394</v>
+        <v>3.4204</v>
       </c>
       <c r="N49" t="n">
         <v>225</v>
@@ -2700,311 +2700,311 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.8004</v>
+        <v>2.9045</v>
       </c>
       <c r="C50" t="n">
-        <v>1.7709</v>
+        <v>1.8367</v>
       </c>
       <c r="D50" t="n">
-        <v>0.6506</v>
+        <v>0.6836</v>
       </c>
       <c r="E50" t="n">
-        <v>2.8004</v>
+        <v>2.9045</v>
       </c>
       <c r="F50" t="n">
-        <v>2.8004</v>
+        <v>2.6823</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>3.4043</v>
+        <v>3.1457</v>
       </c>
       <c r="I50" t="n">
-        <v>3.4043</v>
+        <v>3.1457</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.4043</v>
+        <v>3.1457</v>
       </c>
       <c r="N50" t="n">
-        <v>226</v>
+        <v>204</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>JamYoung</t>
+          <t>Porya</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.7688</v>
+        <v>2.8583</v>
       </c>
       <c r="C51" t="n">
-        <v>1.7509</v>
+        <v>1.8075</v>
       </c>
       <c r="D51" t="n">
-        <v>0.6362</v>
+        <v>0.6629</v>
       </c>
       <c r="E51" t="n">
-        <v>2.7688</v>
+        <v>2.8583</v>
       </c>
       <c r="F51" t="n">
-        <v>2.7688</v>
+        <v>2.7176</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>3.335</v>
+        <v>3.2231</v>
       </c>
       <c r="I51" t="n">
-        <v>3.335</v>
+        <v>3.2231</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.335</v>
+        <v>3.2231</v>
       </c>
       <c r="N51" t="n">
-        <v>219</v>
+        <v>238</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.7441</v>
+        <v>2.8135</v>
       </c>
       <c r="C52" t="n">
-        <v>1.7353</v>
+        <v>1.7792</v>
       </c>
       <c r="D52" t="n">
-        <v>0.625</v>
+        <v>0.6429</v>
       </c>
       <c r="E52" t="n">
-        <v>2.7441</v>
+        <v>2.8135</v>
       </c>
       <c r="F52" t="n">
-        <v>2.7077</v>
+        <v>2.6975</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0364</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>3.2014</v>
+        <v>3.1791</v>
       </c>
       <c r="I52" t="n">
-        <v>3.5444</v>
+        <v>3.1791</v>
       </c>
       <c r="J52" t="n">
-        <v>0.0364</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>316</v>
+        <v>219</v>
       </c>
       <c r="L52" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.5808</v>
+        <v>3.1791</v>
       </c>
       <c r="N52" t="n">
-        <v>355</v>
+        <v>219</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Porya</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.7176</v>
+        <v>2.8124</v>
       </c>
       <c r="C53" t="n">
-        <v>1.7185</v>
+        <v>1.7785</v>
       </c>
       <c r="D53" t="n">
-        <v>0.6129</v>
+        <v>0.6424</v>
       </c>
       <c r="E53" t="n">
-        <v>2.7176</v>
+        <v>2.8124</v>
       </c>
       <c r="F53" t="n">
-        <v>2.7176</v>
+        <v>2.699</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>0.123</v>
       </c>
       <c r="H53" t="n">
-        <v>3.2231</v>
+        <v>3.1823</v>
       </c>
       <c r="I53" t="n">
-        <v>3.2231</v>
+        <v>3.1823</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>0.123</v>
       </c>
       <c r="K53" t="n">
-        <v>238</v>
+        <v>122</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="M53" t="n">
-        <v>3.2231</v>
+        <v>3.3053</v>
       </c>
       <c r="N53" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>aNdu</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.6975</v>
+        <v>2.7897</v>
       </c>
       <c r="C54" t="n">
-        <v>1.7058</v>
+        <v>1.7641</v>
       </c>
       <c r="D54" t="n">
-        <v>0.6038</v>
+        <v>0.6323</v>
       </c>
       <c r="E54" t="n">
-        <v>2.6975</v>
+        <v>2.7897</v>
       </c>
       <c r="F54" t="n">
-        <v>2.6975</v>
+        <v>2.618</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>3.1791</v>
+        <v>3.0051</v>
       </c>
       <c r="I54" t="n">
-        <v>3.1791</v>
+        <v>3.0051</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.1791</v>
+        <v>3.0051</v>
       </c>
       <c r="N54" t="n">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.6823</v>
+        <v>2.764</v>
       </c>
       <c r="C55" t="n">
-        <v>1.6962</v>
+        <v>1.7478</v>
       </c>
       <c r="D55" t="n">
-        <v>0.5968</v>
+        <v>0.6208</v>
       </c>
       <c r="E55" t="n">
-        <v>2.6823</v>
+        <v>2.764</v>
       </c>
       <c r="F55" t="n">
-        <v>2.6823</v>
+        <v>2.7936</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>3.1457</v>
+        <v>3.3894</v>
       </c>
       <c r="I55" t="n">
-        <v>3.1457</v>
+        <v>3.3894</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.1457</v>
+        <v>3.3894</v>
       </c>
       <c r="N55" t="n">
-        <v>204</v>
+        <v>226</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2.6815</v>
+        <v>2.7448</v>
       </c>
       <c r="C56" t="n">
-        <v>1.6957</v>
+        <v>1.7357</v>
       </c>
       <c r="D56" t="n">
-        <v>0.5965</v>
+        <v>0.6122</v>
       </c>
       <c r="E56" t="n">
-        <v>2.6815</v>
+        <v>2.7448</v>
       </c>
       <c r="F56" t="n">
-        <v>3.1568</v>
+        <v>2.7075</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.4753</v>
+        <v>0.0364</v>
       </c>
       <c r="H56" t="n">
-        <v>4.1842</v>
+        <v>3.201</v>
       </c>
       <c r="I56" t="n">
-        <v>4.6325</v>
+        <v>3.5439</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.4753</v>
+        <v>0.0364</v>
       </c>
       <c r="K56" t="n">
         <v>316</v>
@@ -3013,7 +3013,7 @@
         <v>39</v>
       </c>
       <c r="M56" t="n">
-        <v>4.1572</v>
+        <v>3.5803</v>
       </c>
       <c r="N56" t="n">
         <v>355</v>
@@ -3022,185 +3022,185 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2.6524</v>
+        <v>2.7116</v>
       </c>
       <c r="C57" t="n">
-        <v>1.6773</v>
+        <v>1.7147</v>
       </c>
       <c r="D57" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5974</v>
       </c>
       <c r="E57" t="n">
-        <v>2.6524</v>
+        <v>2.7116</v>
       </c>
       <c r="F57" t="n">
-        <v>2.6524</v>
+        <v>3.1689</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>-0.4753</v>
       </c>
       <c r="H57" t="n">
-        <v>3.0804</v>
+        <v>4.2108</v>
       </c>
       <c r="I57" t="n">
-        <v>3.0804</v>
+        <v>4.6619</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>-0.4753</v>
       </c>
       <c r="K57" t="n">
-        <v>208</v>
+        <v>316</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M57" t="n">
-        <v>3.0804</v>
+        <v>4.1866</v>
       </c>
       <c r="N57" t="n">
-        <v>208</v>
+        <v>355</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2.6233</v>
+        <v>2.6915</v>
       </c>
       <c r="C58" t="n">
-        <v>1.6589</v>
+        <v>1.702</v>
       </c>
       <c r="D58" t="n">
-        <v>0.57</v>
+        <v>0.5884</v>
       </c>
       <c r="E58" t="n">
-        <v>2.6233</v>
+        <v>2.6915</v>
       </c>
       <c r="F58" t="n">
-        <v>2.6233</v>
+        <v>2.6524</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>3.0166</v>
+        <v>3.0804</v>
       </c>
       <c r="I58" t="n">
-        <v>3.0166</v>
+        <v>3.0804</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>251</v>
+        <v>208</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.0166</v>
+        <v>3.0804</v>
       </c>
       <c r="N58" t="n">
-        <v>251</v>
+        <v>208</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>aNdu</t>
+          <t>DGL</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2.5833</v>
+        <v>2.6542</v>
       </c>
       <c r="C59" t="n">
-        <v>1.6336</v>
+        <v>1.6784</v>
       </c>
       <c r="D59" t="n">
-        <v>0.5518</v>
+        <v>0.5718</v>
       </c>
       <c r="E59" t="n">
-        <v>2.5833</v>
+        <v>2.6542</v>
       </c>
       <c r="F59" t="n">
-        <v>2.5833</v>
+        <v>2.4418</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>2.929</v>
+        <v>2.6194</v>
       </c>
       <c r="I59" t="n">
-        <v>2.929</v>
+        <v>2.6194</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>2.929</v>
+        <v>2.6194</v>
       </c>
       <c r="N59" t="n">
-        <v>226</v>
+        <v>238</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2.5193</v>
+        <v>2.6389</v>
       </c>
       <c r="C60" t="n">
-        <v>1.5931</v>
+        <v>1.6687</v>
       </c>
       <c r="D60" t="n">
-        <v>0.5226</v>
+        <v>0.5649</v>
       </c>
       <c r="E60" t="n">
-        <v>2.5193</v>
+        <v>2.6389</v>
       </c>
       <c r="F60" t="n">
-        <v>2.1268</v>
+        <v>2.5784</v>
       </c>
       <c r="G60" t="n">
-        <v>0.3925</v>
+        <v>-0.1207</v>
       </c>
       <c r="H60" t="n">
-        <v>2.1268</v>
+        <v>2.9183</v>
       </c>
       <c r="I60" t="n">
-        <v>2.1268</v>
+        <v>2.9183</v>
       </c>
       <c r="J60" t="n">
-        <v>0.3925</v>
+        <v>-0.1207</v>
       </c>
       <c r="K60" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L60" t="n">
-        <v>172</v>
+        <v>114</v>
       </c>
       <c r="M60" t="n">
-        <v>2.5193</v>
+        <v>2.7976</v>
       </c>
       <c r="N60" t="n">
-        <v>293</v>
+        <v>236</v>
       </c>
     </row>
     <row r="61">
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2.4863</v>
+        <v>2.596</v>
       </c>
       <c r="C61" t="n">
-        <v>1.5722</v>
+        <v>1.6416</v>
       </c>
       <c r="D61" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.5458</v>
       </c>
       <c r="E61" t="n">
-        <v>2.4863</v>
+        <v>2.596</v>
       </c>
       <c r="F61" t="n">
-        <v>2.4863</v>
+        <v>2.4866</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>2.7168</v>
+        <v>2.7175</v>
       </c>
       <c r="I61" t="n">
-        <v>2.7168</v>
+        <v>2.7175</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>2.7168</v>
+        <v>2.7175</v>
       </c>
       <c r="N61" t="n">
         <v>286</v>
@@ -3252,262 +3252,262 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kRaSnaL</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2.4686</v>
+        <v>2.5944</v>
       </c>
       <c r="C62" t="n">
-        <v>1.561</v>
+        <v>1.6406</v>
       </c>
       <c r="D62" t="n">
-        <v>0.4996</v>
+        <v>0.545</v>
       </c>
       <c r="E62" t="n">
-        <v>2.4686</v>
+        <v>2.5944</v>
       </c>
       <c r="F62" t="n">
-        <v>2.4686</v>
+        <v>2.4235</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>2.6781</v>
+        <v>2.5794</v>
       </c>
       <c r="I62" t="n">
-        <v>2.7471</v>
+        <v>2.5794</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>385</v>
+        <v>208</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>2.7471</v>
+        <v>2.5794</v>
       </c>
       <c r="N62" t="n">
-        <v>385</v>
+        <v>208</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2.4577</v>
+        <v>2.5719</v>
       </c>
       <c r="C63" t="n">
-        <v>1.5542</v>
+        <v>1.6264</v>
       </c>
       <c r="D63" t="n">
-        <v>0.4946</v>
+        <v>0.535</v>
       </c>
       <c r="E63" t="n">
-        <v>2.4577</v>
+        <v>2.5719</v>
       </c>
       <c r="F63" t="n">
-        <v>2.5784</v>
+        <v>2.3936</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.1207</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>2.9183</v>
+        <v>2.514</v>
       </c>
       <c r="I63" t="n">
-        <v>2.9183</v>
+        <v>2.514</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.1207</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>122</v>
+        <v>238</v>
       </c>
       <c r="L63" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>2.7976</v>
+        <v>2.514</v>
       </c>
       <c r="N63" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>ewjerkz</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2.4486</v>
+        <v>2.5032</v>
       </c>
       <c r="C64" t="n">
-        <v>1.5484</v>
+        <v>1.5829</v>
       </c>
       <c r="D64" t="n">
-        <v>0.4904</v>
+        <v>0.5043</v>
       </c>
       <c r="E64" t="n">
-        <v>2.4486</v>
+        <v>2.5032</v>
       </c>
       <c r="F64" t="n">
-        <v>1.8735</v>
+        <v>2.3854</v>
       </c>
       <c r="G64" t="n">
-        <v>0.5750999999999999</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1.8735</v>
+        <v>2.4959</v>
       </c>
       <c r="I64" t="n">
-        <v>1.8735</v>
+        <v>2.4959</v>
       </c>
       <c r="J64" t="n">
-        <v>0.5750999999999999</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>121</v>
+        <v>228</v>
       </c>
       <c r="L64" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>2.4486</v>
+        <v>2.4959</v>
       </c>
       <c r="N64" t="n">
-        <v>293</v>
+        <v>228</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DGL</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2.4418</v>
+        <v>2.4899</v>
       </c>
       <c r="C65" t="n">
-        <v>1.5441</v>
+        <v>1.5745</v>
       </c>
       <c r="D65" t="n">
-        <v>0.4874</v>
+        <v>0.4984</v>
       </c>
       <c r="E65" t="n">
-        <v>2.4418</v>
+        <v>2.4899</v>
       </c>
       <c r="F65" t="n">
-        <v>2.4418</v>
+        <v>2.6233</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>2.6194</v>
+        <v>3.0166</v>
       </c>
       <c r="I65" t="n">
-        <v>2.6194</v>
+        <v>3.0166</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>2.6194</v>
+        <v>3.0166</v>
       </c>
       <c r="N65" t="n">
-        <v>238</v>
+        <v>251</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2.4293</v>
+        <v>2.4844</v>
       </c>
       <c r="C66" t="n">
-        <v>1.5362</v>
+        <v>1.571</v>
       </c>
       <c r="D66" t="n">
-        <v>0.4817</v>
+        <v>0.4959</v>
       </c>
       <c r="E66" t="n">
-        <v>2.4293</v>
+        <v>2.4844</v>
       </c>
       <c r="F66" t="n">
-        <v>2.4293</v>
+        <v>2.1268</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>0.3925</v>
       </c>
       <c r="H66" t="n">
-        <v>2.5921</v>
+        <v>2.1268</v>
       </c>
       <c r="I66" t="n">
-        <v>2.7977</v>
+        <v>2.1268</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>0.3925</v>
       </c>
       <c r="K66" t="n">
-        <v>372</v>
+        <v>121</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="M66" t="n">
-        <v>2.7977</v>
+        <v>2.5193</v>
       </c>
       <c r="N66" t="n">
-        <v>372</v>
+        <v>293</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2.4235</v>
+        <v>2.4565</v>
       </c>
       <c r="C67" t="n">
-        <v>1.5325</v>
+        <v>1.5534</v>
       </c>
       <c r="D67" t="n">
-        <v>0.479</v>
+        <v>0.4834</v>
       </c>
       <c r="E67" t="n">
-        <v>2.4235</v>
+        <v>2.4565</v>
       </c>
       <c r="F67" t="n">
-        <v>2.4235</v>
+        <v>2.4075</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>2.5794</v>
+        <v>2.5443</v>
       </c>
       <c r="I67" t="n">
-        <v>2.5794</v>
+        <v>2.5443</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>2.5794</v>
+        <v>2.5443</v>
       </c>
       <c r="N67" t="n">
         <v>208</v>
@@ -3532,16 +3532,16 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2.4197</v>
+        <v>2.4001</v>
       </c>
       <c r="C68" t="n">
-        <v>1.5301</v>
+        <v>1.5177</v>
       </c>
       <c r="D68" t="n">
-        <v>0.4773</v>
+        <v>0.4583</v>
       </c>
       <c r="E68" t="n">
-        <v>2.4197</v>
+        <v>2.4001</v>
       </c>
       <c r="F68" t="n">
         <v>2.4197</v>
@@ -3574,507 +3574,507 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2.4075</v>
+        <v>2.373</v>
       </c>
       <c r="C69" t="n">
-        <v>1.5224</v>
+        <v>1.5006</v>
       </c>
       <c r="D69" t="n">
-        <v>0.4717</v>
+        <v>0.4461</v>
       </c>
       <c r="E69" t="n">
-        <v>2.4075</v>
+        <v>2.373</v>
       </c>
       <c r="F69" t="n">
-        <v>2.4075</v>
+        <v>2.4054</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>2.5443</v>
+        <v>2.5398</v>
       </c>
       <c r="I69" t="n">
-        <v>2.5443</v>
+        <v>2.6052</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>208</v>
+        <v>299</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>2.5443</v>
+        <v>2.6052</v>
       </c>
       <c r="N69" t="n">
-        <v>208</v>
+        <v>299</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>kRaSnaL</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2.4054</v>
+        <v>2.3687</v>
       </c>
       <c r="C70" t="n">
-        <v>1.5211</v>
+        <v>1.4979</v>
       </c>
       <c r="D70" t="n">
-        <v>0.4708</v>
+        <v>0.4442</v>
       </c>
       <c r="E70" t="n">
-        <v>2.4054</v>
+        <v>2.3687</v>
       </c>
       <c r="F70" t="n">
-        <v>2.4054</v>
+        <v>2.4686</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>2.5398</v>
+        <v>2.6781</v>
       </c>
       <c r="I70" t="n">
-        <v>2.6052</v>
+        <v>2.7471</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>299</v>
+        <v>385</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>2.6052</v>
+        <v>2.7471</v>
       </c>
       <c r="N70" t="n">
-        <v>299</v>
+        <v>385</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SELLTER</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2.3981</v>
+        <v>2.3672</v>
       </c>
       <c r="C71" t="n">
-        <v>1.5165</v>
+        <v>1.4969</v>
       </c>
       <c r="D71" t="n">
-        <v>0.4675</v>
+        <v>0.4436</v>
       </c>
       <c r="E71" t="n">
-        <v>2.3981</v>
+        <v>2.3672</v>
       </c>
       <c r="F71" t="n">
-        <v>2.3981</v>
+        <v>2.4354</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>2.5237</v>
+        <v>2.6054</v>
       </c>
       <c r="I71" t="n">
-        <v>2.5237</v>
+        <v>2.8121</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>225</v>
+        <v>372</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>2.5237</v>
+        <v>2.8121</v>
       </c>
       <c r="N71" t="n">
-        <v>225</v>
+        <v>372</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>zorte</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2.3936</v>
+        <v>2.3424</v>
       </c>
       <c r="C72" t="n">
-        <v>1.5136</v>
+        <v>1.4812</v>
       </c>
       <c r="D72" t="n">
-        <v>0.4654</v>
+        <v>0.4325</v>
       </c>
       <c r="E72" t="n">
-        <v>2.3936</v>
+        <v>2.3424</v>
       </c>
       <c r="F72" t="n">
-        <v>2.3936</v>
+        <v>2.2877</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>2.514</v>
+        <v>2.2877</v>
       </c>
       <c r="I72" t="n">
-        <v>2.514</v>
+        <v>2.3467</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>2.514</v>
+        <v>2.3467</v>
       </c>
       <c r="N72" t="n">
-        <v>238</v>
+        <v>275</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ewjerkz</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2.3851</v>
+        <v>2.3263</v>
       </c>
       <c r="C73" t="n">
-        <v>1.5082</v>
+        <v>1.4711</v>
       </c>
       <c r="D73" t="n">
-        <v>0.4615</v>
+        <v>0.4253</v>
       </c>
       <c r="E73" t="n">
-        <v>2.3851</v>
+        <v>2.3263</v>
       </c>
       <c r="F73" t="n">
-        <v>2.3851</v>
+        <v>2.2243</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>2.4953</v>
+        <v>2.2243</v>
       </c>
       <c r="I73" t="n">
-        <v>2.4953</v>
+        <v>2.2243</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>228</v>
+        <v>286</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>2.4953</v>
+        <v>2.2243</v>
       </c>
       <c r="N73" t="n">
-        <v>228</v>
+        <v>286</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>aliStair</t>
+          <t>Woro2k</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2.3646</v>
+        <v>2.3003</v>
       </c>
       <c r="C74" t="n">
-        <v>1.4953</v>
+        <v>1.4546</v>
       </c>
       <c r="D74" t="n">
-        <v>0.4522</v>
+        <v>0.4137</v>
       </c>
       <c r="E74" t="n">
-        <v>2.3646</v>
+        <v>2.3003</v>
       </c>
       <c r="F74" t="n">
-        <v>2.3646</v>
+        <v>2.1512</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>2.4504</v>
+        <v>2.1512</v>
       </c>
       <c r="I74" t="n">
-        <v>2.6448</v>
+        <v>2.2066</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>2.6448</v>
+        <v>2.2066</v>
       </c>
       <c r="N74" t="n">
-        <v>372</v>
+        <v>385</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>zorte</t>
+          <t>SELLTER</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2.2877</v>
+        <v>2.2541</v>
       </c>
       <c r="C75" t="n">
-        <v>1.4467</v>
+        <v>1.4254</v>
       </c>
       <c r="D75" t="n">
-        <v>0.4172</v>
+        <v>0.393</v>
       </c>
       <c r="E75" t="n">
-        <v>2.2877</v>
+        <v>2.2541</v>
       </c>
       <c r="F75" t="n">
-        <v>2.2877</v>
+        <v>2.3984</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>2.2877</v>
+        <v>2.5245</v>
       </c>
       <c r="I75" t="n">
-        <v>2.3467</v>
+        <v>2.5245</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>275</v>
+        <v>225</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>2.3467</v>
+        <v>2.5245</v>
       </c>
       <c r="N75" t="n">
-        <v>275</v>
+        <v>225</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>aliStair</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2.2235</v>
+        <v>2.2345</v>
       </c>
       <c r="C76" t="n">
-        <v>1.4061</v>
+        <v>1.413</v>
       </c>
       <c r="D76" t="n">
-        <v>0.388</v>
+        <v>0.3843</v>
       </c>
       <c r="E76" t="n">
-        <v>2.2235</v>
+        <v>2.2345</v>
       </c>
       <c r="F76" t="n">
-        <v>2.2235</v>
+        <v>2.3908</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>2.2235</v>
+        <v>2.5077</v>
       </c>
       <c r="I76" t="n">
-        <v>2.2235</v>
+        <v>2.7066</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>286</v>
+        <v>372</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>2.2235</v>
+        <v>2.7066</v>
       </c>
       <c r="N76" t="n">
-        <v>286</v>
+        <v>372</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Kylar</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2.1987</v>
+        <v>2.1786</v>
       </c>
       <c r="C77" t="n">
-        <v>1.3904</v>
+        <v>1.3777</v>
       </c>
       <c r="D77" t="n">
-        <v>0.3767</v>
+        <v>0.3593</v>
       </c>
       <c r="E77" t="n">
-        <v>2.1987</v>
+        <v>2.1786</v>
       </c>
       <c r="F77" t="n">
-        <v>2.1987</v>
+        <v>1.8735</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="H77" t="n">
-        <v>2.1987</v>
+        <v>1.8735</v>
       </c>
       <c r="I77" t="n">
-        <v>2.1987</v>
+        <v>1.8735</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>216</v>
+        <v>121</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="M77" t="n">
-        <v>2.1987</v>
+        <v>2.4486</v>
       </c>
       <c r="N77" t="n">
-        <v>216</v>
+        <v>293</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Woro2k</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2.1512</v>
+        <v>2.1519</v>
       </c>
       <c r="C78" t="n">
-        <v>1.3603</v>
+        <v>1.3608</v>
       </c>
       <c r="D78" t="n">
-        <v>0.3551</v>
+        <v>0.3474</v>
       </c>
       <c r="E78" t="n">
-        <v>2.1512</v>
+        <v>2.1519</v>
       </c>
       <c r="F78" t="n">
-        <v>2.1512</v>
+        <v>2.1343</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>2.1512</v>
+        <v>2.1343</v>
       </c>
       <c r="I78" t="n">
-        <v>2.2066</v>
+        <v>2.1893</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>385</v>
+        <v>281</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>2.2066</v>
+        <v>2.1893</v>
       </c>
       <c r="N78" t="n">
-        <v>385</v>
+        <v>281</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>Kylar</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2.1343</v>
+        <v>2.1297</v>
       </c>
       <c r="C79" t="n">
-        <v>1.3497</v>
+        <v>1.3467</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3474</v>
+        <v>0.3375</v>
       </c>
       <c r="E79" t="n">
-        <v>2.1343</v>
+        <v>2.1297</v>
       </c>
       <c r="F79" t="n">
-        <v>2.1343</v>
+        <v>2.1987</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>2.1343</v>
+        <v>2.1987</v>
       </c>
       <c r="I79" t="n">
-        <v>2.1893</v>
+        <v>2.1987</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>281</v>
+        <v>216</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>2.1893</v>
+        <v>2.1987</v>
       </c>
       <c r="N79" t="n">
-        <v>281</v>
+        <v>216</v>
       </c>
     </row>
     <row r="80">
@@ -4084,16 +4084,16 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2.1012</v>
+        <v>2.1281</v>
       </c>
       <c r="C80" t="n">
-        <v>1.3287</v>
+        <v>1.3457</v>
       </c>
       <c r="D80" t="n">
-        <v>0.3323</v>
+        <v>0.3368</v>
       </c>
       <c r="E80" t="n">
-        <v>2.1012</v>
+        <v>2.1281</v>
       </c>
       <c r="F80" t="n">
         <v>2.1012</v>
@@ -4130,16 +4130,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1.9543</v>
+        <v>2.0356</v>
       </c>
       <c r="C81" t="n">
-        <v>1.2358</v>
+        <v>1.2872</v>
       </c>
       <c r="D81" t="n">
-        <v>0.2654</v>
+        <v>0.2954</v>
       </c>
       <c r="E81" t="n">
-        <v>1.9543</v>
+        <v>2.0356</v>
       </c>
       <c r="F81" t="n">
         <v>1.9543</v>
@@ -4172,185 +4172,185 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>Djoko</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1.8185</v>
+        <v>2.0309</v>
       </c>
       <c r="C82" t="n">
-        <v>1.15</v>
+        <v>1.2843</v>
       </c>
       <c r="D82" t="n">
-        <v>0.2036</v>
+        <v>0.2933</v>
       </c>
       <c r="E82" t="n">
-        <v>1.8185</v>
+        <v>2.0309</v>
       </c>
       <c r="F82" t="n">
-        <v>2.7652</v>
+        <v>1.8049</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.9467</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>3.3273</v>
+        <v>1.8049</v>
       </c>
       <c r="I82" t="n">
-        <v>3.7787</v>
+        <v>1.8049</v>
       </c>
       <c r="J82" t="n">
-        <v>-0.9467</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>353</v>
+        <v>204</v>
       </c>
       <c r="L82" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>2.832</v>
+        <v>1.8049</v>
       </c>
       <c r="N82" t="n">
-        <v>391</v>
+        <v>204</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Djoko</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1.8049</v>
+        <v>1.857</v>
       </c>
       <c r="C83" t="n">
-        <v>1.1414</v>
+        <v>1.1743</v>
       </c>
       <c r="D83" t="n">
-        <v>0.1974</v>
+        <v>0.2157</v>
       </c>
       <c r="E83" t="n">
-        <v>1.8049</v>
+        <v>1.857</v>
       </c>
       <c r="F83" t="n">
-        <v>1.8049</v>
+        <v>2.7739</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>-0.9467</v>
       </c>
       <c r="H83" t="n">
-        <v>1.8049</v>
+        <v>3.3463</v>
       </c>
       <c r="I83" t="n">
-        <v>1.8049</v>
+        <v>3.8003</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>-0.9467</v>
       </c>
       <c r="K83" t="n">
-        <v>204</v>
+        <v>353</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M83" t="n">
-        <v>1.8049</v>
+        <v>2.8536</v>
       </c>
       <c r="N83" t="n">
-        <v>204</v>
+        <v>391</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>roman</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1.7129</v>
+        <v>1.6262</v>
       </c>
       <c r="C84" t="n">
-        <v>1.0832</v>
+        <v>1.0283</v>
       </c>
       <c r="D84" t="n">
-        <v>0.1555</v>
+        <v>0.1126</v>
       </c>
       <c r="E84" t="n">
-        <v>1.7129</v>
+        <v>1.6262</v>
       </c>
       <c r="F84" t="n">
-        <v>1.7129</v>
+        <v>1.6824</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>1.7129</v>
+        <v>1.6824</v>
       </c>
       <c r="I84" t="n">
-        <v>1.7129</v>
+        <v>1.6824</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>1.7129</v>
+        <v>1.6824</v>
       </c>
       <c r="N84" t="n">
-        <v>228</v>
+        <v>207</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>roman</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1.6824</v>
+        <v>1.5883</v>
       </c>
       <c r="C85" t="n">
-        <v>1.0639</v>
+        <v>1.0044</v>
       </c>
       <c r="D85" t="n">
-        <v>0.1417</v>
+        <v>0.0956</v>
       </c>
       <c r="E85" t="n">
-        <v>1.6824</v>
+        <v>1.5883</v>
       </c>
       <c r="F85" t="n">
-        <v>1.6824</v>
+        <v>1.7139</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>1.6824</v>
+        <v>1.7139</v>
       </c>
       <c r="I85" t="n">
-        <v>1.6824</v>
+        <v>1.7139</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>1.6824</v>
+        <v>1.7139</v>
       </c>
       <c r="N85" t="n">
-        <v>207</v>
+        <v>228</v>
       </c>
     </row>
     <row r="86">
@@ -4360,28 +4360,28 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1.5754</v>
+        <v>1.5648</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9962</v>
+        <v>0.9895</v>
       </c>
       <c r="D86" t="n">
-        <v>0.093</v>
+        <v>0.0851</v>
       </c>
       <c r="E86" t="n">
-        <v>1.5754</v>
+        <v>1.5648</v>
       </c>
       <c r="F86" t="n">
-        <v>1.5754</v>
+        <v>1.5766</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>1.5754</v>
+        <v>1.5766</v>
       </c>
       <c r="I86" t="n">
-        <v>1.5754</v>
+        <v>1.5766</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -4393,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>1.5754</v>
+        <v>1.5766</v>
       </c>
       <c r="N86" t="n">
         <v>225</v>
@@ -4402,599 +4402,599 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1.5553</v>
+        <v>1.4795</v>
       </c>
       <c r="C87" t="n">
-        <v>0.9835</v>
+        <v>0.9356</v>
       </c>
       <c r="D87" t="n">
-        <v>0.0838</v>
+        <v>0.047</v>
       </c>
       <c r="E87" t="n">
-        <v>1.5553</v>
+        <v>1.4795</v>
       </c>
       <c r="F87" t="n">
-        <v>2.5357</v>
+        <v>1.2841</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.9804</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>2.825</v>
+        <v>1.2841</v>
       </c>
       <c r="I87" t="n">
-        <v>3.1276</v>
+        <v>1.2841</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.9804</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>316</v>
+        <v>237</v>
       </c>
       <c r="L87" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>2.1472</v>
+        <v>1.2841</v>
       </c>
       <c r="N87" t="n">
-        <v>355</v>
+        <v>237</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1.4845</v>
+        <v>1.4657</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9387</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="D88" t="n">
-        <v>0.0516</v>
+        <v>0.0409</v>
       </c>
       <c r="E88" t="n">
-        <v>1.4845</v>
+        <v>1.4657</v>
       </c>
       <c r="F88" t="n">
-        <v>1.4845</v>
+        <v>2.5395</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>-0.9804</v>
       </c>
       <c r="H88" t="n">
-        <v>1.4845</v>
+        <v>2.8333</v>
       </c>
       <c r="I88" t="n">
-        <v>1.4845</v>
+        <v>3.1368</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>-0.9804</v>
       </c>
       <c r="K88" t="n">
-        <v>208</v>
+        <v>316</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M88" t="n">
-        <v>1.4845</v>
+        <v>2.1564</v>
       </c>
       <c r="N88" t="n">
-        <v>208</v>
+        <v>355</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>rdnzao</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1.4386</v>
+        <v>1.3949</v>
       </c>
       <c r="C89" t="n">
-        <v>0.9097</v>
+        <v>0.8821</v>
       </c>
       <c r="D89" t="n">
-        <v>0.0307</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="E89" t="n">
-        <v>1.4386</v>
+        <v>1.3949</v>
       </c>
       <c r="F89" t="n">
-        <v>1.4386</v>
+        <v>1.4245</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>1.4386</v>
+        <v>1.4245</v>
       </c>
       <c r="I89" t="n">
-        <v>1.4386</v>
+        <v>1.4245</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>165</v>
+        <v>226</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>1.4386</v>
+        <v>1.4245</v>
       </c>
       <c r="N89" t="n">
-        <v>165</v>
+        <v>226</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>freshie</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1.4273</v>
+        <v>1.3651</v>
       </c>
       <c r="C90" t="n">
-        <v>0.9026</v>
+        <v>0.8632</v>
       </c>
       <c r="D90" t="n">
-        <v>0.0255</v>
+        <v>-0.0041</v>
       </c>
       <c r="E90" t="n">
-        <v>1.4273</v>
+        <v>1.3651</v>
       </c>
       <c r="F90" t="n">
-        <v>1.4273</v>
+        <v>1.353</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>1.4273</v>
+        <v>1.353</v>
       </c>
       <c r="I90" t="n">
-        <v>1.4273</v>
+        <v>1.353</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>208</v>
+        <v>155</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>1.4273</v>
+        <v>1.353</v>
       </c>
       <c r="N90" t="n">
-        <v>208</v>
+        <v>155</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1.4101</v>
+        <v>1.3417</v>
       </c>
       <c r="C91" t="n">
-        <v>0.8917</v>
+        <v>0.8484</v>
       </c>
       <c r="D91" t="n">
-        <v>0.0177</v>
+        <v>-0.0145</v>
       </c>
       <c r="E91" t="n">
-        <v>1.4101</v>
+        <v>1.3417</v>
       </c>
       <c r="F91" t="n">
-        <v>1.4101</v>
+        <v>1.4845</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>1.4101</v>
+        <v>1.4845</v>
       </c>
       <c r="I91" t="n">
-        <v>1.4101</v>
+        <v>1.4845</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>1.4101</v>
+        <v>1.4845</v>
       </c>
       <c r="N91" t="n">
-        <v>226</v>
+        <v>208</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>freshie</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1.3528</v>
+        <v>1.3382</v>
       </c>
       <c r="C92" t="n">
-        <v>0.8555</v>
+        <v>0.8462</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0161</v>
       </c>
       <c r="E92" t="n">
-        <v>1.3528</v>
+        <v>1.3382</v>
       </c>
       <c r="F92" t="n">
-        <v>1.3528</v>
+        <v>1.4273</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>1.3528</v>
+        <v>1.4273</v>
       </c>
       <c r="I92" t="n">
-        <v>1.3528</v>
+        <v>1.4273</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>155</v>
+        <v>208</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>1.3528</v>
+        <v>1.4273</v>
       </c>
       <c r="N92" t="n">
-        <v>155</v>
+        <v>208</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>dycha</t>
+          <t>rdnzao</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1.352</v>
+        <v>1.3307</v>
       </c>
       <c r="C93" t="n">
-        <v>0.855</v>
+        <v>0.8415</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0194</v>
       </c>
       <c r="E93" t="n">
-        <v>1.352</v>
+        <v>1.3307</v>
       </c>
       <c r="F93" t="n">
-        <v>1.352</v>
+        <v>1.4386</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>1.352</v>
+        <v>1.4386</v>
       </c>
       <c r="I93" t="n">
-        <v>1.352</v>
+        <v>1.4386</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>216</v>
+        <v>165</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>1.352</v>
+        <v>1.4386</v>
       </c>
       <c r="N93" t="n">
-        <v>216</v>
+        <v>165</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>NickelBack</t>
+          <t>r1nkle</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1.3263</v>
+        <v>1.2941</v>
       </c>
       <c r="C94" t="n">
-        <v>0.8387</v>
+        <v>0.8183</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.0204</v>
+        <v>-0.0358</v>
       </c>
       <c r="E94" t="n">
-        <v>1.3263</v>
+        <v>1.2941</v>
       </c>
       <c r="F94" t="n">
-        <v>1.3263</v>
+        <v>1.1944</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>1.3263</v>
+        <v>1.1944</v>
       </c>
       <c r="I94" t="n">
-        <v>1.3263</v>
+        <v>1.1944</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>1.3263</v>
+        <v>1.1944</v>
       </c>
       <c r="N94" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>dycha</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1.2841</v>
+        <v>1.2587</v>
       </c>
       <c r="C95" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.796</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.0397</v>
+        <v>-0.0516</v>
       </c>
       <c r="E95" t="n">
-        <v>1.2841</v>
+        <v>1.2587</v>
       </c>
       <c r="F95" t="n">
-        <v>1.2841</v>
+        <v>1.352</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>1.2841</v>
+        <v>1.352</v>
       </c>
       <c r="I95" t="n">
-        <v>1.2841</v>
+        <v>1.352</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>1.2841</v>
+        <v>1.352</v>
       </c>
       <c r="N95" t="n">
-        <v>237</v>
+        <v>216</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>reck</t>
+          <t>shalfey</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1.2673</v>
+        <v>1.2418</v>
       </c>
       <c r="C96" t="n">
-        <v>0.8014</v>
+        <v>0.7853</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.0473</v>
+        <v>-0.0591</v>
       </c>
       <c r="E96" t="n">
-        <v>1.2673</v>
+        <v>1.2418</v>
       </c>
       <c r="F96" t="n">
-        <v>1.2673</v>
+        <v>0.9916</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>1.2673</v>
+        <v>0.9916</v>
       </c>
       <c r="I96" t="n">
-        <v>1.3335</v>
+        <v>0.9916</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>394</v>
+        <v>225</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>1.3335</v>
+        <v>0.9916</v>
       </c>
       <c r="N96" t="n">
-        <v>394</v>
+        <v>225</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>afro</t>
+          <t>Cryptic</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1.2306</v>
+        <v>1.2199</v>
       </c>
       <c r="C97" t="n">
-        <v>0.7782</v>
+        <v>0.7714</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.064</v>
+        <v>-0.0689</v>
       </c>
       <c r="E97" t="n">
-        <v>1.2306</v>
+        <v>1.2199</v>
       </c>
       <c r="F97" t="n">
-        <v>1.2306</v>
+        <v>0.8702</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>1.2306</v>
+        <v>0.8702</v>
       </c>
       <c r="I97" t="n">
-        <v>1.2306</v>
+        <v>0.8702</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>240</v>
+        <v>155</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>1.2306</v>
+        <v>0.8702</v>
       </c>
       <c r="N97" t="n">
-        <v>240</v>
+        <v>155</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1.2107</v>
+        <v>1.1967</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.7567</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.0731</v>
+        <v>-0.0793</v>
       </c>
       <c r="E98" t="n">
-        <v>1.2107</v>
+        <v>1.1967</v>
       </c>
       <c r="F98" t="n">
-        <v>1.589</v>
+        <v>1.2024</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.3783</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>1.589</v>
+        <v>1.2024</v>
       </c>
       <c r="I98" t="n">
-        <v>1.589</v>
+        <v>1.2978</v>
       </c>
       <c r="J98" t="n">
-        <v>-0.3783</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>172</v>
+        <v>372</v>
       </c>
       <c r="L98" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>1.2107</v>
+        <v>1.2978</v>
       </c>
       <c r="N98" t="n">
-        <v>270</v>
+        <v>372</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>r1nkle</t>
+          <t>afro</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1.1944</v>
+        <v>1.1862</v>
       </c>
       <c r="C99" t="n">
-        <v>0.7553</v>
+        <v>0.7501</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.0805</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="E99" t="n">
-        <v>1.1944</v>
+        <v>1.1862</v>
       </c>
       <c r="F99" t="n">
-        <v>1.1944</v>
+        <v>1.2306</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>1.1944</v>
+        <v>1.2306</v>
       </c>
       <c r="I99" t="n">
-        <v>1.1944</v>
+        <v>1.2306</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>1.1944</v>
+        <v>1.2306</v>
       </c>
       <c r="N99" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
     </row>
     <row r="100">
@@ -5004,16 +5004,16 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1.1738</v>
+        <v>1.1561</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7423</v>
+        <v>0.7311</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-0.0974</v>
       </c>
       <c r="E100" t="n">
-        <v>1.1738</v>
+        <v>1.1561</v>
       </c>
       <c r="F100" t="n">
         <v>1.1738</v>
@@ -5046,369 +5046,369 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1.1735</v>
+        <v>1.1358</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7421</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.09</v>
+        <v>-0.1065</v>
       </c>
       <c r="E101" t="n">
-        <v>1.1735</v>
+        <v>1.1358</v>
       </c>
       <c r="F101" t="n">
-        <v>1.1735</v>
+        <v>2.0519</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>-0.954</v>
       </c>
       <c r="H101" t="n">
-        <v>1.1735</v>
+        <v>2.0519</v>
       </c>
       <c r="I101" t="n">
-        <v>1.2666</v>
+        <v>2.0519</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>-0.954</v>
       </c>
       <c r="K101" t="n">
-        <v>372</v>
+        <v>249</v>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M101" t="n">
-        <v>1.2666</v>
+        <v>1.0979</v>
       </c>
       <c r="N101" t="n">
-        <v>372</v>
+        <v>291</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>reck</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1.0979</v>
+        <v>1.128</v>
       </c>
       <c r="C102" t="n">
-        <v>0.6943</v>
+        <v>0.7133</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.1244</v>
+        <v>-0.11</v>
       </c>
       <c r="E102" t="n">
-        <v>1.0979</v>
+        <v>1.128</v>
       </c>
       <c r="F102" t="n">
-        <v>2.0519</v>
+        <v>1.2673</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.954</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>2.0519</v>
+        <v>1.2673</v>
       </c>
       <c r="I102" t="n">
-        <v>2.0519</v>
+        <v>1.3335</v>
       </c>
       <c r="J102" t="n">
-        <v>-0.954</v>
+        <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>249</v>
+        <v>394</v>
       </c>
       <c r="L102" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>1.0979</v>
+        <v>1.3335</v>
       </c>
       <c r="N102" t="n">
-        <v>291</v>
+        <v>394</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>doc</t>
+          <t>Vexite</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1.055</v>
+        <v>1.0767</v>
       </c>
       <c r="C103" t="n">
-        <v>0.6671</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.1439</v>
+        <v>-0.1329</v>
       </c>
       <c r="E103" t="n">
-        <v>1.055</v>
+        <v>1.0767</v>
       </c>
       <c r="F103" t="n">
-        <v>1.055</v>
+        <v>1.046</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>1.055</v>
+        <v>1.046</v>
       </c>
       <c r="I103" t="n">
-        <v>1.055</v>
+        <v>1.129</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>165</v>
+        <v>372</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>1.055</v>
+        <v>1.129</v>
       </c>
       <c r="N103" t="n">
-        <v>165</v>
+        <v>372</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Vexite</t>
+          <t>NickelBack</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1.0076</v>
+        <v>1.074</v>
       </c>
       <c r="C104" t="n">
-        <v>0.6372</v>
+        <v>0.6792</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.1655</v>
+        <v>-0.1341</v>
       </c>
       <c r="E104" t="n">
-        <v>1.0076</v>
+        <v>1.074</v>
       </c>
       <c r="F104" t="n">
-        <v>1.0076</v>
+        <v>1.3181</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>1.0076</v>
+        <v>1.3181</v>
       </c>
       <c r="I104" t="n">
-        <v>1.0875</v>
+        <v>1.3181</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>372</v>
+        <v>225</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>1.0875</v>
+        <v>1.3181</v>
       </c>
       <c r="N104" t="n">
-        <v>372</v>
+        <v>225</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>shalfey</t>
+          <t>doc</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.9996</v>
+        <v>1.07</v>
       </c>
       <c r="C105" t="n">
-        <v>0.6321</v>
+        <v>0.6766</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.1692</v>
+        <v>-0.1359</v>
       </c>
       <c r="E105" t="n">
-        <v>0.9996</v>
+        <v>1.07</v>
       </c>
       <c r="F105" t="n">
-        <v>0.9996</v>
+        <v>1.055</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>0.9996</v>
+        <v>1.055</v>
       </c>
       <c r="I105" t="n">
-        <v>0.9996</v>
+        <v>1.055</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>225</v>
+        <v>165</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>0.9996</v>
+        <v>1.055</v>
       </c>
       <c r="N105" t="n">
-        <v>225</v>
+        <v>165</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Cryptic</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.8792</v>
+        <v>0.9942</v>
       </c>
       <c r="C106" t="n">
-        <v>0.556</v>
+        <v>0.6287</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.224</v>
+        <v>-0.1697</v>
       </c>
       <c r="E106" t="n">
-        <v>0.8792</v>
+        <v>0.9942</v>
       </c>
       <c r="F106" t="n">
-        <v>0.8792</v>
+        <v>1.589</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>-0.3783</v>
       </c>
       <c r="H106" t="n">
-        <v>0.8792</v>
+        <v>1.589</v>
       </c>
       <c r="I106" t="n">
-        <v>0.8792</v>
+        <v>1.589</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
+        <v>-0.3783</v>
       </c>
       <c r="K106" t="n">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="M106" t="n">
-        <v>0.8792</v>
+        <v>1.2107</v>
       </c>
       <c r="N106" t="n">
-        <v>155</v>
+        <v>270</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>hazr</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.7486</v>
       </c>
       <c r="C107" t="n">
-        <v>0.4382</v>
+        <v>0.4734</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.3087</v>
+        <v>-0.2794</v>
       </c>
       <c r="E107" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.7486</v>
       </c>
       <c r="F107" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.5476</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.5476</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.5476</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.5476</v>
       </c>
       <c r="N107" t="n">
-        <v>240</v>
+        <v>130</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.6839</v>
+        <v>0.7084</v>
       </c>
       <c r="C108" t="n">
-        <v>0.4325</v>
+        <v>0.448</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.3129</v>
+        <v>-0.2974</v>
       </c>
       <c r="E108" t="n">
-        <v>0.6839</v>
+        <v>0.7084</v>
       </c>
       <c r="F108" t="n">
-        <v>0.6839</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>0.6839</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6839</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>0.6839</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="N108" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="109">
@@ -5418,16 +5418,16 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.6786</v>
+        <v>0.6474</v>
       </c>
       <c r="C109" t="n">
-        <v>0.4291</v>
+        <v>0.4094</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.3153</v>
+        <v>-0.3246</v>
       </c>
       <c r="E109" t="n">
-        <v>0.6786</v>
+        <v>0.6474</v>
       </c>
       <c r="F109" t="n">
         <v>0.6786</v>
@@ -5460,369 +5460,369 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>hazr</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5476</v>
+        <v>0.4865</v>
       </c>
       <c r="C110" t="n">
-        <v>0.3463</v>
+        <v>0.3076</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.3749</v>
+        <v>-0.3965</v>
       </c>
       <c r="E110" t="n">
-        <v>0.5476</v>
+        <v>0.4865</v>
       </c>
       <c r="F110" t="n">
-        <v>0.5476</v>
+        <v>0.6839</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>0.5476</v>
+        <v>0.6839</v>
       </c>
       <c r="I110" t="n">
-        <v>0.5476</v>
+        <v>0.6839</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>130</v>
+        <v>237</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>0.5476</v>
+        <v>0.6839</v>
       </c>
       <c r="N110" t="n">
-        <v>130</v>
+        <v>237</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5235</v>
+        <v>0.4242</v>
       </c>
       <c r="C111" t="n">
-        <v>0.331</v>
+        <v>0.2682</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.3859</v>
+        <v>-0.4243</v>
       </c>
       <c r="E111" t="n">
-        <v>0.5235</v>
+        <v>0.4242</v>
       </c>
       <c r="F111" t="n">
-        <v>0.5235</v>
+        <v>0.5496</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>0.5235</v>
+        <v>0.5496</v>
       </c>
       <c r="I111" t="n">
-        <v>0.5235</v>
+        <v>0.5496</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>0.5235</v>
+        <v>0.5496</v>
       </c>
       <c r="N111" t="n">
-        <v>251</v>
+        <v>226</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5182</v>
+        <v>0.3685</v>
       </c>
       <c r="C112" t="n">
-        <v>0.3277</v>
+        <v>0.233</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.3883</v>
+        <v>-0.4492</v>
       </c>
       <c r="E112" t="n">
-        <v>0.5182</v>
+        <v>0.3685</v>
       </c>
       <c r="F112" t="n">
-        <v>0.5182</v>
+        <v>0.2381</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>0.5182</v>
+        <v>0.2381</v>
       </c>
       <c r="I112" t="n">
-        <v>0.5182</v>
+        <v>0.2381</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>0.5182</v>
+        <v>0.2381</v>
       </c>
       <c r="N112" t="n">
-        <v>226</v>
+        <v>237</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>decenty</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.2381</v>
+        <v>0.3675</v>
       </c>
       <c r="C113" t="n">
-        <v>0.1506</v>
+        <v>0.2324</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.5158</v>
+        <v>-0.4497</v>
       </c>
       <c r="E113" t="n">
-        <v>0.2381</v>
+        <v>0.3675</v>
       </c>
       <c r="F113" t="n">
-        <v>0.2381</v>
+        <v>0.159</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>0.2381</v>
+        <v>0.159</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2381</v>
+        <v>0.159</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>237</v>
+        <v>151</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>0.2381</v>
+        <v>0.159</v>
       </c>
       <c r="N113" t="n">
-        <v>237</v>
+        <v>151</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.231</v>
+        <v>0.2958</v>
       </c>
       <c r="C114" t="n">
-        <v>0.1461</v>
+        <v>0.1871</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.519</v>
+        <v>-0.4817</v>
       </c>
       <c r="E114" t="n">
-        <v>0.231</v>
+        <v>0.2958</v>
       </c>
       <c r="F114" t="n">
-        <v>0.231</v>
+        <v>0.5235</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>0.231</v>
+        <v>0.5235</v>
       </c>
       <c r="I114" t="n">
-        <v>0.237</v>
+        <v>0.5235</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>281</v>
+        <v>251</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>0.237</v>
+        <v>0.5235</v>
       </c>
       <c r="N114" t="n">
-        <v>281</v>
+        <v>251</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.1869</v>
+        <v>0.1614</v>
       </c>
       <c r="C115" t="n">
-        <v>0.1182</v>
+        <v>0.1021</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.5391</v>
+        <v>-0.5417</v>
       </c>
       <c r="E115" t="n">
-        <v>0.1869</v>
+        <v>0.1614</v>
       </c>
       <c r="F115" t="n">
-        <v>0.1869</v>
+        <v>0.231</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>0.1869</v>
+        <v>0.231</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1869</v>
+        <v>0.237</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>0.1869</v>
+        <v>0.237</v>
       </c>
       <c r="N115" t="n">
-        <v>251</v>
+        <v>281</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.1723</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="C116" t="n">
-        <v>0.109</v>
+        <v>0.0615</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.5458</v>
+        <v>-0.5704</v>
       </c>
       <c r="E116" t="n">
-        <v>0.1723</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="F116" t="n">
-        <v>0.7847</v>
+        <v>0.1869</v>
       </c>
       <c r="G116" t="n">
-        <v>-0.6124000000000001</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>0.7847</v>
+        <v>0.1869</v>
       </c>
       <c r="I116" t="n">
-        <v>0.7847</v>
+        <v>0.1869</v>
       </c>
       <c r="J116" t="n">
-        <v>-0.6124000000000001</v>
+        <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>122</v>
+        <v>251</v>
       </c>
       <c r="L116" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>0.1722999999999999</v>
+        <v>0.1869</v>
       </c>
       <c r="N116" t="n">
-        <v>236</v>
+        <v>251</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>decenty</t>
+          <t>ryu</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.159</v>
+        <v>0.0124</v>
       </c>
       <c r="C117" t="n">
-        <v>0.1005</v>
+        <v>0.0078</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.5518</v>
+        <v>-0.6083</v>
       </c>
       <c r="E117" t="n">
-        <v>0.159</v>
+        <v>0.0124</v>
       </c>
       <c r="F117" t="n">
-        <v>0.159</v>
+        <v>-0.0078</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>0.159</v>
+        <v>-0.0078</v>
       </c>
       <c r="I117" t="n">
-        <v>0.159</v>
+        <v>-0.008</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>151</v>
+        <v>385</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>0.159</v>
+        <v>-0.008</v>
       </c>
       <c r="N117" t="n">
-        <v>151</v>
+        <v>385</v>
       </c>
     </row>
     <row r="118">
@@ -5832,16 +5832,16 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0067</v>
       </c>
       <c r="C118" t="n">
-        <v>0.0593</v>
+        <v>0.0042</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.5815</v>
+        <v>-0.6108</v>
       </c>
       <c r="E118" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0067</v>
       </c>
       <c r="F118" t="n">
         <v>0.09370000000000001</v>
@@ -5878,16 +5878,16 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.0707</v>
+        <v>-0.0402</v>
       </c>
       <c r="C119" t="n">
-        <v>0.0447</v>
+        <v>-0.0254</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.592</v>
+        <v>-0.6318</v>
       </c>
       <c r="E119" t="n">
-        <v>0.0707</v>
+        <v>-0.0402</v>
       </c>
       <c r="F119" t="n">
         <v>0.0707</v>
@@ -5920,323 +5920,323 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.0164</v>
+        <v>-0.1399</v>
       </c>
       <c r="C120" t="n">
-        <v>0.0104</v>
+        <v>-0.0885</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.6167</v>
+        <v>-0.6763</v>
       </c>
       <c r="E120" t="n">
-        <v>0.0164</v>
+        <v>-0.1399</v>
       </c>
       <c r="F120" t="n">
-        <v>0.0164</v>
+        <v>-0.0533</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>0.0164</v>
+        <v>-0.0533</v>
       </c>
       <c r="I120" t="n">
-        <v>0.0164</v>
+        <v>-0.0533</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>286</v>
+        <v>151</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>0.0164</v>
+        <v>-0.0533</v>
       </c>
       <c r="N120" t="n">
-        <v>286</v>
+        <v>151</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ryu</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-0.0078</v>
+        <v>-0.1528</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.0049</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.6278</v>
+        <v>-0.6821</v>
       </c>
       <c r="E121" t="n">
-        <v>-0.0078</v>
+        <v>-0.1528</v>
       </c>
       <c r="F121" t="n">
-        <v>-0.0078</v>
+        <v>-0.1609</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>-0.0078</v>
+        <v>-0.1609</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.008</v>
+        <v>-0.1609</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>385</v>
+        <v>204</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>-0.008</v>
+        <v>-0.1609</v>
       </c>
       <c r="N121" t="n">
-        <v>385</v>
+        <v>204</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-0.0322</v>
+        <v>-0.1577</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.0204</v>
+        <v>-0.0997</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.6389</v>
+        <v>-0.6843</v>
       </c>
       <c r="E122" t="n">
-        <v>-0.0322</v>
+        <v>-0.1577</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.0322</v>
+        <v>-0.0209</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>-0.0322</v>
+        <v>-0.0209</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.0322</v>
+        <v>-0.0209</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>204</v>
+        <v>286</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>-0.0322</v>
+        <v>-0.0209</v>
       </c>
       <c r="N122" t="n">
-        <v>204</v>
+        <v>286</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-0.0533</v>
+        <v>-0.1754</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.0337</v>
+        <v>-0.1109</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.6485</v>
+        <v>-0.6922</v>
       </c>
       <c r="E123" t="n">
-        <v>-0.0533</v>
+        <v>-0.1754</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.0533</v>
+        <v>-0.0322</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>-0.0533</v>
+        <v>-0.0322</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0533</v>
+        <v>-0.0322</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>151</v>
+        <v>204</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>-0.0533</v>
+        <v>-0.0322</v>
       </c>
       <c r="N123" t="n">
-        <v>151</v>
+        <v>204</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>-0.0723</v>
+        <v>-0.2027</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.0457</v>
+        <v>-0.1282</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.6571</v>
+        <v>-0.7044</v>
       </c>
       <c r="E124" t="n">
-        <v>-0.0723</v>
+        <v>-0.2027</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.2111</v>
+        <v>0.7847</v>
       </c>
       <c r="G124" t="n">
-        <v>0.1388</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="H124" t="n">
-        <v>-0.2111</v>
+        <v>0.7847</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2111</v>
+        <v>0.7847</v>
       </c>
       <c r="J124" t="n">
-        <v>0.1388</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="K124" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L124" t="n">
-        <v>172</v>
+        <v>114</v>
       </c>
       <c r="M124" t="n">
-        <v>-0.0723</v>
+        <v>0.1722999999999999</v>
       </c>
       <c r="N124" t="n">
-        <v>293</v>
+        <v>236</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>pz</t>
+          <t>drg</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-0.158</v>
+        <v>-0.2222</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.0999</v>
+        <v>-0.1405</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.6961000000000001</v>
+        <v>-0.7131</v>
       </c>
       <c r="E125" t="n">
-        <v>-0.158</v>
+        <v>-0.2222</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.158</v>
+        <v>-0.241</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>-0.158</v>
+        <v>-0.241</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.158</v>
+        <v>-0.241</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>-0.158</v>
+        <v>-0.241</v>
       </c>
       <c r="N125" t="n">
-        <v>130</v>
+        <v>165</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>-0.1609</v>
+        <v>-0.261</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.1017</v>
+        <v>-0.165</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.6974</v>
+        <v>-0.7304</v>
       </c>
       <c r="E126" t="n">
-        <v>-0.1609</v>
+        <v>-0.261</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.1609</v>
+        <v>-0.2111</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>0.1388</v>
       </c>
       <c r="H126" t="n">
-        <v>-0.1609</v>
+        <v>-0.2111</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.1609</v>
+        <v>-0.2111</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>0.1388</v>
       </c>
       <c r="K126" t="n">
-        <v>204</v>
+        <v>121</v>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="M126" t="n">
-        <v>-0.1609</v>
+        <v>-0.0723</v>
       </c>
       <c r="N126" t="n">
-        <v>204</v>
+        <v>293</v>
       </c>
     </row>
     <row r="127">
@@ -6246,16 +6246,16 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>-0.2149</v>
+        <v>-0.2875</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.1359</v>
+        <v>-0.1818</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.722</v>
+        <v>-0.7422</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.2149</v>
+        <v>-0.2875</v>
       </c>
       <c r="F127" t="n">
         <v>-0.2149</v>
@@ -6288,139 +6288,139 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>drg</t>
+          <t>PwnAlone</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-0.241</v>
+        <v>-0.3632</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.1524</v>
+        <v>-0.2297</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.7339</v>
+        <v>-0.7761</v>
       </c>
       <c r="E128" t="n">
-        <v>-0.241</v>
+        <v>-0.3632</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.241</v>
+        <v>-0.3572</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>-0.241</v>
+        <v>-0.3572</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.241</v>
+        <v>-0.3572</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>-0.241</v>
+        <v>-0.3572</v>
       </c>
       <c r="N128" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kyuubii</t>
+          <t>pz</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-0.3056</v>
+        <v>-0.3825</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.1932</v>
+        <v>-0.2419</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.7633</v>
+        <v>-0.7847</v>
       </c>
       <c r="E129" t="n">
-        <v>-0.3056</v>
+        <v>-0.3825</v>
       </c>
       <c r="F129" t="n">
-        <v>-0.3056</v>
+        <v>-0.158</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>-0.3056</v>
+        <v>-0.158</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3056</v>
+        <v>-0.158</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>-0.3056</v>
+        <v>-0.158</v>
       </c>
       <c r="N129" t="n">
-        <v>240</v>
+        <v>130</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S1ren</t>
+          <t>kyuubii</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>-0.3248</v>
+        <v>-0.4223</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.2054</v>
+        <v>-0.267</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.7721</v>
+        <v>-0.8025</v>
       </c>
       <c r="E130" t="n">
-        <v>-0.3248</v>
+        <v>-0.4223</v>
       </c>
       <c r="F130" t="n">
-        <v>-0.3248</v>
+        <v>-0.3056</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>-0.3248</v>
+        <v>-0.3056</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3332</v>
+        <v>-0.3056</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>275</v>
+        <v>240</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>-0.3332</v>
+        <v>-0.3056</v>
       </c>
       <c r="N130" t="n">
-        <v>275</v>
+        <v>240</v>
       </c>
     </row>
     <row r="131">
@@ -6430,16 +6430,16 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>-0.346</v>
+        <v>-0.5204</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.2188</v>
+        <v>-0.3291</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.7817</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="E131" t="n">
-        <v>-0.346</v>
+        <v>-0.5204</v>
       </c>
       <c r="F131" t="n">
         <v>-0.1162</v>
@@ -6472,277 +6472,277 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>PwnAlone</t>
+          <t>S1ren</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-0.3575</v>
+        <v>-0.5239</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.2261</v>
+        <v>-0.3313</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.7869</v>
+        <v>-0.8478</v>
       </c>
       <c r="E132" t="n">
-        <v>-0.3575</v>
+        <v>-0.5239</v>
       </c>
       <c r="F132" t="n">
-        <v>-0.3575</v>
+        <v>-0.3248</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>-0.3575</v>
+        <v>-0.3248</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.3575</v>
+        <v>-0.3332</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>155</v>
+        <v>275</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>-0.3575</v>
+        <v>-0.3332</v>
       </c>
       <c r="N132" t="n">
-        <v>155</v>
+        <v>275</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>FaNg</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-0.4467</v>
+        <v>-0.5451</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.2825</v>
+        <v>-0.3447</v>
       </c>
       <c r="D133" t="n">
-        <v>-0.8276</v>
+        <v>-0.8573</v>
       </c>
       <c r="E133" t="n">
-        <v>-0.4467</v>
+        <v>-0.5451</v>
       </c>
       <c r="F133" t="n">
-        <v>-0.4467</v>
+        <v>-0.5775</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>-0.4467</v>
+        <v>-0.5775</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.4467</v>
+        <v>-0.5775</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>-0.4467</v>
+        <v>-0.5775</v>
       </c>
       <c r="N133" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kye</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-0.4787</v>
+        <v>-0.5923</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.3027</v>
+        <v>-0.3745</v>
       </c>
       <c r="D134" t="n">
-        <v>-0.8421</v>
+        <v>-0.8784</v>
       </c>
       <c r="E134" t="n">
-        <v>-0.4787</v>
+        <v>-0.5923</v>
       </c>
       <c r="F134" t="n">
-        <v>-0.4787</v>
+        <v>-0.4467</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>-0.4787</v>
+        <v>-0.4467</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.4787</v>
+        <v>-0.4467</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>251</v>
+        <v>151</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>-0.4787</v>
+        <v>-0.4467</v>
       </c>
       <c r="N134" t="n">
-        <v>251</v>
+        <v>151</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>kye</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>-0.5236</v>
+        <v>-0.623</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.3311</v>
+        <v>-0.394</v>
       </c>
       <c r="D135" t="n">
-        <v>-0.8626</v>
+        <v>-0.8921</v>
       </c>
       <c r="E135" t="n">
-        <v>-0.5236</v>
+        <v>-0.623</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.5236</v>
+        <v>-0.4787</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>-0.5236</v>
+        <v>-0.4787</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.5236</v>
+        <v>-0.4787</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>216</v>
+        <v>251</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>-0.5236</v>
+        <v>-0.4787</v>
       </c>
       <c r="N135" t="n">
-        <v>216</v>
+        <v>251</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>FaNg</t>
+          <t>ADDICT</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-0.5778</v>
+        <v>-0.7481</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.3654</v>
+        <v>-0.4731</v>
       </c>
       <c r="D136" t="n">
-        <v>-0.8872</v>
+        <v>-0.948</v>
       </c>
       <c r="E136" t="n">
-        <v>-0.5778</v>
+        <v>-0.7481</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.5778</v>
+        <v>-0.8996</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>-0.5778</v>
+        <v>-0.8996</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5778</v>
+        <v>-0.8996</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>-0.5778</v>
+        <v>-0.8996</v>
       </c>
       <c r="N136" t="n">
-        <v>155</v>
+        <v>130</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-0.6859</v>
+        <v>-0.8985</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.4337</v>
+        <v>-0.5682</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.9364</v>
+        <v>-1.0152</v>
       </c>
       <c r="E137" t="n">
-        <v>-0.6859</v>
+        <v>-0.8985</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.6859</v>
+        <v>-0.5236</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>-0.6859</v>
+        <v>-0.5236</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.6859</v>
+        <v>-0.5236</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>-0.6859</v>
+        <v>-0.5236</v>
       </c>
       <c r="N137" t="n">
-        <v>207</v>
+        <v>216</v>
       </c>
     </row>
     <row r="138">
@@ -6752,16 +6752,16 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-0.7774</v>
+        <v>-0.9044</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.4916</v>
+        <v>-0.5719</v>
       </c>
       <c r="D138" t="n">
-        <v>-0.9781</v>
+        <v>-1.0178</v>
       </c>
       <c r="E138" t="n">
-        <v>-0.7774</v>
+        <v>-0.9044</v>
       </c>
       <c r="F138" t="n">
         <v>-0.7774</v>
@@ -6794,47 +6794,47 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ADDICT</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>-0.8996</v>
+        <v>-0.978</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.5689</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="D139" t="n">
-        <v>-1.0337</v>
+        <v>-1.0507</v>
       </c>
       <c r="E139" t="n">
-        <v>-0.8996</v>
+        <v>-0.978</v>
       </c>
       <c r="F139" t="n">
-        <v>-0.8996</v>
+        <v>-0.6859</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>-0.8996</v>
+        <v>-0.6859</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.8996</v>
+        <v>-0.6859</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>130</v>
+        <v>207</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>-0.8996</v>
+        <v>-0.6859</v>
       </c>
       <c r="N139" t="n">
-        <v>130</v>
+        <v>207</v>
       </c>
     </row>
     <row r="140">
@@ -6844,16 +6844,16 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>-1.0843</v>
+        <v>-1.3698</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.6857</v>
+        <v>-0.8662</v>
       </c>
       <c r="D140" t="n">
-        <v>-1.1178</v>
+        <v>-1.2257</v>
       </c>
       <c r="E140" t="n">
-        <v>-1.0843</v>
+        <v>-1.3698</v>
       </c>
       <c r="F140" t="n">
         <v>-1.0843</v>
@@ -6886,47 +6886,47 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-1.2559</v>
+        <v>-1.3952</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.7942</v>
+        <v>-0.8823</v>
       </c>
       <c r="D141" t="n">
-        <v>-1.1959</v>
+        <v>-1.237</v>
       </c>
       <c r="E141" t="n">
-        <v>-1.2559</v>
+        <v>-1.3952</v>
       </c>
       <c r="F141" t="n">
-        <v>-1.2559</v>
+        <v>-1.509</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>0.1248</v>
       </c>
       <c r="H141" t="n">
-        <v>-1.2559</v>
+        <v>-1.509</v>
       </c>
       <c r="I141" t="n">
-        <v>-1.2883</v>
+        <v>-1.509</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>0.1248</v>
       </c>
       <c r="K141" t="n">
-        <v>275</v>
+        <v>249</v>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M141" t="n">
-        <v>-1.2883</v>
+        <v>-1.3842</v>
       </c>
       <c r="N141" t="n">
-        <v>275</v>
+        <v>291</v>
       </c>
     </row>
     <row r="142">
@@ -6936,16 +6936,16 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-1.2955</v>
+        <v>-1.4594</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.8192</v>
+        <v>-0.9229000000000001</v>
       </c>
       <c r="D142" t="n">
-        <v>-1.2139</v>
+        <v>-1.2657</v>
       </c>
       <c r="E142" t="n">
-        <v>-1.2955</v>
+        <v>-1.4594</v>
       </c>
       <c r="F142" t="n">
         <v>-1.2955</v>
@@ -6978,185 +6978,185 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>kaze</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-1.3602</v>
+        <v>-1.525</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.8601</v>
+        <v>-0.9644</v>
       </c>
       <c r="D143" t="n">
-        <v>-1.2434</v>
+        <v>-1.295</v>
       </c>
       <c r="E143" t="n">
-        <v>-1.3602</v>
+        <v>-1.525</v>
       </c>
       <c r="F143" t="n">
-        <v>-1.3602</v>
+        <v>-0.6861</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>-0.6988</v>
       </c>
       <c r="H143" t="n">
-        <v>-1.3602</v>
+        <v>-0.6861</v>
       </c>
       <c r="I143" t="n">
-        <v>-1.3602</v>
+        <v>-0.7792</v>
       </c>
       <c r="J143" t="n">
-        <v>0</v>
+        <v>-0.6988</v>
       </c>
       <c r="K143" t="n">
-        <v>219</v>
+        <v>353</v>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M143" t="n">
-        <v>-1.3602</v>
+        <v>-1.478</v>
       </c>
       <c r="N143" t="n">
-        <v>219</v>
+        <v>391</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>kaze</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-1.38</v>
+        <v>-1.554</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.8727</v>
+        <v>-0.9827</v>
       </c>
       <c r="D144" t="n">
-        <v>-1.2524</v>
+        <v>-1.308</v>
       </c>
       <c r="E144" t="n">
-        <v>-1.38</v>
+        <v>-1.554</v>
       </c>
       <c r="F144" t="n">
-        <v>-1.38</v>
+        <v>-1.3602</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>-1.38</v>
+        <v>-1.3602</v>
       </c>
       <c r="I144" t="n">
-        <v>-1.38</v>
+        <v>-1.3602</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>151</v>
+        <v>219</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>-1.38</v>
+        <v>-1.3602</v>
       </c>
       <c r="N144" t="n">
-        <v>151</v>
+        <v>219</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-1.3842</v>
+        <v>-1.5741</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.8753</v>
+        <v>-0.9954</v>
       </c>
       <c r="D145" t="n">
-        <v>-1.2543</v>
+        <v>-1.3169</v>
       </c>
       <c r="E145" t="n">
-        <v>-1.3842</v>
+        <v>-1.5741</v>
       </c>
       <c r="F145" t="n">
-        <v>-1.509</v>
+        <v>-1.2559</v>
       </c>
       <c r="G145" t="n">
-        <v>0.1248</v>
+        <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>-1.509</v>
+        <v>-1.2559</v>
       </c>
       <c r="I145" t="n">
-        <v>-1.509</v>
+        <v>-1.2883</v>
       </c>
       <c r="J145" t="n">
-        <v>0.1248</v>
+        <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="L145" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>-1.3842</v>
+        <v>-1.2883</v>
       </c>
       <c r="N145" t="n">
-        <v>291</v>
+        <v>275</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-1.4118</v>
+        <v>-1.5943</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.8928</v>
+        <v>-1.0082</v>
       </c>
       <c r="D146" t="n">
-        <v>-1.2669</v>
+        <v>-1.326</v>
       </c>
       <c r="E146" t="n">
-        <v>-1.4118</v>
+        <v>-1.5943</v>
       </c>
       <c r="F146" t="n">
-        <v>-0.713</v>
+        <v>-1.38</v>
       </c>
       <c r="G146" t="n">
-        <v>-0.6988</v>
+        <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>-0.713</v>
+        <v>-1.38</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.8097</v>
+        <v>-1.38</v>
       </c>
       <c r="J146" t="n">
-        <v>-0.6988</v>
+        <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>353</v>
+        <v>151</v>
       </c>
       <c r="L146" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>-1.5085</v>
+        <v>-1.38</v>
       </c>
       <c r="N146" t="n">
-        <v>391</v>
+        <v>151</v>
       </c>
     </row>
     <row r="147">
@@ -7166,16 +7166,16 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-1.492</v>
+        <v>-1.7407</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.9435</v>
+        <v>-1.1008</v>
       </c>
       <c r="D147" t="n">
-        <v>-1.3034</v>
+        <v>-1.3914</v>
       </c>
       <c r="E147" t="n">
-        <v>-1.492</v>
+        <v>-1.7407</v>
       </c>
       <c r="F147" t="n">
         <v>-1.492</v>
@@ -7212,16 +7212,16 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-1.5554</v>
+        <v>-1.8476</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.9836</v>
+        <v>-1.1684</v>
       </c>
       <c r="D148" t="n">
-        <v>-1.3323</v>
+        <v>-1.4391</v>
       </c>
       <c r="E148" t="n">
-        <v>-1.5554</v>
+        <v>-1.8476</v>
       </c>
       <c r="F148" t="n">
         <v>-1.5554</v>
@@ -7258,16 +7258,16 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-1.6828</v>
+        <v>-1.8994</v>
       </c>
       <c r="C149" t="n">
-        <v>-1.0641</v>
+        <v>-1.2011</v>
       </c>
       <c r="D149" t="n">
-        <v>-1.3902</v>
+        <v>-1.4622</v>
       </c>
       <c r="E149" t="n">
-        <v>-1.6828</v>
+        <v>-1.8994</v>
       </c>
       <c r="F149" t="n">
         <v>-1.2864</v>
@@ -7304,28 +7304,28 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>-1.7664</v>
+        <v>-2.0505</v>
       </c>
       <c r="C150" t="n">
-        <v>-1.117</v>
+        <v>-1.2967</v>
       </c>
       <c r="D150" t="n">
-        <v>-1.4283</v>
+        <v>-1.5297</v>
       </c>
       <c r="E150" t="n">
-        <v>-1.7664</v>
+        <v>-2.0505</v>
       </c>
       <c r="F150" t="n">
-        <v>-1.7664</v>
+        <v>-1.7659</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>-1.7664</v>
+        <v>-1.7659</v>
       </c>
       <c r="I150" t="n">
-        <v>-1.7664</v>
+        <v>-1.7659</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -7337,7 +7337,7 @@
         <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>-1.7664</v>
+        <v>-1.7659</v>
       </c>
       <c r="N150" t="n">
         <v>286</v>
@@ -7346,124 +7346,124 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Bibu</t>
+          <t>Gizmy</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-1.8235</v>
+        <v>-2.0626</v>
       </c>
       <c r="C151" t="n">
-        <v>-1.1531</v>
+        <v>-1.3043</v>
       </c>
       <c r="D151" t="n">
-        <v>-1.4543</v>
+        <v>-1.5351</v>
       </c>
       <c r="E151" t="n">
-        <v>-1.8235</v>
+        <v>-2.0626</v>
       </c>
       <c r="F151" t="n">
-        <v>-1.8235</v>
+        <v>-1.9203</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
       </c>
       <c r="H151" t="n">
-        <v>-1.8235</v>
+        <v>-1.9203</v>
       </c>
       <c r="I151" t="n">
-        <v>-1.8235</v>
+        <v>-1.9698</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>238</v>
+        <v>385</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>-1.8235</v>
+        <v>-1.9698</v>
       </c>
       <c r="N151" t="n">
-        <v>238</v>
+        <v>385</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Gizmy</t>
+          <t>Bibu</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-1.9203</v>
+        <v>-2.1283</v>
       </c>
       <c r="C152" t="n">
-        <v>-1.2143</v>
+        <v>-1.3459</v>
       </c>
       <c r="D152" t="n">
-        <v>-1.4984</v>
+        <v>-1.5645</v>
       </c>
       <c r="E152" t="n">
-        <v>-1.9203</v>
+        <v>-2.1283</v>
       </c>
       <c r="F152" t="n">
-        <v>-1.9203</v>
+        <v>-1.8235</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>-1.9203</v>
+        <v>-1.8235</v>
       </c>
       <c r="I152" t="n">
-        <v>-1.9698</v>
+        <v>-1.8235</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
       </c>
       <c r="K152" t="n">
-        <v>385</v>
+        <v>238</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>-1.9698</v>
+        <v>-1.8235</v>
       </c>
       <c r="N152" t="n">
-        <v>385</v>
+        <v>238</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BRACE</t>
+          <t>damyo</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>-1.9766</v>
+        <v>-2.2167</v>
       </c>
       <c r="C153" t="n">
-        <v>-1.2499</v>
+        <v>-1.4018</v>
       </c>
       <c r="D153" t="n">
-        <v>-1.524</v>
+        <v>-1.604</v>
       </c>
       <c r="E153" t="n">
-        <v>-1.9766</v>
+        <v>-2.2167</v>
       </c>
       <c r="F153" t="n">
-        <v>-1.9766</v>
+        <v>-1.9942</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>-1.9766</v>
+        <v>-1.9942</v>
       </c>
       <c r="I153" t="n">
-        <v>-1.9766</v>
+        <v>-1.9942</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -7475,7 +7475,7 @@
         <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>-1.9766</v>
+        <v>-1.9942</v>
       </c>
       <c r="N153" t="n">
         <v>130</v>
@@ -7484,32 +7484,32 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>damyo</t>
+          <t>BRACE</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>-1.9942</v>
+        <v>-2.385</v>
       </c>
       <c r="C154" t="n">
-        <v>-1.2611</v>
+        <v>-1.5082</v>
       </c>
       <c r="D154" t="n">
-        <v>-1.532</v>
+        <v>-1.6791</v>
       </c>
       <c r="E154" t="n">
-        <v>-1.9942</v>
+        <v>-2.385</v>
       </c>
       <c r="F154" t="n">
-        <v>-1.9942</v>
+        <v>-1.9766</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>-1.9942</v>
+        <v>-1.9766</v>
       </c>
       <c r="I154" t="n">
-        <v>-1.9942</v>
+        <v>-1.9766</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -7521,7 +7521,7 @@
         <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>-1.9942</v>
+        <v>-1.9766</v>
       </c>
       <c r="N154" t="n">
         <v>130</v>
@@ -7534,28 +7534,28 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>-2.0612</v>
+        <v>-2.4681</v>
       </c>
       <c r="C155" t="n">
-        <v>-1.3034</v>
+        <v>-1.5607</v>
       </c>
       <c r="D155" t="n">
-        <v>-1.5625</v>
+        <v>-1.7163</v>
       </c>
       <c r="E155" t="n">
-        <v>-2.0612</v>
+        <v>-2.4681</v>
       </c>
       <c r="F155" t="n">
-        <v>-2.0612</v>
+        <v>-2.071</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>-2.0612</v>
+        <v>-2.071</v>
       </c>
       <c r="I155" t="n">
-        <v>-2.0612</v>
+        <v>-2.071</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -7567,7 +7567,7 @@
         <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>-2.0612</v>
+        <v>-2.071</v>
       </c>
       <c r="N155" t="n">
         <v>228</v>
@@ -7580,28 +7580,28 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-2.1271</v>
+        <v>-2.5778</v>
       </c>
       <c r="C156" t="n">
-        <v>-1.3451</v>
+        <v>-1.6301</v>
       </c>
       <c r="D156" t="n">
-        <v>-1.5925</v>
+        <v>-1.7653</v>
       </c>
       <c r="E156" t="n">
-        <v>-2.1271</v>
+        <v>-2.5778</v>
       </c>
       <c r="F156" t="n">
-        <v>-2.1271</v>
+        <v>-2.1268</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>-2.1271</v>
+        <v>-2.1268</v>
       </c>
       <c r="I156" t="n">
-        <v>-2.1271</v>
+        <v>-2.1268</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -7613,7 +7613,7 @@
         <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>-2.1271</v>
+        <v>-2.1268</v>
       </c>
       <c r="N156" t="n">
         <v>155</v>
@@ -7626,16 +7626,16 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-2.2213</v>
+        <v>-2.6828</v>
       </c>
       <c r="C157" t="n">
-        <v>-1.4047</v>
+        <v>-1.6965</v>
       </c>
       <c r="D157" t="n">
-        <v>-1.6354</v>
+        <v>-1.8122</v>
       </c>
       <c r="E157" t="n">
-        <v>-2.2213</v>
+        <v>-2.6828</v>
       </c>
       <c r="F157" t="n">
         <v>-2.2213</v>
@@ -7672,16 +7672,16 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-2.4668</v>
+        <v>-2.7308</v>
       </c>
       <c r="C158" t="n">
-        <v>-1.5599</v>
+        <v>-1.7269</v>
       </c>
       <c r="D158" t="n">
-        <v>-1.7471</v>
+        <v>-1.8336</v>
       </c>
       <c r="E158" t="n">
-        <v>-2.4668</v>
+        <v>-2.7308</v>
       </c>
       <c r="F158" t="n">
         <v>-2.4668</v>
@@ -7718,16 +7718,16 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>-2.5573</v>
+        <v>-2.8414</v>
       </c>
       <c r="C159" t="n">
-        <v>-1.6171</v>
+        <v>-1.7968</v>
       </c>
       <c r="D159" t="n">
-        <v>-1.7883</v>
+        <v>-1.883</v>
       </c>
       <c r="E159" t="n">
-        <v>-2.5573</v>
+        <v>-2.8414</v>
       </c>
       <c r="F159" t="n">
         <v>-2.5573</v>
@@ -7764,16 +7764,16 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>-3.9722</v>
+        <v>-4.3184</v>
       </c>
       <c r="C160" t="n">
-        <v>-2.5119</v>
+        <v>-2.7308</v>
       </c>
       <c r="D160" t="n">
-        <v>-2.4324</v>
+        <v>-2.5428</v>
       </c>
       <c r="E160" t="n">
-        <v>-3.9722</v>
+        <v>-4.3184</v>
       </c>
       <c r="F160" t="n">
         <v>-3.5708</v>
@@ -7810,16 +7810,16 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-4.3476</v>
+        <v>-4.9628</v>
       </c>
       <c r="C161" t="n">
-        <v>-2.7493</v>
+        <v>-3.1383</v>
       </c>
       <c r="D161" t="n">
-        <v>-2.6033</v>
+        <v>-2.8306</v>
       </c>
       <c r="E161" t="n">
-        <v>-4.3476</v>
+        <v>-4.9628</v>
       </c>
       <c r="F161" t="n">
         <v>-4.3476</v>
@@ -21523,7 +21523,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -21563,7 +21563,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -21603,7 +21603,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -21643,7 +21643,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -21683,7 +21683,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -21728,7 +21728,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D347" t="n">
@@ -21768,7 +21768,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D348" t="n">
@@ -21808,7 +21808,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D349" t="n">
@@ -21848,7 +21848,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D350" t="n">
@@ -21888,7 +21888,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D351" t="n">
@@ -21923,7 +21923,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -21963,7 +21963,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -22003,7 +22003,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -22083,7 +22083,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -22128,7 +22128,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D357" t="n">
@@ -22168,7 +22168,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D358" t="n">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D359" t="n">
@@ -22248,7 +22248,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D360" t="n">
@@ -22288,7 +22288,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D361" t="n">
@@ -22323,7 +22323,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -22363,7 +22363,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -22403,7 +22403,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -22443,7 +22443,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -22483,7 +22483,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -22528,7 +22528,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D367" t="n">
@@ -22568,7 +22568,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D368" t="n">
@@ -22608,7 +22608,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D369" t="n">
@@ -22648,7 +22648,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D370" t="n">
@@ -22688,7 +22688,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D371" t="n">
@@ -37946,19 +37946,19 @@
         <v>16</v>
       </c>
       <c r="H752" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="I752" t="n">
-        <v>1.4761</v>
+        <v>1.4612</v>
       </c>
       <c r="J752" t="n">
-        <v>23.6176</v>
+        <v>23.3792</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>sl3nd</t>
+          <t>aNdu</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
@@ -37986,19 +37986,19 @@
         <v>16</v>
       </c>
       <c r="H753" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="I753" t="n">
-        <v>1.0521</v>
+        <v>1.1282</v>
       </c>
       <c r="J753" t="n">
-        <v>16.8336</v>
+        <v>18.0512</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>aNdu</t>
+          <t>sl3nd</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
@@ -38026,13 +38026,13 @@
         <v>16</v>
       </c>
       <c r="H754" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="I754" t="n">
-        <v>1.0521</v>
+        <v>1.0642</v>
       </c>
       <c r="J754" t="n">
-        <v>16.8336</v>
+        <v>17.0272</v>
       </c>
     </row>
     <row r="755">
@@ -38066,13 +38066,13 @@
         <v>16</v>
       </c>
       <c r="H755" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="I755" t="n">
-        <v>0.9795</v>
+        <v>0.9939</v>
       </c>
       <c r="J755" t="n">
-        <v>15.672</v>
+        <v>15.9024</v>
       </c>
     </row>
     <row r="756">
@@ -38106,13 +38106,13 @@
         <v>16</v>
       </c>
       <c r="H756" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="I756" t="n">
-        <v>0.0635</v>
+        <v>0.0949</v>
       </c>
       <c r="J756" t="n">
-        <v>1.016</v>
+        <v>1.5184</v>
       </c>
     </row>
     <row r="757">
@@ -38146,13 +38146,13 @@
         <v>16</v>
       </c>
       <c r="H757" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="I757" t="n">
-        <v>0.3231</v>
+        <v>0.3041</v>
       </c>
       <c r="J757" t="n">
-        <v>5.1696</v>
+        <v>4.8656</v>
       </c>
     </row>
     <row r="758">
@@ -38189,10 +38189,10 @@
         <v>0.87</v>
       </c>
       <c r="I758" t="n">
-        <v>-0.1506</v>
+        <v>-0.1494</v>
       </c>
       <c r="J758" t="n">
-        <v>-2.4096</v>
+        <v>-2.3904</v>
       </c>
     </row>
     <row r="759">
@@ -38229,10 +38229,10 @@
         <v>0.77</v>
       </c>
       <c r="I759" t="n">
-        <v>-0.2554</v>
+        <v>-0.2546</v>
       </c>
       <c r="J759" t="n">
-        <v>-4.0864</v>
+        <v>-4.0736</v>
       </c>
     </row>
     <row r="760">
@@ -38266,13 +38266,13 @@
         <v>16</v>
       </c>
       <c r="H760" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="I760" t="n">
-        <v>-0.3994</v>
+        <v>-0.4076</v>
       </c>
       <c r="J760" t="n">
-        <v>-6.3904</v>
+        <v>-6.5216</v>
       </c>
     </row>
     <row r="761">
@@ -38306,13 +38306,13 @@
         <v>16</v>
       </c>
       <c r="H761" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="I761" t="n">
-        <v>-0.7027</v>
+        <v>-0.7107</v>
       </c>
       <c r="J761" t="n">
-        <v>-11.2432</v>
+        <v>-11.3712</v>
       </c>
     </row>
     <row r="762">
@@ -43946,13 +43946,13 @@
         <v>16</v>
       </c>
       <c r="H902" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="I902" t="n">
-        <v>1.576</v>
+        <v>1.5956</v>
       </c>
       <c r="J902" t="n">
-        <v>25.216</v>
+        <v>25.5296</v>
       </c>
     </row>
     <row r="903">
@@ -43986,13 +43986,13 @@
         <v>16</v>
       </c>
       <c r="H903" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="I903" t="n">
-        <v>0.9808</v>
+        <v>0.9952</v>
       </c>
       <c r="J903" t="n">
-        <v>15.6928</v>
+        <v>15.9232</v>
       </c>
     </row>
     <row r="904">
@@ -44026,13 +44026,13 @@
         <v>16</v>
       </c>
       <c r="H904" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="I904" t="n">
-        <v>0.9485</v>
+        <v>0.9797</v>
       </c>
       <c r="J904" t="n">
-        <v>15.176</v>
+        <v>15.6752</v>
       </c>
     </row>
     <row r="905">
@@ -44066,13 +44066,13 @@
         <v>16</v>
       </c>
       <c r="H905" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="I905" t="n">
-        <v>0.5346</v>
+        <v>0.5964</v>
       </c>
       <c r="J905" t="n">
-        <v>8.553599999999999</v>
+        <v>9.542400000000001</v>
       </c>
     </row>
     <row r="906">
@@ -44106,13 +44106,13 @@
         <v>16</v>
       </c>
       <c r="H906" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="I906" t="n">
-        <v>0.4902</v>
+        <v>0.5317</v>
       </c>
       <c r="J906" t="n">
-        <v>7.8432</v>
+        <v>8.507199999999999</v>
       </c>
     </row>
     <row r="907">
@@ -44149,10 +44149,10 @@
         <v>0.77</v>
       </c>
       <c r="I907" t="n">
-        <v>-0.2457</v>
+        <v>-0.2454</v>
       </c>
       <c r="J907" t="n">
-        <v>-3.9312</v>
+        <v>-3.9264</v>
       </c>
     </row>
     <row r="908">
@@ -44186,13 +44186,13 @@
         <v>16</v>
       </c>
       <c r="H908" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="I908" t="n">
-        <v>-0.3042</v>
+        <v>-0.3132</v>
       </c>
       <c r="J908" t="n">
-        <v>-4.8672</v>
+        <v>-5.0112</v>
       </c>
     </row>
     <row r="909">
@@ -44229,10 +44229,10 @@
         <v>0.67</v>
       </c>
       <c r="I909" t="n">
-        <v>-0.3403</v>
+        <v>-0.3401</v>
       </c>
       <c r="J909" t="n">
-        <v>-5.4448</v>
+        <v>-5.4416</v>
       </c>
     </row>
     <row r="910">
@@ -44269,10 +44269,10 @@
         <v>0.58</v>
       </c>
       <c r="I910" t="n">
-        <v>-0.4183</v>
+        <v>-0.418</v>
       </c>
       <c r="J910" t="n">
-        <v>-6.6928</v>
+        <v>-6.688</v>
       </c>
     </row>
     <row r="911">
@@ -44309,10 +44309,10 @@
         <v>0.57</v>
       </c>
       <c r="I911" t="n">
-        <v>-0.4271</v>
+        <v>-0.4268</v>
       </c>
       <c r="J911" t="n">
-        <v>-6.8336</v>
+        <v>-6.8288</v>
       </c>
     </row>
     <row r="912">
@@ -61923,7 +61923,7 @@
       </c>
       <c r="B1352" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1352" t="inlineStr">
@@ -61963,7 +61963,7 @@
       </c>
       <c r="B1353" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1353" t="inlineStr">
@@ -62003,7 +62003,7 @@
       </c>
       <c r="B1354" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1354" t="inlineStr">
@@ -62043,7 +62043,7 @@
       </c>
       <c r="B1355" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1355" t="inlineStr">
@@ -62083,7 +62083,7 @@
       </c>
       <c r="B1356" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1356" t="inlineStr">
@@ -62128,7 +62128,7 @@
       </c>
       <c r="C1357" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1357" t="n">
@@ -62168,7 +62168,7 @@
       </c>
       <c r="C1358" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1358" t="n">
@@ -62208,7 +62208,7 @@
       </c>
       <c r="C1359" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1359" t="n">
@@ -62248,7 +62248,7 @@
       </c>
       <c r="C1360" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1360" t="n">
@@ -62288,7 +62288,7 @@
       </c>
       <c r="C1361" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1361" t="n">
@@ -62323,7 +62323,7 @@
       </c>
       <c r="B1362" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1362" t="inlineStr">
@@ -62363,7 +62363,7 @@
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1363" t="inlineStr">
@@ -62403,7 +62403,7 @@
       </c>
       <c r="B1364" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1364" t="inlineStr">
@@ -62443,7 +62443,7 @@
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1365" t="inlineStr">
@@ -62483,7 +62483,7 @@
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1366" t="inlineStr">
@@ -62528,7 +62528,7 @@
       </c>
       <c r="C1367" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1367" t="n">
@@ -62568,7 +62568,7 @@
       </c>
       <c r="C1368" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1368" t="n">
@@ -62608,7 +62608,7 @@
       </c>
       <c r="C1369" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1369" t="n">
@@ -62648,7 +62648,7 @@
       </c>
       <c r="C1370" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1370" t="n">
@@ -62688,7 +62688,7 @@
       </c>
       <c r="C1371" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1371" t="n">
@@ -62723,7 +62723,7 @@
       </c>
       <c r="B1372" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1372" t="inlineStr">
@@ -62763,7 +62763,7 @@
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1373" t="inlineStr">
@@ -62803,7 +62803,7 @@
       </c>
       <c r="B1374" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1374" t="inlineStr">
@@ -62843,7 +62843,7 @@
       </c>
       <c r="B1375" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1375" t="inlineStr">
@@ -62883,7 +62883,7 @@
       </c>
       <c r="B1376" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1376" t="inlineStr">
@@ -62928,7 +62928,7 @@
       </c>
       <c r="C1377" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1377" t="n">
@@ -62968,7 +62968,7 @@
       </c>
       <c r="C1378" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1378" t="n">
@@ -63008,7 +63008,7 @@
       </c>
       <c r="C1379" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1379" t="n">
@@ -63048,7 +63048,7 @@
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1380" t="n">
@@ -63088,7 +63088,7 @@
       </c>
       <c r="C1381" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1381" t="n">
@@ -63946,13 +63946,13 @@
         <v>22</v>
       </c>
       <c r="H1402" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="I1402" t="n">
-        <v>0.504</v>
+        <v>0.5148</v>
       </c>
       <c r="J1402" t="n">
-        <v>11.088</v>
+        <v>11.3256</v>
       </c>
     </row>
     <row r="1403">
@@ -63986,13 +63986,13 @@
         <v>22</v>
       </c>
       <c r="H1403" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="I1403" t="n">
-        <v>-0.0132</v>
+        <v>0.0162</v>
       </c>
       <c r="J1403" t="n">
-        <v>-0.2904</v>
+        <v>0.3564</v>
       </c>
     </row>
     <row r="1404">
@@ -64029,10 +64029,10 @@
         <v>0.83</v>
       </c>
       <c r="I1404" t="n">
-        <v>-0.2101</v>
+        <v>-0.2106</v>
       </c>
       <c r="J1404" t="n">
-        <v>-4.6222</v>
+        <v>-4.6332</v>
       </c>
     </row>
     <row r="1405">
@@ -64066,13 +64066,13 @@
         <v>22</v>
       </c>
       <c r="H1405" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="I1405" t="n">
-        <v>-0.2497</v>
+        <v>-0.2405</v>
       </c>
       <c r="J1405" t="n">
-        <v>-5.4934</v>
+        <v>-5.291</v>
       </c>
     </row>
     <row r="1406">
@@ -64109,10 +64109,10 @@
         <v>0.43</v>
       </c>
       <c r="I1406" t="n">
-        <v>-0.5717</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="J1406" t="n">
-        <v>-12.5774</v>
+        <v>-12.5862</v>
       </c>
     </row>
     <row r="1407">
@@ -64146,13 +64146,13 @@
         <v>22</v>
       </c>
       <c r="H1407" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="I1407" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="J1407" t="n">
-        <v>16.9994</v>
+        <v>16.1788</v>
       </c>
     </row>
     <row r="1408">
@@ -64189,10 +64189,10 @@
         <v>1.36</v>
       </c>
       <c r="I1408" t="n">
-        <v>0.4716</v>
+        <v>0.4724</v>
       </c>
       <c r="J1408" t="n">
-        <v>10.3752</v>
+        <v>10.3928</v>
       </c>
     </row>
     <row r="1409">
@@ -64229,10 +64229,10 @@
         <v>1.22</v>
       </c>
       <c r="I1409" t="n">
-        <v>0.3187</v>
+        <v>0.3193</v>
       </c>
       <c r="J1409" t="n">
-        <v>7.0114</v>
+        <v>7.0246</v>
       </c>
     </row>
     <row r="1410">
@@ -64269,10 +64269,10 @@
         <v>1.17</v>
       </c>
       <c r="I1410" t="n">
-        <v>0.2581</v>
+        <v>0.2588</v>
       </c>
       <c r="J1410" t="n">
-        <v>5.6782</v>
+        <v>5.6936</v>
       </c>
     </row>
     <row r="1411">
@@ -64309,10 +64309,10 @@
         <v>0.91</v>
       </c>
       <c r="I1411" t="n">
-        <v>-0.1564</v>
+        <v>-0.1559</v>
       </c>
       <c r="J1411" t="n">
-        <v>-3.4408</v>
+        <v>-3.4298</v>
       </c>
     </row>
     <row r="1412">
@@ -67128,7 +67128,7 @@
       </c>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1482" t="n">
@@ -67168,7 +67168,7 @@
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1483" t="n">
@@ -67208,7 +67208,7 @@
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1484" t="n">
@@ -67248,7 +67248,7 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1485" t="n">
@@ -67288,7 +67288,7 @@
       </c>
       <c r="C1486" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1486" t="n">
@@ -67323,7 +67323,7 @@
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1487" t="inlineStr">
@@ -67363,7 +67363,7 @@
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1488" t="inlineStr">
@@ -67403,7 +67403,7 @@
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1489" t="inlineStr">
@@ -67443,7 +67443,7 @@
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1490" t="inlineStr">
@@ -67483,7 +67483,7 @@
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1491" t="inlineStr">
@@ -67528,7 +67528,7 @@
       </c>
       <c r="C1492" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1492" t="n">
@@ -67568,7 +67568,7 @@
       </c>
       <c r="C1493" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1493" t="n">
@@ -67608,7 +67608,7 @@
       </c>
       <c r="C1494" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1494" t="n">
@@ -67648,7 +67648,7 @@
       </c>
       <c r="C1495" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1495" t="n">
@@ -67688,7 +67688,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1496" t="n">
@@ -67723,7 +67723,7 @@
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1497" t="inlineStr">
@@ -67763,7 +67763,7 @@
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1498" t="inlineStr">
@@ -67803,7 +67803,7 @@
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1499" t="inlineStr">
@@ -67843,7 +67843,7 @@
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1500" t="inlineStr">
@@ -67883,7 +67883,7 @@
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1501" t="inlineStr">
@@ -71128,7 +71128,7 @@
       </c>
       <c r="C1582" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1582" t="n">
@@ -71168,7 +71168,7 @@
       </c>
       <c r="C1583" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1583" t="n">
@@ -71208,7 +71208,7 @@
       </c>
       <c r="C1584" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1584" t="n">
@@ -71248,7 +71248,7 @@
       </c>
       <c r="C1585" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1585" t="n">
@@ -71288,7 +71288,7 @@
       </c>
       <c r="C1586" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1586" t="n">
@@ -71323,7 +71323,7 @@
       </c>
       <c r="B1587" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1587" t="inlineStr">
@@ -71363,7 +71363,7 @@
       </c>
       <c r="B1588" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1588" t="inlineStr">
@@ -71403,7 +71403,7 @@
       </c>
       <c r="B1589" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1589" t="inlineStr">
@@ -71443,7 +71443,7 @@
       </c>
       <c r="B1590" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1590" t="inlineStr">
@@ -71483,7 +71483,7 @@
       </c>
       <c r="B1591" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1591" t="inlineStr">
@@ -71528,7 +71528,7 @@
       </c>
       <c r="C1592" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1592" t="n">
@@ -71568,7 +71568,7 @@
       </c>
       <c r="C1593" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1593" t="n">
@@ -71608,7 +71608,7 @@
       </c>
       <c r="C1594" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1594" t="n">
@@ -71648,7 +71648,7 @@
       </c>
       <c r="C1595" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1595" t="n">
@@ -71688,7 +71688,7 @@
       </c>
       <c r="C1596" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1596" t="n">
@@ -71723,7 +71723,7 @@
       </c>
       <c r="B1597" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1597" t="inlineStr">
@@ -71763,7 +71763,7 @@
       </c>
       <c r="B1598" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1598" t="inlineStr">
@@ -71803,7 +71803,7 @@
       </c>
       <c r="B1599" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1599" t="inlineStr">
@@ -71843,7 +71843,7 @@
       </c>
       <c r="B1600" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1600" t="inlineStr">
@@ -71883,7 +71883,7 @@
       </c>
       <c r="B1601" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1601" t="inlineStr">
@@ -77146,13 +77146,13 @@
         <v>24</v>
       </c>
       <c r="H1732" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="I1732" t="n">
-        <v>0.3558</v>
+        <v>0.3392</v>
       </c>
       <c r="J1732" t="n">
-        <v>8.539199999999999</v>
+        <v>8.1408</v>
       </c>
     </row>
     <row r="1733">
@@ -77189,10 +77189,10 @@
         <v>1.13</v>
       </c>
       <c r="I1733" t="n">
-        <v>0.302</v>
+        <v>0.303</v>
       </c>
       <c r="J1733" t="n">
-        <v>7.248</v>
+        <v>7.272</v>
       </c>
     </row>
     <row r="1734">
@@ -77226,13 +77226,13 @@
         <v>24</v>
       </c>
       <c r="H1734" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="I1734" t="n">
-        <v>0.1858</v>
+        <v>0.1653</v>
       </c>
       <c r="J1734" t="n">
-        <v>4.4592</v>
+        <v>3.9672</v>
       </c>
     </row>
     <row r="1735">
@@ -77269,10 +77269,10 @@
         <v>1.01</v>
       </c>
       <c r="I1735" t="n">
-        <v>0.0397</v>
+        <v>0.0403</v>
       </c>
       <c r="J1735" t="n">
-        <v>0.9528</v>
+        <v>0.9671999999999999</v>
       </c>
     </row>
     <row r="1736">
@@ -77306,13 +77306,13 @@
         <v>24</v>
       </c>
       <c r="H1736" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="I1736" t="n">
-        <v>-0.2156</v>
+        <v>-0.2254</v>
       </c>
       <c r="J1736" t="n">
-        <v>-5.1744</v>
+        <v>-5.4096</v>
       </c>
     </row>
     <row r="1737">
@@ -77346,13 +77346,13 @@
         <v>24</v>
       </c>
       <c r="H1737" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="I1737" t="n">
-        <v>1.1711</v>
+        <v>1.1833</v>
       </c>
       <c r="J1737" t="n">
-        <v>28.1064</v>
+        <v>28.3992</v>
       </c>
     </row>
     <row r="1738">
@@ -77389,10 +77389,10 @@
         <v>1.11</v>
       </c>
       <c r="I1738" t="n">
-        <v>0.3492</v>
+        <v>0.3486</v>
       </c>
       <c r="J1738" t="n">
-        <v>8.380800000000001</v>
+        <v>8.366400000000001</v>
       </c>
     </row>
     <row r="1739">
@@ -77426,13 +77426,13 @@
         <v>24</v>
       </c>
       <c r="H1739" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I1739" t="n">
-        <v>0.1549</v>
+        <v>0.1854</v>
       </c>
       <c r="J1739" t="n">
-        <v>3.7176</v>
+        <v>4.4496</v>
       </c>
     </row>
     <row r="1740">
@@ -77469,10 +77469,10 @@
         <v>1.04</v>
       </c>
       <c r="I1740" t="n">
-        <v>0.1549</v>
+        <v>0.1539</v>
       </c>
       <c r="J1740" t="n">
-        <v>3.7176</v>
+        <v>3.6936</v>
       </c>
     </row>
     <row r="1741">
@@ -77506,13 +77506,13 @@
         <v>24</v>
       </c>
       <c r="H1741" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="I1741" t="n">
-        <v>-0.6532</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="J1741" t="n">
-        <v>-15.6768</v>
+        <v>-15.1584</v>
       </c>
     </row>
     <row r="1742">
@@ -79528,7 +79528,7 @@
       </c>
       <c r="C1792" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1792" t="n">
@@ -79568,7 +79568,7 @@
       </c>
       <c r="C1793" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1793" t="n">
@@ -79608,7 +79608,7 @@
       </c>
       <c r="C1794" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1794" t="n">
@@ -79648,7 +79648,7 @@
       </c>
       <c r="C1795" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1795" t="n">
@@ -79688,7 +79688,7 @@
       </c>
       <c r="C1796" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1796" t="n">
@@ -79723,7 +79723,7 @@
       </c>
       <c r="B1797" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1797" t="inlineStr">
@@ -79763,7 +79763,7 @@
       </c>
       <c r="B1798" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1798" t="inlineStr">
@@ -79803,7 +79803,7 @@
       </c>
       <c r="B1799" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1799" t="inlineStr">
@@ -79843,7 +79843,7 @@
       </c>
       <c r="B1800" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1800" t="inlineStr">
@@ -79883,7 +79883,7 @@
       </c>
       <c r="B1801" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1801" t="inlineStr">
@@ -79928,7 +79928,7 @@
       </c>
       <c r="C1802" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1802" t="n">
@@ -79968,7 +79968,7 @@
       </c>
       <c r="C1803" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1803" t="n">
@@ -80008,7 +80008,7 @@
       </c>
       <c r="C1804" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1804" t="n">
@@ -80048,7 +80048,7 @@
       </c>
       <c r="C1805" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1805" t="n">
@@ -80088,7 +80088,7 @@
       </c>
       <c r="C1806" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1806" t="n">
@@ -80123,7 +80123,7 @@
       </c>
       <c r="B1807" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1807" t="inlineStr">
@@ -80163,7 +80163,7 @@
       </c>
       <c r="B1808" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1808" t="inlineStr">
@@ -80203,7 +80203,7 @@
       </c>
       <c r="B1809" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1809" t="inlineStr">
@@ -80243,7 +80243,7 @@
       </c>
       <c r="B1810" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1810" t="inlineStr">
@@ -80283,7 +80283,7 @@
       </c>
       <c r="B1811" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1811" t="inlineStr">
@@ -80328,7 +80328,7 @@
       </c>
       <c r="C1812" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1812" t="n">
@@ -80368,7 +80368,7 @@
       </c>
       <c r="C1813" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1813" t="n">
@@ -80408,7 +80408,7 @@
       </c>
       <c r="C1814" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1814" t="n">
@@ -80448,7 +80448,7 @@
       </c>
       <c r="C1815" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1815" t="n">
@@ -80488,7 +80488,7 @@
       </c>
       <c r="C1816" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D1816" t="n">
@@ -80523,7 +80523,7 @@
       </c>
       <c r="B1817" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1817" t="inlineStr">
@@ -80563,7 +80563,7 @@
       </c>
       <c r="B1818" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1818" t="inlineStr">
@@ -80603,7 +80603,7 @@
       </c>
       <c r="B1819" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1819" t="inlineStr">
@@ -80643,7 +80643,7 @@
       </c>
       <c r="B1820" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1820" t="inlineStr">
@@ -80683,7 +80683,7 @@
       </c>
       <c r="B1821" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C1821" t="inlineStr">
